--- a/demo_output/test/prompt_7/figure_00_Globale aktiemarkeder — indekseret kursudvikl.xlsx
+++ b/demo_output/test/prompt_7/figure_00_Globale aktiemarkeder — indekseret kursudvikl.xlsx
@@ -37934,7 +37934,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>48.14879608154297</v>
+        <v>48.14879989624023</v>
       </c>
     </row>
     <row r="4">
@@ -37944,7 +37944,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>48.50472259521484</v>
+        <v>48.50472640991211</v>
       </c>
     </row>
     <row r="5">
@@ -37964,7 +37964,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>48.8250732421875</v>
+        <v>48.82506942749023</v>
       </c>
     </row>
     <row r="7">
@@ -37974,7 +37974,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>49.83058166503906</v>
+        <v>49.83057403564453</v>
       </c>
     </row>
     <row r="8">
@@ -37984,7 +37984,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>49.91065979003906</v>
+        <v>49.91066360473633</v>
       </c>
     </row>
     <row r="9">
@@ -37994,7 +37994,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>49.37676239013672</v>
+        <v>49.37676620483398</v>
       </c>
     </row>
     <row r="10">
@@ -38004,7 +38004,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>49.82168579101562</v>
+        <v>49.82167434692383</v>
       </c>
     </row>
     <row r="11">
@@ -38014,7 +38014,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>49.57252883911133</v>
+        <v>49.5725212097168</v>
       </c>
     </row>
     <row r="12">
@@ -38024,7 +38024,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>49.33227157592773</v>
+        <v>49.332275390625</v>
       </c>
     </row>
     <row r="13">
@@ -38044,7 +38044,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>49.58403396606445</v>
+        <v>49.58402633666992</v>
       </c>
     </row>
     <row r="15">
@@ -38054,7 +38054,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>49.41422271728516</v>
+        <v>49.41422653198242</v>
       </c>
     </row>
     <row r="16">
@@ -38074,7 +38074,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>49.20867156982422</v>
+        <v>49.20866775512695</v>
       </c>
     </row>
     <row r="18">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>48.53836822509766</v>
+        <v>48.53837585449219</v>
       </c>
     </row>
     <row r="19">
@@ -38094,7 +38094,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>48.80649566650391</v>
+        <v>48.80648803710938</v>
       </c>
     </row>
     <row r="20">
@@ -38114,7 +38114,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>48.67242813110352</v>
+        <v>48.67243194580078</v>
       </c>
     </row>
     <row r="22">
@@ -38144,7 +38144,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>49.1907958984375</v>
+        <v>49.19079208374023</v>
       </c>
     </row>
     <row r="25">
@@ -38174,7 +38174,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>49.61084365844727</v>
+        <v>49.61083984375</v>
       </c>
     </row>
     <row r="28">
@@ -38184,7 +38184,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>49.28910064697266</v>
+        <v>49.28910446166992</v>
       </c>
     </row>
     <row r="29">
@@ -38204,7 +38204,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>48.95841598510742</v>
+        <v>48.95842361450195</v>
       </c>
     </row>
     <row r="31">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>48.10044097900391</v>
+        <v>48.10044479370117</v>
       </c>
     </row>
     <row r="32">
@@ -38224,7 +38224,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>48.04682540893555</v>
+        <v>48.04681396484375</v>
       </c>
     </row>
     <row r="33">
@@ -38234,7 +38234,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>47.04584884643555</v>
+        <v>47.04584121704102</v>
       </c>
     </row>
     <row r="34">
@@ -38244,7 +38244,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>47.859130859375</v>
+        <v>47.85913848876953</v>
       </c>
     </row>
     <row r="35">
@@ -38254,7 +38254,7 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>47.9038200378418</v>
+        <v>47.90382385253906</v>
       </c>
     </row>
     <row r="36">
@@ -38274,7 +38274,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>48.1540641784668</v>
+        <v>48.15406799316406</v>
       </c>
     </row>
     <row r="38">
@@ -38284,7 +38284,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>48.27024841308594</v>
+        <v>48.27024459838867</v>
       </c>
     </row>
     <row r="39">
@@ -38294,7 +38294,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>47.89488220214844</v>
+        <v>47.8948860168457</v>
       </c>
     </row>
     <row r="40">
@@ -38304,7 +38304,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>47.09052658081055</v>
+        <v>47.09053039550781</v>
       </c>
     </row>
     <row r="41">
@@ -38314,7 +38314,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>47.24246978759766</v>
+        <v>47.24246597290039</v>
       </c>
     </row>
     <row r="42">
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>47.54633331298828</v>
+        <v>47.54634094238281</v>
       </c>
     </row>
     <row r="43">
@@ -38334,7 +38334,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>47.63570022583008</v>
+        <v>47.63571166992188</v>
       </c>
     </row>
     <row r="44">
@@ -38344,7 +38344,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46.92966079711914</v>
+        <v>46.92966461181641</v>
       </c>
     </row>
     <row r="45">
@@ -38354,7 +38354,7 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46.03593444824219</v>
+        <v>46.03593063354492</v>
       </c>
     </row>
     <row r="46">
@@ -38364,7 +38364,7 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45.10646057128906</v>
+        <v>45.10644912719727</v>
       </c>
     </row>
     <row r="47">
@@ -38384,7 +38384,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46.56323623657227</v>
+        <v>46.56322860717773</v>
       </c>
     </row>
     <row r="49">
@@ -38404,7 +38404,7 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46.44705200195312</v>
+        <v>46.44704818725586</v>
       </c>
     </row>
     <row r="51">
@@ -38414,7 +38414,7 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46.64367294311523</v>
+        <v>46.6436653137207</v>
       </c>
     </row>
     <row r="52">
@@ -38434,7 +38434,7 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46.8134765625</v>
+        <v>46.81346893310547</v>
       </c>
     </row>
     <row r="54">
@@ -38444,7 +38444,7 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46.42023086547852</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="55">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46.57216644287109</v>
+        <v>46.57216262817383</v>
       </c>
     </row>
     <row r="56">
@@ -38464,7 +38464,7 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46.63472747802734</v>
+        <v>46.63473129272461</v>
       </c>
     </row>
     <row r="57">
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46.75984573364258</v>
+        <v>46.75985336303711</v>
       </c>
     </row>
     <row r="58">
@@ -38484,7 +38484,7 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46.34873962402344</v>
+        <v>46.34873580932617</v>
       </c>
     </row>
     <row r="59">
@@ -38494,7 +38494,7 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46.2325553894043</v>
+        <v>46.23255157470703</v>
       </c>
     </row>
     <row r="60">
@@ -38504,7 +38504,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45.81249618530273</v>
+        <v>45.8125</v>
       </c>
     </row>
     <row r="61">
@@ -38514,7 +38514,7 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>44.97239303588867</v>
+        <v>44.9724006652832</v>
       </c>
     </row>
     <row r="62">
@@ -38534,7 +38534,7 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>44.27528762817383</v>
+        <v>44.27529144287109</v>
       </c>
     </row>
     <row r="64">
@@ -38554,7 +38554,7 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>44.90983963012695</v>
+        <v>44.90983581542969</v>
       </c>
     </row>
     <row r="66">
@@ -38574,7 +38574,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45.98230743408203</v>
+        <v>45.9823112487793</v>
       </c>
     </row>
     <row r="68">
@@ -38604,7 +38604,7 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46.20574569702148</v>
+        <v>46.20574188232422</v>
       </c>
     </row>
     <row r="71">
@@ -38614,7 +38614,7 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46.84028625488281</v>
+        <v>46.84028244018555</v>
       </c>
     </row>
     <row r="72">
@@ -38624,7 +38624,7 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>47.43908309936523</v>
+        <v>47.4390869140625</v>
       </c>
     </row>
     <row r="73">
@@ -38634,7 +38634,7 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>47.2245979309082</v>
+        <v>47.22458648681641</v>
       </c>
     </row>
     <row r="74">
@@ -38664,7 +38664,7 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>47.05477905273438</v>
+        <v>47.05478286743164</v>
       </c>
     </row>
     <row r="77">
@@ -38684,7 +38684,7 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46.91178894042969</v>
+        <v>46.91178512573242</v>
       </c>
     </row>
     <row r="79">
@@ -38704,7 +38704,7 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46.64367294311523</v>
+        <v>46.6436653137207</v>
       </c>
     </row>
     <row r="81">
@@ -38714,7 +38714,7 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46.63472747802734</v>
+        <v>46.63473129272461</v>
       </c>
     </row>
     <row r="82">
@@ -38734,7 +38734,7 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45.91081237792969</v>
+        <v>45.91080856323242</v>
       </c>
     </row>
     <row r="84">
@@ -38754,7 +38754,7 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45.00814437866211</v>
+        <v>45.00814056396484</v>
       </c>
     </row>
     <row r="86">
@@ -38764,7 +38764,7 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45.57118988037109</v>
+        <v>45.57119750976562</v>
       </c>
     </row>
     <row r="87">
@@ -38784,7 +38784,7 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45.38351058959961</v>
+        <v>45.38350677490234</v>
       </c>
     </row>
     <row r="89">
@@ -38814,7 +38814,7 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>44.66852951049805</v>
+        <v>44.66853332519531</v>
       </c>
     </row>
     <row r="92">
@@ -38824,7 +38824,7 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45.02602767944336</v>
+        <v>45.02602386474609</v>
       </c>
     </row>
     <row r="93">
@@ -38844,7 +38844,7 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>44.31997299194336</v>
+        <v>44.31997680664062</v>
       </c>
     </row>
     <row r="95">
@@ -38854,7 +38854,7 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>44.63278198242188</v>
+        <v>44.63277816772461</v>
       </c>
     </row>
     <row r="96">
@@ -38924,7 +38924,7 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45.86612701416016</v>
+        <v>45.86612319946289</v>
       </c>
     </row>
     <row r="103">
@@ -38934,7 +38934,7 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46.42023086547852</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="104">
@@ -38954,7 +38954,7 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46.92071914672852</v>
+        <v>46.92072296142578</v>
       </c>
     </row>
     <row r="106">
@@ -38964,7 +38964,7 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46.91178894042969</v>
+        <v>46.91178512573242</v>
       </c>
     </row>
     <row r="107">
@@ -38974,7 +38974,7 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46.60792541503906</v>
+        <v>46.60791397094727</v>
       </c>
     </row>
     <row r="108">
@@ -38994,7 +38994,7 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46.75091552734375</v>
+        <v>46.75091934204102</v>
       </c>
     </row>
     <row r="110">
@@ -39014,7 +39014,7 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46.13424301147461</v>
+        <v>46.13424682617188</v>
       </c>
     </row>
     <row r="112">
@@ -39034,7 +39034,7 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50862884521484</v>
       </c>
     </row>
     <row r="114">
@@ -39044,7 +39044,7 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45.86612701416016</v>
+        <v>45.86612319946289</v>
       </c>
     </row>
     <row r="115">
@@ -39084,7 +39084,7 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50862884521484</v>
       </c>
     </row>
     <row r="119">
@@ -39104,7 +39104,7 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45.74994659423828</v>
+        <v>45.74993515014648</v>
       </c>
     </row>
     <row r="121">
@@ -39124,7 +39124,7 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46.34873962402344</v>
+        <v>46.34873580932617</v>
       </c>
     </row>
     <row r="123">
@@ -39144,7 +39144,7 @@
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46.32192993164062</v>
+        <v>46.32192611694336</v>
       </c>
     </row>
     <row r="125">
@@ -39154,7 +39154,7 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46.38448333740234</v>
+        <v>46.38449096679688</v>
       </c>
     </row>
     <row r="126">
@@ -39164,7 +39164,7 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46.14318466186523</v>
+        <v>46.14318084716797</v>
       </c>
     </row>
     <row r="127">
@@ -39174,7 +39174,7 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45.58012771606445</v>
+        <v>45.58013153076172</v>
       </c>
     </row>
     <row r="128">
@@ -39184,7 +39184,7 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50862884521484</v>
       </c>
     </row>
     <row r="129">
@@ -39214,7 +39214,7 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45.03495407104492</v>
+        <v>45.03495788574219</v>
       </c>
     </row>
     <row r="132">
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>43.52455520629883</v>
+        <v>43.52455902099609</v>
       </c>
     </row>
     <row r="133">
@@ -39234,7 +39234,7 @@
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>43.69436264038086</v>
+        <v>43.69436645507812</v>
       </c>
     </row>
     <row r="134">
@@ -39244,7 +39244,7 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>43.64968109130859</v>
+        <v>43.64967727661133</v>
       </c>
     </row>
     <row r="135">
@@ -39254,7 +39254,7 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>43.81055450439453</v>
+        <v>43.810546875</v>
       </c>
     </row>
     <row r="136">
@@ -39264,7 +39264,7 @@
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>44.34678649902344</v>
+        <v>44.3467903137207</v>
       </c>
     </row>
     <row r="137">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>44.93664932250977</v>
+        <v>44.9366455078125</v>
       </c>
     </row>
     <row r="141">
@@ -39344,7 +39344,7 @@
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>43.94837188720703</v>
+        <v>43.9483757019043</v>
       </c>
     </row>
     <row r="145">
@@ -39354,7 +39354,7 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>43.82146072387695</v>
+        <v>43.82146453857422</v>
       </c>
     </row>
     <row r="146">
@@ -39364,7 +39364,7 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>43.87585067749023</v>
+        <v>43.8758544921875</v>
       </c>
     </row>
     <row r="147">
@@ -39374,7 +39374,7 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>43.65829086303711</v>
+        <v>43.65828704833984</v>
       </c>
     </row>
     <row r="148">
@@ -39394,7 +39394,7 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>43.73080825805664</v>
+        <v>43.73081207275391</v>
       </c>
     </row>
     <row r="150">
@@ -39404,7 +39404,7 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>43.93930816650391</v>
+        <v>43.93931198120117</v>
       </c>
     </row>
     <row r="151">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>44.22033309936523</v>
+        <v>44.22032928466797</v>
       </c>
     </row>
     <row r="154">
@@ -39444,7 +39444,7 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>44.02090454101562</v>
+        <v>44.02090072631836</v>
       </c>
     </row>
     <row r="155">
@@ -39454,7 +39454,7 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>44.52519607543945</v>
+        <v>44.52519226074219</v>
       </c>
     </row>
     <row r="156">
@@ -39464,7 +39464,7 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>44.30751037597656</v>
+        <v>44.3075065612793</v>
       </c>
     </row>
     <row r="157">
@@ -39484,7 +39484,7 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>44.47077560424805</v>
+        <v>44.47076797485352</v>
       </c>
     </row>
     <row r="159">
@@ -39494,7 +39494,7 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>43.74516296386719</v>
+        <v>43.74516677856445</v>
       </c>
     </row>
     <row r="160">
@@ -39514,7 +39514,7 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>44.34379196166992</v>
+        <v>44.34379577636719</v>
       </c>
     </row>
     <row r="162">
@@ -39524,7 +39524,7 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>44.34379196166992</v>
+        <v>44.34379577636719</v>
       </c>
     </row>
     <row r="163">
@@ -39534,7 +39534,7 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45.36870956420898</v>
+        <v>45.36871719360352</v>
       </c>
     </row>
     <row r="164">
@@ -39554,7 +39554,7 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>45.46848678588867</v>
+        <v>45.46849060058594</v>
       </c>
     </row>
     <row r="166">
@@ -39564,7 +39564,7 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45.45035171508789</v>
+        <v>45.45034790039062</v>
       </c>
     </row>
     <row r="167">
@@ -39584,7 +39584,7 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>44.83357620239258</v>
+        <v>44.83358001708984</v>
       </c>
     </row>
     <row r="169">
@@ -39604,7 +39604,7 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>44.44356155395508</v>
+        <v>44.44356536865234</v>
       </c>
     </row>
     <row r="171">
@@ -39624,7 +39624,7 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>43.7360954284668</v>
+        <v>43.73609161376953</v>
       </c>
     </row>
     <row r="173">
@@ -39634,7 +39634,7 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>43.18281936645508</v>
+        <v>43.18281173706055</v>
       </c>
     </row>
     <row r="174">
@@ -39654,7 +39654,7 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>42.89257431030273</v>
+        <v>42.892578125</v>
       </c>
     </row>
     <row r="176">
@@ -39664,7 +39664,7 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>44.29844284057617</v>
+        <v>44.29843521118164</v>
       </c>
     </row>
     <row r="177">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>44.57054138183594</v>
+        <v>44.57054901123047</v>
       </c>
     </row>
     <row r="178">
@@ -39694,7 +39694,7 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>44.02634048461914</v>
+        <v>44.02634429931641</v>
       </c>
     </row>
     <row r="180">
@@ -39704,7 +39704,7 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>44.13518142700195</v>
+        <v>44.13517761230469</v>
       </c>
     </row>
     <row r="181">
@@ -39724,7 +39724,7 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>44.47077560424805</v>
+        <v>44.47076797485352</v>
       </c>
     </row>
     <row r="183">
@@ -39744,7 +39744,7 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>44.86986541748047</v>
+        <v>44.8698616027832</v>
       </c>
     </row>
     <row r="185">
@@ -39754,7 +39754,7 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>44.18959808349609</v>
+        <v>44.18960189819336</v>
       </c>
     </row>
     <row r="186">
@@ -39764,7 +39764,7 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>43.88122177124023</v>
+        <v>43.88121795654297</v>
       </c>
     </row>
     <row r="187">
@@ -39774,7 +39774,7 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>44.83357620239258</v>
+        <v>44.83358001708984</v>
       </c>
     </row>
     <row r="188">
@@ -39804,7 +39804,7 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>44.18959808349609</v>
+        <v>44.18960189819336</v>
       </c>
     </row>
     <row r="191">
@@ -39844,7 +39844,7 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>42.94699859619141</v>
+        <v>42.94699478149414</v>
       </c>
     </row>
     <row r="195">
@@ -39854,7 +39854,7 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>42.38464736938477</v>
+        <v>42.3846435546875</v>
       </c>
     </row>
     <row r="196">
@@ -39874,7 +39874,7 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>41.89485931396484</v>
+        <v>41.89485549926758</v>
       </c>
     </row>
     <row r="198">
@@ -39884,7 +39884,7 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>41.30530548095703</v>
+        <v>41.30530166625977</v>
       </c>
     </row>
     <row r="199">
@@ -39894,7 +39894,7 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>40.47084808349609</v>
+        <v>40.47085189819336</v>
       </c>
     </row>
     <row r="200">
@@ -39904,7 +39904,7 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>38.95614242553711</v>
+        <v>38.95613861083984</v>
       </c>
     </row>
     <row r="201">
@@ -39914,7 +39914,7 @@
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>39.08312225341797</v>
+        <v>39.08312606811523</v>
       </c>
     </row>
     <row r="202">
@@ -39924,7 +39924,7 @@
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>40.18967437744141</v>
+        <v>40.18968200683594</v>
       </c>
     </row>
     <row r="203">
@@ -39934,7 +39934,7 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>39.43685531616211</v>
+        <v>39.43686294555664</v>
       </c>
     </row>
     <row r="204">
@@ -39944,7 +39944,7 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>38.61148452758789</v>
+        <v>38.61148071289062</v>
       </c>
     </row>
     <row r="205">
@@ -39964,7 +39964,7 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>37.73167419433594</v>
+        <v>37.7316780090332</v>
       </c>
     </row>
     <row r="207">
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>40.77016448974609</v>
+        <v>40.77017211914062</v>
       </c>
     </row>
     <row r="208">
@@ -39984,7 +39984,7 @@
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>40.56155395507812</v>
+        <v>40.56156158447266</v>
       </c>
     </row>
     <row r="209">
@@ -39994,7 +39994,7 @@
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>41.14204406738281</v>
+        <v>41.14204025268555</v>
       </c>
     </row>
     <row r="210">
@@ -40004,7 +40004,7 @@
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>40.50713729858398</v>
+        <v>40.50712966918945</v>
       </c>
     </row>
     <row r="211">
@@ -40014,7 +40014,7 @@
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>41.24181365966797</v>
+        <v>41.24181747436523</v>
       </c>
     </row>
     <row r="212">
@@ -40024,7 +40024,7 @@
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>40.96969985961914</v>
+        <v>40.96970367431641</v>
       </c>
     </row>
     <row r="213">
@@ -40034,7 +40034,7 @@
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>41.18739318847656</v>
+        <v>41.18739700317383</v>
       </c>
     </row>
     <row r="214">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>40.86086273193359</v>
+        <v>40.86087417602539</v>
       </c>
     </row>
     <row r="215">
@@ -40054,7 +40054,7 @@
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>40.99692153930664</v>
+        <v>40.99691772460938</v>
       </c>
     </row>
     <row r="216">
@@ -40064,7 +40064,7 @@
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>41.69532012939453</v>
+        <v>41.6953239440918</v>
       </c>
     </row>
     <row r="217">
@@ -40074,7 +40074,7 @@
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>41.5774040222168</v>
+        <v>41.57740783691406</v>
       </c>
     </row>
     <row r="218">
@@ -40094,7 +40094,7 @@
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>41.63182830810547</v>
+        <v>41.6318244934082</v>
       </c>
     </row>
     <row r="220">
@@ -40104,7 +40104,7 @@
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>42.36650848388672</v>
+        <v>42.36650466918945</v>
       </c>
     </row>
     <row r="221">
@@ -40114,7 +40114,7 @@
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>41.58647155761719</v>
+        <v>41.58648300170898</v>
       </c>
     </row>
     <row r="222">
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>41.04227828979492</v>
+        <v>41.04227066040039</v>
       </c>
     </row>
     <row r="223">
@@ -40134,7 +40134,7 @@
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>40.71574783325195</v>
+        <v>40.71574401855469</v>
       </c>
     </row>
     <row r="224">
@@ -40164,7 +40164,7 @@
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>40.11711502075195</v>
+        <v>40.11711883544922</v>
       </c>
     </row>
     <row r="227">
@@ -40174,7 +40174,7 @@
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>40.6431884765625</v>
+        <v>40.64319229125977</v>
       </c>
     </row>
     <row r="228">
@@ -40184,7 +40184,7 @@
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>40.11711502075195</v>
+        <v>40.11711883544922</v>
       </c>
     </row>
     <row r="229">
@@ -40194,7 +40194,7 @@
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>39.98106384277344</v>
+        <v>39.98107147216797</v>
       </c>
     </row>
     <row r="230">
@@ -40204,7 +40204,7 @@
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>39.78152847290039</v>
+        <v>39.78152084350586</v>
       </c>
     </row>
     <row r="231">
@@ -40224,7 +40224,7 @@
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>38.78380966186523</v>
+        <v>38.78380584716797</v>
       </c>
     </row>
     <row r="233">
@@ -40234,7 +40234,7 @@
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>38.43914794921875</v>
+        <v>38.43915176391602</v>
       </c>
     </row>
     <row r="234">
@@ -40244,7 +40244,7 @@
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>38.1579704284668</v>
+        <v>38.15796661376953</v>
       </c>
     </row>
     <row r="235">
@@ -40264,7 +40264,7 @@
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>37.75889205932617</v>
+        <v>37.75888824462891</v>
       </c>
     </row>
     <row r="237">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>38.43914794921875</v>
+        <v>38.43915176391602</v>
       </c>
     </row>
     <row r="239">
@@ -40294,7 +40294,7 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>38.38472747802734</v>
+        <v>38.38472366333008</v>
       </c>
     </row>
     <row r="240">
@@ -40304,7 +40304,7 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>38.66590118408203</v>
+        <v>38.6659049987793</v>
       </c>
     </row>
     <row r="241">
@@ -40314,7 +40314,7 @@
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>39.08312225341797</v>
+        <v>39.08312606811523</v>
       </c>
     </row>
     <row r="242">
@@ -40324,7 +40324,7 @@
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>37.64097595214844</v>
+        <v>37.6409797668457</v>
       </c>
     </row>
     <row r="243">
@@ -40334,7 +40334,7 @@
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>37.12397766113281</v>
+        <v>37.12398147583008</v>
       </c>
     </row>
     <row r="244">
@@ -40354,7 +40354,7 @@
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>36.22603988647461</v>
+        <v>36.22603607177734</v>
       </c>
     </row>
     <row r="246">
@@ -40364,7 +40364,7 @@
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>35.97208404541016</v>
+        <v>35.97208023071289</v>
       </c>
     </row>
     <row r="247">
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>37.16026306152344</v>
+        <v>37.1602668762207</v>
       </c>
     </row>
     <row r="253">
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>36.94257736206055</v>
+        <v>36.94257354736328</v>
       </c>
     </row>
     <row r="256">
@@ -40464,7 +40464,7 @@
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>37.12397766113281</v>
+        <v>37.12398147583008</v>
       </c>
     </row>
     <row r="257">
@@ -40494,7 +40494,7 @@
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>38.67497634887695</v>
+        <v>38.67497253417969</v>
       </c>
     </row>
     <row r="260">
@@ -40504,7 +40504,7 @@
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>38.40287017822266</v>
+        <v>38.40286636352539</v>
       </c>
     </row>
     <row r="261">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>38.43007659912109</v>
+        <v>38.43008041381836</v>
       </c>
     </row>
     <row r="263">
@@ -40534,7 +40534,7 @@
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>38.63868713378906</v>
+        <v>38.63869476318359</v>
       </c>
     </row>
     <row r="264">
@@ -40554,7 +40554,7 @@
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>38.96521377563477</v>
+        <v>38.96521759033203</v>
       </c>
     </row>
     <row r="266">
@@ -40564,7 +40564,7 @@
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>38.04317855834961</v>
+        <v>38.04317474365234</v>
       </c>
     </row>
     <row r="267">
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>37.62240600585938</v>
+        <v>37.62240219116211</v>
       </c>
     </row>
     <row r="268">
@@ -40584,7 +40584,7 @@
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>36.30520629882812</v>
+        <v>36.30521011352539</v>
       </c>
     </row>
     <row r="269">
@@ -40604,7 +40604,7 @@
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>37.2931022644043</v>
+        <v>37.29310989379883</v>
       </c>
     </row>
     <row r="271">
@@ -40614,7 +40614,7 @@
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>36.14971160888672</v>
+        <v>36.14970779418945</v>
       </c>
     </row>
     <row r="272">
@@ -40634,7 +40634,7 @@
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>36.87233734130859</v>
+        <v>36.87234115600586</v>
       </c>
     </row>
     <row r="274">
@@ -40644,7 +40644,7 @@
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>36.21374130249023</v>
+        <v>36.21373748779297</v>
       </c>
     </row>
     <row r="275">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>36.32350158691406</v>
+        <v>36.3234977722168</v>
       </c>
     </row>
     <row r="276">
@@ -40664,7 +40664,7 @@
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>37.18334197998047</v>
+        <v>37.1833381652832</v>
       </c>
     </row>
     <row r="277">
@@ -40684,7 +40684,7 @@
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>37.00040054321289</v>
+        <v>37.00039672851562</v>
       </c>
     </row>
     <row r="279">
@@ -40704,7 +40704,7 @@
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>36.68024444580078</v>
+        <v>36.68024826049805</v>
       </c>
     </row>
     <row r="281">
@@ -40714,7 +40714,7 @@
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>36.45156478881836</v>
+        <v>36.45156097412109</v>
       </c>
     </row>
     <row r="282">
@@ -40734,7 +40734,7 @@
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>35.94846725463867</v>
+        <v>35.94847106933594</v>
       </c>
     </row>
     <row r="284">
@@ -40744,7 +40744,7 @@
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>36.67109680175781</v>
+        <v>36.67109298706055</v>
       </c>
     </row>
     <row r="285">
@@ -40754,7 +40754,7 @@
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>36.67109680175781</v>
+        <v>36.67109298706055</v>
       </c>
     </row>
     <row r="286">
@@ -40774,7 +40774,7 @@
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>35.55513763427734</v>
+        <v>35.55513381958008</v>
       </c>
     </row>
     <row r="288">
@@ -40784,7 +40784,7 @@
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>35.47281265258789</v>
+        <v>35.47281646728516</v>
       </c>
     </row>
     <row r="289">
@@ -40804,7 +40804,7 @@
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>35.33560943603516</v>
+        <v>35.33560562133789</v>
       </c>
     </row>
     <row r="291">
@@ -40814,7 +40814,7 @@
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>35.58257675170898</v>
+        <v>35.58258438110352</v>
       </c>
     </row>
     <row r="292">
@@ -40834,7 +40834,7 @@
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>36.01249694824219</v>
+        <v>36.01250457763672</v>
       </c>
     </row>
     <row r="294">
@@ -40854,7 +40854,7 @@
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>36.0582389831543</v>
+        <v>36.05823135375977</v>
       </c>
     </row>
     <row r="296">
@@ -40864,7 +40864,7 @@
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>36.18629837036133</v>
+        <v>36.1862907409668</v>
       </c>
     </row>
     <row r="297">
@@ -40904,7 +40904,7 @@
         </is>
       </c>
       <c r="B300" s="2" t="n">
-        <v>36.55218505859375</v>
+        <v>36.55218124389648</v>
       </c>
     </row>
     <row r="301">
@@ -40914,7 +40914,7 @@
         </is>
       </c>
       <c r="B301" s="2" t="n">
-        <v>36.24117660522461</v>
+        <v>36.24118041992188</v>
       </c>
     </row>
     <row r="302">
@@ -40944,7 +40944,7 @@
         </is>
       </c>
       <c r="B304" s="2" t="n">
-        <v>36.60707092285156</v>
+        <v>36.6070671081543</v>
       </c>
     </row>
     <row r="305">
@@ -40954,7 +40954,7 @@
         </is>
       </c>
       <c r="B305" s="2" t="n">
-        <v>36.64365386962891</v>
+        <v>36.64366149902344</v>
       </c>
     </row>
     <row r="306">
@@ -40964,7 +40964,7 @@
         </is>
       </c>
       <c r="B306" s="2" t="n">
-        <v>36.68938827514648</v>
+        <v>36.68939208984375</v>
       </c>
     </row>
     <row r="307">
@@ -40974,7 +40974,7 @@
         </is>
       </c>
       <c r="B307" s="2" t="n">
-        <v>36.55218505859375</v>
+        <v>36.55218124389648</v>
       </c>
     </row>
     <row r="308">
@@ -41004,7 +41004,7 @@
         </is>
       </c>
       <c r="B310" s="2" t="n">
-        <v>37.54923248291016</v>
+        <v>37.54922485351562</v>
       </c>
     </row>
     <row r="311">
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="B312" s="2" t="n">
-        <v>37.36627960205078</v>
+        <v>37.36628341674805</v>
       </c>
     </row>
     <row r="313">
@@ -41044,7 +41044,7 @@
         </is>
       </c>
       <c r="B314" s="2" t="n">
-        <v>37.00040054321289</v>
+        <v>37.00039672851562</v>
       </c>
     </row>
     <row r="315">
@@ -41064,7 +41064,7 @@
         </is>
       </c>
       <c r="B316" s="2" t="n">
-        <v>36.17715072631836</v>
+        <v>36.17715454101562</v>
       </c>
     </row>
     <row r="317">
@@ -41084,7 +41084,7 @@
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>36.36008834838867</v>
+        <v>36.3600959777832</v>
       </c>
     </row>
     <row r="319">
@@ -41104,7 +41104,7 @@
         </is>
       </c>
       <c r="B320" s="2" t="n">
-        <v>36.59792327880859</v>
+        <v>36.59791946411133</v>
       </c>
     </row>
     <row r="321">
@@ -41124,7 +41124,7 @@
         </is>
       </c>
       <c r="B322" s="2" t="n">
-        <v>35.9393196105957</v>
+        <v>35.93932342529297</v>
       </c>
     </row>
     <row r="323">
@@ -41144,7 +41144,7 @@
         </is>
       </c>
       <c r="B324" s="2" t="n">
-        <v>35.78381729125977</v>
+        <v>35.78382110595703</v>
       </c>
     </row>
     <row r="325">
@@ -41214,7 +41214,7 @@
         </is>
       </c>
       <c r="B331" s="2" t="n">
-        <v>35.08863067626953</v>
+        <v>35.0886344909668</v>
       </c>
     </row>
     <row r="332">
@@ -41224,7 +41224,7 @@
         </is>
       </c>
       <c r="B332" s="2" t="n">
-        <v>35.26243591308594</v>
+        <v>35.26242446899414</v>
       </c>
     </row>
     <row r="333">
@@ -41234,7 +41234,7 @@
         </is>
       </c>
       <c r="B333" s="2" t="n">
-        <v>34.88739776611328</v>
+        <v>34.88739013671875</v>
       </c>
     </row>
     <row r="334">
@@ -41244,7 +41244,7 @@
         </is>
       </c>
       <c r="B334" s="2" t="n">
-        <v>34.56724548339844</v>
+        <v>34.56723785400391</v>
       </c>
     </row>
     <row r="335">
@@ -41294,7 +41294,7 @@
         </is>
       </c>
       <c r="B339" s="2" t="n">
-        <v>32.91159820556641</v>
+        <v>32.91160583496094</v>
       </c>
     </row>
     <row r="340">
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="B342" s="2" t="n">
-        <v>32.75609970092773</v>
+        <v>32.756103515625</v>
       </c>
     </row>
     <row r="343">
@@ -41344,7 +41344,7 @@
         </is>
       </c>
       <c r="B344" s="2" t="n">
-        <v>31.90541076660156</v>
+        <v>31.90540885925293</v>
       </c>
     </row>
     <row r="345">
@@ -41364,7 +41364,7 @@
         </is>
       </c>
       <c r="B346" s="2" t="n">
-        <v>33.48787689208984</v>
+        <v>33.48788452148438</v>
       </c>
     </row>
     <row r="347">
@@ -41384,7 +41384,7 @@
         </is>
       </c>
       <c r="B348" s="2" t="n">
-        <v>33.30492782592773</v>
+        <v>33.304931640625</v>
       </c>
     </row>
     <row r="349">
@@ -41394,7 +41394,7 @@
         </is>
       </c>
       <c r="B349" s="2" t="n">
-        <v>32.60974884033203</v>
+        <v>32.60974502563477</v>
       </c>
     </row>
     <row r="350">
@@ -41404,7 +41404,7 @@
         </is>
       </c>
       <c r="B350" s="2" t="n">
-        <v>32.15238189697266</v>
+        <v>32.15238571166992</v>
       </c>
     </row>
     <row r="351">
@@ -41414,7 +41414,7 @@
         </is>
       </c>
       <c r="B351" s="2" t="n">
-        <v>31.64014053344727</v>
+        <v>31.6401424407959</v>
       </c>
     </row>
     <row r="352">
@@ -41434,7 +41434,7 @@
         </is>
       </c>
       <c r="B353" s="2" t="n">
-        <v>31.7681999206543</v>
+        <v>31.76820182800293</v>
       </c>
     </row>
     <row r="354">
@@ -41454,7 +41454,7 @@
         </is>
       </c>
       <c r="B355" s="2" t="n">
-        <v>32.15238189697266</v>
+        <v>32.15238571166992</v>
       </c>
     </row>
     <row r="356">
@@ -41464,7 +41464,7 @@
         </is>
       </c>
       <c r="B356" s="2" t="n">
-        <v>32.16153717041016</v>
+        <v>32.16152954101562</v>
       </c>
     </row>
     <row r="357">
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="B357" s="2" t="n">
-        <v>31.57610893249512</v>
+        <v>31.57611465454102</v>
       </c>
     </row>
     <row r="358">
@@ -41484,7 +41484,7 @@
         </is>
       </c>
       <c r="B358" s="2" t="n">
-        <v>31.77735328674316</v>
+        <v>31.77734756469727</v>
       </c>
     </row>
     <row r="359">
@@ -41494,7 +41494,7 @@
         </is>
       </c>
       <c r="B359" s="2" t="n">
-        <v>32.26215362548828</v>
+        <v>32.26214981079102</v>
       </c>
     </row>
     <row r="360">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="B360" s="2" t="n">
-        <v>31.03642845153809</v>
+        <v>31.03642654418945</v>
       </c>
     </row>
     <row r="361">
@@ -41534,7 +41534,7 @@
         </is>
       </c>
       <c r="B363" s="2" t="n">
-        <v>31.55782127380371</v>
+        <v>31.55781936645508</v>
       </c>
     </row>
     <row r="364">
@@ -41554,7 +41554,7 @@
         </is>
       </c>
       <c r="B365" s="2" t="n">
-        <v>31.27425193786621</v>
+        <v>31.27425003051758</v>
       </c>
     </row>
     <row r="366">
@@ -41564,7 +41564,7 @@
         </is>
       </c>
       <c r="B366" s="2" t="n">
-        <v>31.85052490234375</v>
+        <v>31.85052680969238</v>
       </c>
     </row>
     <row r="367">
@@ -41574,7 +41574,7 @@
         </is>
       </c>
       <c r="B367" s="2" t="n">
-        <v>31.58525466918945</v>
+        <v>31.58525657653809</v>
       </c>
     </row>
     <row r="368">
@@ -41584,7 +41584,7 @@
         </is>
       </c>
       <c r="B368" s="2" t="n">
-        <v>31.7681999206543</v>
+        <v>31.76820182800293</v>
       </c>
     </row>
     <row r="369">
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="B370" s="2" t="n">
-        <v>33.13113403320312</v>
+        <v>33.13113021850586</v>
       </c>
     </row>
     <row r="371">
@@ -41634,7 +41634,7 @@
         </is>
       </c>
       <c r="B373" s="2" t="n">
-        <v>33.98182678222656</v>
+        <v>33.9818229675293</v>
       </c>
     </row>
     <row r="374">
@@ -41644,7 +41644,7 @@
         </is>
       </c>
       <c r="B374" s="2" t="n">
-        <v>34.90568923950195</v>
+        <v>34.90568542480469</v>
       </c>
     </row>
     <row r="375">
@@ -41654,7 +41654,7 @@
         </is>
       </c>
       <c r="B375" s="2" t="n">
-        <v>34.6953010559082</v>
+        <v>34.69529724121094</v>
       </c>
     </row>
     <row r="376">
@@ -41674,7 +41674,7 @@
         </is>
       </c>
       <c r="B377" s="2" t="n">
-        <v>34.92398834228516</v>
+        <v>34.92398452758789</v>
       </c>
     </row>
     <row r="378">
@@ -41684,7 +41684,7 @@
         </is>
       </c>
       <c r="B378" s="2" t="n">
-        <v>34.98801803588867</v>
+        <v>34.98801422119141</v>
       </c>
     </row>
     <row r="379">
@@ -41694,7 +41694,7 @@
         </is>
       </c>
       <c r="B379" s="2" t="n">
-        <v>34.78676986694336</v>
+        <v>34.78677749633789</v>
       </c>
     </row>
     <row r="380">
@@ -41704,7 +41704,7 @@
         </is>
       </c>
       <c r="B380" s="2" t="n">
-        <v>34.34770584106445</v>
+        <v>34.34771347045898</v>
       </c>
     </row>
     <row r="381">
@@ -41734,7 +41734,7 @@
         </is>
       </c>
       <c r="B383" s="2" t="n">
-        <v>34.5489501953125</v>
+        <v>34.54895401000977</v>
       </c>
     </row>
     <row r="384">
@@ -41744,7 +41744,7 @@
         </is>
       </c>
       <c r="B384" s="2" t="n">
-        <v>34.39344787597656</v>
+        <v>34.3934440612793</v>
       </c>
     </row>
     <row r="385">
@@ -41754,7 +41754,7 @@
         </is>
       </c>
       <c r="B385" s="2" t="n">
-        <v>35.13436508178711</v>
+        <v>35.13436889648438</v>
       </c>
     </row>
     <row r="386">
@@ -41764,7 +41764,7 @@
         </is>
       </c>
       <c r="B386" s="2" t="n">
-        <v>36.14971160888672</v>
+        <v>36.14970779418945</v>
       </c>
     </row>
     <row r="387">
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="B387" s="2" t="n">
-        <v>36.03079605102539</v>
+        <v>36.03079223632812</v>
       </c>
     </row>
     <row r="388">
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="B389" s="2" t="n">
-        <v>35.75638198852539</v>
+        <v>35.75637817382812</v>
       </c>
     </row>
     <row r="390">
@@ -41804,7 +41804,7 @@
         </is>
       </c>
       <c r="B390" s="2" t="n">
-        <v>35.71064758300781</v>
+        <v>35.71064376831055</v>
       </c>
     </row>
     <row r="391">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="B391" s="2" t="n">
-        <v>35.50026321411133</v>
+        <v>35.5002555847168</v>
       </c>
     </row>
     <row r="392">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="B394" s="2" t="n">
-        <v>35.58257675170898</v>
+        <v>35.58258438110352</v>
       </c>
     </row>
     <row r="395">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="B395" s="2" t="n">
-        <v>35.83703994750977</v>
+        <v>35.8370361328125</v>
       </c>
     </row>
     <row r="396">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="B397" s="2" t="n">
-        <v>35.02910614013672</v>
+        <v>35.02909851074219</v>
       </c>
     </row>
     <row r="398">
@@ -41894,7 +41894,7 @@
         </is>
       </c>
       <c r="B399" s="2" t="n">
-        <v>35.15911102294922</v>
+        <v>35.15911483764648</v>
       </c>
     </row>
     <row r="400">
@@ -41904,7 +41904,7 @@
         </is>
       </c>
       <c r="B400" s="2" t="n">
-        <v>35.14982604980469</v>
+        <v>35.14982223510742</v>
       </c>
     </row>
     <row r="401">
@@ -41924,7 +41924,7 @@
         </is>
       </c>
       <c r="B402" s="2" t="n">
-        <v>35.14982604980469</v>
+        <v>35.14982223510742</v>
       </c>
     </row>
     <row r="403">
@@ -41934,7 +41934,7 @@
         </is>
       </c>
       <c r="B403" s="2" t="n">
-        <v>35.1033935546875</v>
+        <v>35.10339736938477</v>
       </c>
     </row>
     <row r="404">
@@ -41954,7 +41954,7 @@
         </is>
       </c>
       <c r="B405" s="2" t="n">
-        <v>35.1033935546875</v>
+        <v>35.10339736938477</v>
       </c>
     </row>
     <row r="406">
@@ -41974,7 +41974,7 @@
         </is>
       </c>
       <c r="B407" s="2" t="n">
-        <v>35.19625854492188</v>
+        <v>35.19626235961914</v>
       </c>
     </row>
     <row r="408">
@@ -41994,7 +41994,7 @@
         </is>
       </c>
       <c r="B409" s="2" t="n">
-        <v>36.5613899230957</v>
+        <v>36.56139755249023</v>
       </c>
     </row>
     <row r="410">
@@ -42004,7 +42004,7 @@
         </is>
       </c>
       <c r="B410" s="2" t="n">
-        <v>36.449951171875</v>
+        <v>36.44994735717773</v>
       </c>
     </row>
     <row r="411">
@@ -42014,7 +42014,7 @@
         </is>
       </c>
       <c r="B411" s="2" t="n">
-        <v>37.21145629882812</v>
+        <v>37.21145248413086</v>
       </c>
     </row>
     <row r="412">
@@ -42044,7 +42044,7 @@
         </is>
       </c>
       <c r="B414" s="2" t="n">
-        <v>37.917236328125</v>
+        <v>37.91724014282227</v>
       </c>
     </row>
     <row r="415">
@@ -42074,7 +42074,7 @@
         </is>
       </c>
       <c r="B417" s="2" t="n">
-        <v>38.14011764526367</v>
+        <v>38.14011383056641</v>
       </c>
     </row>
     <row r="418">
@@ -42094,7 +42094,7 @@
         </is>
       </c>
       <c r="B419" s="2" t="n">
-        <v>38.16797637939453</v>
+        <v>38.16797256469727</v>
       </c>
     </row>
     <row r="420">
@@ -42104,7 +42104,7 @@
         </is>
       </c>
       <c r="B420" s="2" t="n">
-        <v>38.75302886962891</v>
+        <v>38.75303268432617</v>
       </c>
     </row>
     <row r="421">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="B421" s="2" t="n">
-        <v>39.03163146972656</v>
+        <v>39.0316276550293</v>
       </c>
     </row>
     <row r="422">
@@ -42124,7 +42124,7 @@
         </is>
       </c>
       <c r="B422" s="2" t="n">
-        <v>39.05949020385742</v>
+        <v>39.05949401855469</v>
       </c>
     </row>
     <row r="423">
@@ -42144,7 +42144,7 @@
         </is>
       </c>
       <c r="B424" s="2" t="n">
-        <v>39.46810150146484</v>
+        <v>39.46809768676758</v>
       </c>
     </row>
     <row r="425">
@@ -42164,7 +42164,7 @@
         </is>
       </c>
       <c r="B426" s="2" t="n">
-        <v>38.49300765991211</v>
+        <v>38.49300384521484</v>
       </c>
     </row>
     <row r="427">
@@ -42174,7 +42174,7 @@
         </is>
       </c>
       <c r="B427" s="2" t="n">
-        <v>38.409423828125</v>
+        <v>38.40942764282227</v>
       </c>
     </row>
     <row r="428">
@@ -42184,7 +42184,7 @@
         </is>
       </c>
       <c r="B428" s="2" t="n">
-        <v>38.8830451965332</v>
+        <v>38.88304138183594</v>
       </c>
     </row>
     <row r="429">
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="B432" s="2" t="n">
-        <v>37.55505752563477</v>
+        <v>37.5550537109375</v>
       </c>
     </row>
     <row r="433">
@@ -42234,7 +42234,7 @@
         </is>
       </c>
       <c r="B433" s="2" t="n">
-        <v>37.50862503051758</v>
+        <v>37.50862884521484</v>
       </c>
     </row>
     <row r="434">
@@ -42244,7 +42244,7 @@
         </is>
       </c>
       <c r="B434" s="2" t="n">
-        <v>37.68507385253906</v>
+        <v>37.6850700378418</v>
       </c>
     </row>
     <row r="435">
@@ -42254,7 +42254,7 @@
         </is>
       </c>
       <c r="B435" s="2" t="n">
-        <v>37.3228874206543</v>
+        <v>37.32289123535156</v>
       </c>
     </row>
     <row r="436">
@@ -42284,7 +42284,7 @@
         </is>
       </c>
       <c r="B438" s="2" t="n">
-        <v>37.24859619140625</v>
+        <v>37.24860000610352</v>
       </c>
     </row>
     <row r="439">
@@ -42304,7 +42304,7 @@
         </is>
       </c>
       <c r="B440" s="2" t="n">
-        <v>36.84927368164062</v>
+        <v>36.84927749633789</v>
       </c>
     </row>
     <row r="441">
@@ -42324,7 +42324,7 @@
         </is>
       </c>
       <c r="B442" s="2" t="n">
-        <v>36.20850372314453</v>
+        <v>36.20849990844727</v>
       </c>
     </row>
     <row r="443">
@@ -42354,7 +42354,7 @@
         </is>
       </c>
       <c r="B445" s="2" t="n">
-        <v>35.75345230102539</v>
+        <v>35.75345993041992</v>
       </c>
     </row>
     <row r="446">
@@ -42364,7 +42364,7 @@
         </is>
       </c>
       <c r="B446" s="2" t="n">
-        <v>35.50271987915039</v>
+        <v>35.50271606445312</v>
       </c>
     </row>
     <row r="447">
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="B447" s="2" t="n">
-        <v>36.26422500610352</v>
+        <v>36.26421737670898</v>
       </c>
     </row>
     <row r="448">
@@ -42404,7 +42404,7 @@
         </is>
       </c>
       <c r="B450" s="2" t="n">
-        <v>36.58924865722656</v>
+        <v>36.58925628662109</v>
       </c>
     </row>
     <row r="451">
@@ -42414,7 +42414,7 @@
         </is>
       </c>
       <c r="B451" s="2" t="n">
-        <v>35.97633361816406</v>
+        <v>35.97633743286133</v>
       </c>
     </row>
     <row r="452">
@@ -42424,7 +42424,7 @@
         </is>
       </c>
       <c r="B452" s="2" t="n">
-        <v>36.12491607666016</v>
+        <v>36.12492370605469</v>
       </c>
     </row>
     <row r="453">
@@ -42454,7 +42454,7 @@
         </is>
       </c>
       <c r="B455" s="2" t="n">
-        <v>35.19625854492188</v>
+        <v>35.19626235961914</v>
       </c>
     </row>
     <row r="456">
@@ -42464,7 +42464,7 @@
         </is>
       </c>
       <c r="B456" s="2" t="n">
-        <v>35.21482849121094</v>
+        <v>35.2148323059082</v>
       </c>
     </row>
     <row r="457">
@@ -42474,7 +42474,7 @@
         </is>
       </c>
       <c r="B457" s="2" t="n">
-        <v>34.61120223999023</v>
+        <v>34.61119842529297</v>
       </c>
     </row>
     <row r="458">
@@ -42504,7 +42504,7 @@
         </is>
       </c>
       <c r="B460" s="2" t="n">
-        <v>35.05696487426758</v>
+        <v>35.05696105957031</v>
       </c>
     </row>
     <row r="461">
@@ -42514,7 +42514,7 @@
         </is>
       </c>
       <c r="B461" s="2" t="n">
-        <v>35.37270355224609</v>
+        <v>35.37270736694336</v>
       </c>
     </row>
     <row r="462">
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="B462" s="2" t="n">
-        <v>35.51200485229492</v>
+        <v>35.51200866699219</v>
       </c>
     </row>
     <row r="463">
@@ -42544,7 +42544,7 @@
         </is>
       </c>
       <c r="B464" s="2" t="n">
-        <v>35.91132736206055</v>
+        <v>35.91132354736328</v>
       </c>
     </row>
     <row r="465">
@@ -42574,7 +42574,7 @@
         </is>
       </c>
       <c r="B467" s="2" t="n">
-        <v>36.3292236328125</v>
+        <v>36.32922744750977</v>
       </c>
     </row>
     <row r="468">
@@ -42594,7 +42594,7 @@
         </is>
       </c>
       <c r="B469" s="2" t="n">
-        <v>36.64496994018555</v>
+        <v>36.64496612548828</v>
       </c>
     </row>
     <row r="470">
@@ -42624,7 +42624,7 @@
         </is>
       </c>
       <c r="B472" s="2" t="n">
-        <v>36.43137741088867</v>
+        <v>36.43138122558594</v>
       </c>
     </row>
     <row r="473">
@@ -42654,7 +42654,7 @@
         </is>
       </c>
       <c r="B475" s="2" t="n">
-        <v>36.83998870849609</v>
+        <v>36.83998489379883</v>
       </c>
     </row>
     <row r="476">
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="B477" s="2" t="n">
-        <v>37.08143997192383</v>
+        <v>37.08144378662109</v>
       </c>
     </row>
     <row r="478">
@@ -42684,7 +42684,7 @@
         </is>
       </c>
       <c r="B478" s="2" t="n">
-        <v>36.88642120361328</v>
+        <v>36.88642501831055</v>
       </c>
     </row>
     <row r="479">
@@ -42704,7 +42704,7 @@
         </is>
       </c>
       <c r="B480" s="2" t="n">
-        <v>36.99786376953125</v>
+        <v>36.99785995483398</v>
       </c>
     </row>
     <row r="481">
@@ -42764,7 +42764,7 @@
         </is>
       </c>
       <c r="B486" s="2" t="n">
-        <v>35.66987228393555</v>
+        <v>35.66987609863281</v>
       </c>
     </row>
     <row r="487">
@@ -42784,7 +42784,7 @@
         </is>
       </c>
       <c r="B488" s="2" t="n">
-        <v>36.33851623535156</v>
+        <v>36.3385124206543</v>
       </c>
     </row>
     <row r="489">
@@ -42804,7 +42804,7 @@
         </is>
       </c>
       <c r="B490" s="2" t="n">
-        <v>35.86489486694336</v>
+        <v>35.86489105224609</v>
       </c>
     </row>
     <row r="491">
@@ -42814,7 +42814,7 @@
         </is>
       </c>
       <c r="B491" s="2" t="n">
-        <v>35.80918121337891</v>
+        <v>35.80917358398438</v>
       </c>
     </row>
     <row r="492">
@@ -42844,7 +42844,7 @@
         </is>
       </c>
       <c r="B494" s="2" t="n">
-        <v>36.59853744506836</v>
+        <v>36.59854125976562</v>
       </c>
     </row>
     <row r="495">
@@ -42864,7 +42864,7 @@
         </is>
       </c>
       <c r="B496" s="2" t="n">
-        <v>36.35708999633789</v>
+        <v>36.35708618164062</v>
       </c>
     </row>
     <row r="497">
@@ -42884,7 +42884,7 @@
         </is>
       </c>
       <c r="B498" s="2" t="n">
-        <v>35.79989624023438</v>
+        <v>35.79988479614258</v>
       </c>
     </row>
     <row r="499">
@@ -42904,7 +42904,7 @@
         </is>
       </c>
       <c r="B500" s="2" t="n">
-        <v>36.19921493530273</v>
+        <v>36.19921112060547</v>
       </c>
     </row>
     <row r="501">
@@ -42914,7 +42914,7 @@
         </is>
       </c>
       <c r="B501" s="2" t="n">
-        <v>36.36637115478516</v>
+        <v>36.36637496948242</v>
       </c>
     </row>
     <row r="502">
@@ -42924,7 +42924,7 @@
         </is>
       </c>
       <c r="B502" s="2" t="n">
-        <v>36.17135238647461</v>
+        <v>36.17135620117188</v>
       </c>
     </row>
     <row r="503">
@@ -42934,7 +42934,7 @@
         </is>
       </c>
       <c r="B503" s="2" t="n">
-        <v>36.19921493530273</v>
+        <v>36.19921112060547</v>
       </c>
     </row>
     <row r="504">
@@ -42944,7 +42944,7 @@
         </is>
       </c>
       <c r="B504" s="2" t="n">
-        <v>36.49638366699219</v>
+        <v>36.49638748168945</v>
       </c>
     </row>
     <row r="505">
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="B506" s="2" t="n">
-        <v>35.66058731079102</v>
+        <v>35.66059112548828</v>
       </c>
     </row>
     <row r="507">
@@ -42994,7 +42994,7 @@
         </is>
       </c>
       <c r="B509" s="2" t="n">
-        <v>35.79989624023438</v>
+        <v>35.79988479614258</v>
       </c>
     </row>
     <row r="510">
@@ -43054,7 +43054,7 @@
         </is>
       </c>
       <c r="B515" s="2" t="n">
-        <v>36.87590026855469</v>
+        <v>36.87590408325195</v>
       </c>
     </row>
     <row r="516">
@@ -43084,7 +43084,7 @@
         </is>
       </c>
       <c r="B518" s="2" t="n">
-        <v>37.38130569458008</v>
+        <v>37.38130187988281</v>
       </c>
     </row>
     <row r="519">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="B519" s="2" t="n">
-        <v>37.75568008422852</v>
+        <v>37.75568389892578</v>
       </c>
     </row>
     <row r="520">
@@ -43114,7 +43114,7 @@
         </is>
       </c>
       <c r="B521" s="2" t="n">
-        <v>38.39212036132812</v>
+        <v>38.39211654663086</v>
       </c>
     </row>
     <row r="522">
@@ -43124,7 +43124,7 @@
         </is>
       </c>
       <c r="B522" s="2" t="n">
-        <v>38.26108169555664</v>
+        <v>38.26108932495117</v>
       </c>
     </row>
     <row r="523">
@@ -43134,7 +43134,7 @@
         </is>
       </c>
       <c r="B523" s="2" t="n">
-        <v>37.5123405456543</v>
+        <v>37.51233673095703</v>
       </c>
     </row>
     <row r="524">
@@ -43154,7 +43154,7 @@
         </is>
       </c>
       <c r="B525" s="2" t="n">
-        <v>37.20347595214844</v>
+        <v>37.2034797668457</v>
       </c>
     </row>
     <row r="526">
@@ -43174,7 +43174,7 @@
         </is>
       </c>
       <c r="B527" s="2" t="n">
-        <v>36.78230285644531</v>
+        <v>36.78230667114258</v>
       </c>
     </row>
     <row r="528">
@@ -43204,7 +43204,7 @@
         </is>
       </c>
       <c r="B530" s="2" t="n">
-        <v>36.73550796508789</v>
+        <v>36.73550415039062</v>
       </c>
     </row>
     <row r="531">
@@ -43214,7 +43214,7 @@
         </is>
       </c>
       <c r="B531" s="2" t="n">
-        <v>37.02565002441406</v>
+        <v>37.0256462097168</v>
       </c>
     </row>
     <row r="532">
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="B533" s="2" t="n">
-        <v>37.21283721923828</v>
+        <v>37.21283340454102</v>
       </c>
     </row>
     <row r="534">
@@ -43254,7 +43254,7 @@
         </is>
       </c>
       <c r="B535" s="2" t="n">
-        <v>36.86653900146484</v>
+        <v>36.86653518676758</v>
       </c>
     </row>
     <row r="536">
@@ -43264,7 +43264,7 @@
         </is>
       </c>
       <c r="B536" s="2" t="n">
-        <v>36.89461898803711</v>
+        <v>36.89461135864258</v>
       </c>
     </row>
     <row r="537">
@@ -43294,7 +43294,7 @@
         </is>
       </c>
       <c r="B539" s="2" t="n">
-        <v>38.59802627563477</v>
+        <v>38.5980224609375</v>
       </c>
     </row>
     <row r="540">
@@ -43304,7 +43304,7 @@
         </is>
       </c>
       <c r="B540" s="2" t="n">
-        <v>38.38275527954102</v>
+        <v>38.38275909423828</v>
       </c>
     </row>
     <row r="541">
@@ -43314,7 +43314,7 @@
         </is>
       </c>
       <c r="B541" s="2" t="n">
-        <v>38.42955780029297</v>
+        <v>38.4295539855957</v>
       </c>
     </row>
     <row r="542">
@@ -43344,7 +43344,7 @@
         </is>
       </c>
       <c r="B544" s="2" t="n">
-        <v>37.79311370849609</v>
+        <v>37.79311752319336</v>
       </c>
     </row>
     <row r="545">
@@ -43354,7 +43354,7 @@
         </is>
       </c>
       <c r="B545" s="2" t="n">
-        <v>37.73695755004883</v>
+        <v>37.73696136474609</v>
       </c>
     </row>
     <row r="546">
@@ -43374,7 +43374,7 @@
         </is>
       </c>
       <c r="B547" s="2" t="n">
-        <v>38.5699462890625</v>
+        <v>38.56994247436523</v>
       </c>
     </row>
     <row r="548">
@@ -43384,7 +43384,7 @@
         </is>
       </c>
       <c r="B548" s="2" t="n">
-        <v>38.79457092285156</v>
+        <v>38.79456329345703</v>
       </c>
     </row>
     <row r="549">
@@ -43404,7 +43404,7 @@
         </is>
       </c>
       <c r="B550" s="2" t="n">
-        <v>39.24382019042969</v>
+        <v>39.24381637573242</v>
       </c>
     </row>
     <row r="551">
@@ -43424,7 +43424,7 @@
         </is>
       </c>
       <c r="B552" s="2" t="n">
-        <v>38.7664909362793</v>
+        <v>38.76648712158203</v>
       </c>
     </row>
     <row r="553">
@@ -43434,7 +43434,7 @@
         </is>
       </c>
       <c r="B553" s="2" t="n">
-        <v>37.83991241455078</v>
+        <v>37.83991622924805</v>
       </c>
     </row>
     <row r="554">
@@ -43444,7 +43444,7 @@
         </is>
       </c>
       <c r="B554" s="2" t="n">
-        <v>37.98966217041016</v>
+        <v>37.98966598510742</v>
       </c>
     </row>
     <row r="555">
@@ -43464,7 +43464,7 @@
         </is>
       </c>
       <c r="B556" s="2" t="n">
-        <v>37.8867073059082</v>
+        <v>37.88671493530273</v>
       </c>
     </row>
     <row r="557">
@@ -43484,7 +43484,7 @@
         </is>
       </c>
       <c r="B558" s="2" t="n">
-        <v>37.52169799804688</v>
+        <v>37.52169418334961</v>
       </c>
     </row>
     <row r="559">
@@ -43494,7 +43494,7 @@
         </is>
       </c>
       <c r="B559" s="2" t="n">
-        <v>37.57785415649414</v>
+        <v>37.57785034179688</v>
       </c>
     </row>
     <row r="560">
@@ -43504,7 +43504,7 @@
         </is>
       </c>
       <c r="B560" s="2" t="n">
-        <v>37.02565002441406</v>
+        <v>37.0256462097168</v>
       </c>
     </row>
     <row r="561">
@@ -43514,7 +43514,7 @@
         </is>
       </c>
       <c r="B561" s="2" t="n">
-        <v>36.84782028198242</v>
+        <v>36.84782409667969</v>
       </c>
     </row>
     <row r="562">
@@ -43534,7 +43534,7 @@
         </is>
       </c>
       <c r="B563" s="2" t="n">
-        <v>36.09907531738281</v>
+        <v>36.09907150268555</v>
       </c>
     </row>
     <row r="564">
@@ -43544,7 +43544,7 @@
         </is>
       </c>
       <c r="B564" s="2" t="n">
-        <v>36.18330764770508</v>
+        <v>36.18330383300781</v>
       </c>
     </row>
     <row r="565">
@@ -43554,7 +43554,7 @@
         </is>
       </c>
       <c r="B565" s="2" t="n">
-        <v>35.93996429443359</v>
+        <v>35.93996047973633</v>
       </c>
     </row>
     <row r="566">
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="B567" s="2" t="n">
-        <v>35.94931793212891</v>
+        <v>35.94932174682617</v>
       </c>
     </row>
     <row r="568">
@@ -43584,7 +43584,7 @@
         </is>
       </c>
       <c r="B568" s="2" t="n">
-        <v>36.52024841308594</v>
+        <v>36.52024459838867</v>
       </c>
     </row>
     <row r="569">
@@ -43604,7 +43604,7 @@
         </is>
       </c>
       <c r="B570" s="2" t="n">
-        <v>36.41728591918945</v>
+        <v>36.41728973388672</v>
       </c>
     </row>
     <row r="571">
@@ -43614,7 +43614,7 @@
         </is>
       </c>
       <c r="B571" s="2" t="n">
-        <v>36.77294158935547</v>
+        <v>36.77294921875</v>
       </c>
     </row>
     <row r="572">
@@ -43624,7 +43624,7 @@
         </is>
       </c>
       <c r="B572" s="2" t="n">
-        <v>37.24091339111328</v>
+        <v>37.24091720581055</v>
       </c>
     </row>
     <row r="573">
@@ -43634,7 +43634,7 @@
         </is>
       </c>
       <c r="B573" s="2" t="n">
-        <v>37.11924362182617</v>
+        <v>37.11924743652344</v>
       </c>
     </row>
     <row r="574">
@@ -43654,7 +43654,7 @@
         </is>
       </c>
       <c r="B575" s="2" t="n">
-        <v>37.09116744995117</v>
+        <v>37.09117126464844</v>
       </c>
     </row>
     <row r="576">
@@ -43664,7 +43664,7 @@
         </is>
       </c>
       <c r="B576" s="2" t="n">
-        <v>36.79166412353516</v>
+        <v>36.79166793823242</v>
       </c>
     </row>
     <row r="577">
@@ -43674,7 +43674,7 @@
         </is>
       </c>
       <c r="B577" s="2" t="n">
-        <v>36.58576202392578</v>
+        <v>36.58575820922852</v>
       </c>
     </row>
     <row r="578">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="B580" s="2" t="n">
-        <v>36.67934799194336</v>
+        <v>36.67935180664062</v>
       </c>
     </row>
     <row r="581">
@@ -43714,7 +43714,7 @@
         </is>
       </c>
       <c r="B581" s="2" t="n">
-        <v>36.56704330444336</v>
+        <v>36.56703948974609</v>
       </c>
     </row>
     <row r="582">
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="B582" s="2" t="n">
-        <v>36.52024841308594</v>
+        <v>36.52024459838867</v>
       </c>
     </row>
     <row r="583">
@@ -43734,7 +43734,7 @@
         </is>
       </c>
       <c r="B583" s="2" t="n">
-        <v>36.76358795166016</v>
+        <v>36.76358413696289</v>
       </c>
     </row>
     <row r="584">
@@ -43764,7 +43764,7 @@
         </is>
       </c>
       <c r="B586" s="2" t="n">
-        <v>36.36112976074219</v>
+        <v>36.36113357543945</v>
       </c>
     </row>
     <row r="587">
@@ -43774,7 +43774,7 @@
         </is>
       </c>
       <c r="B587" s="2" t="n">
-        <v>36.21138381958008</v>
+        <v>36.21138000488281</v>
       </c>
     </row>
     <row r="588">
@@ -43784,7 +43784,7 @@
         </is>
       </c>
       <c r="B588" s="2" t="n">
-        <v>35.58431243896484</v>
+        <v>35.58430862426758</v>
       </c>
     </row>
     <row r="589">
@@ -43794,7 +43794,7 @@
         </is>
       </c>
       <c r="B589" s="2" t="n">
-        <v>36.00547790527344</v>
+        <v>36.0054817199707</v>
       </c>
     </row>
     <row r="590">
@@ -43804,7 +43804,7 @@
         </is>
       </c>
       <c r="B590" s="2" t="n">
-        <v>35.84636688232422</v>
+        <v>35.84637069702148</v>
       </c>
     </row>
     <row r="591">
@@ -43814,7 +43814,7 @@
         </is>
       </c>
       <c r="B591" s="2" t="n">
-        <v>35.34096145629883</v>
+        <v>35.34096527099609</v>
       </c>
     </row>
     <row r="592">
@@ -43834,7 +43834,7 @@
         </is>
       </c>
       <c r="B593" s="2" t="n">
-        <v>35.49070739746094</v>
+        <v>35.4907112121582</v>
       </c>
     </row>
     <row r="594">
@@ -43844,7 +43844,7 @@
         </is>
       </c>
       <c r="B594" s="2" t="n">
-        <v>35.51879119873047</v>
+        <v>35.51879501342773</v>
       </c>
     </row>
     <row r="595">
@@ -43854,7 +43854,7 @@
         </is>
       </c>
       <c r="B595" s="2" t="n">
-        <v>35.34096145629883</v>
+        <v>35.34096527099609</v>
       </c>
     </row>
     <row r="596">
@@ -43864,7 +43864,7 @@
         </is>
       </c>
       <c r="B596" s="2" t="n">
-        <v>34.87299346923828</v>
+        <v>34.87299728393555</v>
       </c>
     </row>
     <row r="597">
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="B597" s="2" t="n">
-        <v>34.77004623413086</v>
+        <v>34.77004241943359</v>
       </c>
     </row>
     <row r="598">
@@ -43884,7 +43884,7 @@
         </is>
       </c>
       <c r="B598" s="2" t="n">
-        <v>34.90107345581055</v>
+        <v>34.90107727050781</v>
       </c>
     </row>
     <row r="599">
@@ -43924,7 +43924,7 @@
         </is>
       </c>
       <c r="B602" s="2" t="n">
-        <v>35.96803665161133</v>
+        <v>35.96804428100586</v>
       </c>
     </row>
     <row r="603">
@@ -43934,7 +43934,7 @@
         </is>
       </c>
       <c r="B603" s="2" t="n">
-        <v>35.56558609008789</v>
+        <v>35.56558227539062</v>
       </c>
     </row>
     <row r="604">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="B604" s="2" t="n">
-        <v>35.4345588684082</v>
+        <v>35.43455505371094</v>
       </c>
     </row>
     <row r="605">
@@ -43954,7 +43954,7 @@
         </is>
       </c>
       <c r="B605" s="2" t="n">
-        <v>35.69662094116211</v>
+        <v>35.69661712646484</v>
       </c>
     </row>
     <row r="606">
@@ -43974,7 +43974,7 @@
         </is>
       </c>
       <c r="B607" s="2" t="n">
-        <v>35.0601806640625</v>
+        <v>35.06018447875977</v>
       </c>
     </row>
     <row r="608">
@@ -43984,7 +43984,7 @@
         </is>
       </c>
       <c r="B608" s="2" t="n">
-        <v>34.85427856445312</v>
+        <v>34.85427474975586</v>
       </c>
     </row>
     <row r="609">
@@ -43994,7 +43994,7 @@
         </is>
       </c>
       <c r="B609" s="2" t="n">
-        <v>34.43310165405273</v>
+        <v>34.43310928344727</v>
       </c>
     </row>
     <row r="610">
@@ -44014,7 +44014,7 @@
         </is>
       </c>
       <c r="B611" s="2" t="n">
-        <v>34.84491729736328</v>
+        <v>34.84491348266602</v>
       </c>
     </row>
     <row r="612">
@@ -44064,7 +44064,7 @@
         </is>
       </c>
       <c r="B616" s="2" t="n">
-        <v>34.34887313842773</v>
+        <v>34.34886932373047</v>
       </c>
     </row>
     <row r="617">
@@ -44074,7 +44074,7 @@
         </is>
       </c>
       <c r="B617" s="2" t="n">
-        <v>34.66709136962891</v>
+        <v>34.66708755493164</v>
       </c>
     </row>
     <row r="618">
@@ -44084,7 +44084,7 @@
         </is>
       </c>
       <c r="B618" s="2" t="n">
-        <v>35.27545166015625</v>
+        <v>35.27544784545898</v>
       </c>
     </row>
     <row r="619">
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="B619" s="2" t="n">
-        <v>35.99611663818359</v>
+        <v>35.99612045288086</v>
       </c>
     </row>
     <row r="620">
@@ -44124,7 +44124,7 @@
         </is>
       </c>
       <c r="B622" s="2" t="n">
-        <v>35.97739791870117</v>
+        <v>35.97740173339844</v>
       </c>
     </row>
     <row r="623">
@@ -44144,7 +44144,7 @@
         </is>
       </c>
       <c r="B624" s="2" t="n">
-        <v>35.89316558837891</v>
+        <v>35.89316177368164</v>
       </c>
     </row>
     <row r="625">
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="B627" s="2" t="n">
-        <v>37.14731597900391</v>
+        <v>37.14732360839844</v>
       </c>
     </row>
     <row r="628">
@@ -44184,7 +44184,7 @@
         </is>
       </c>
       <c r="B628" s="2" t="n">
-        <v>36.79166412353516</v>
+        <v>36.79166793823242</v>
       </c>
     </row>
     <row r="629">
@@ -44204,7 +44204,7 @@
         </is>
       </c>
       <c r="B630" s="2" t="n">
-        <v>37.29706954956055</v>
+        <v>37.29706573486328</v>
       </c>
     </row>
     <row r="631">
@@ -44214,7 +44214,7 @@
         </is>
       </c>
       <c r="B631" s="2" t="n">
-        <v>37.06308746337891</v>
+        <v>37.06307983398438</v>
       </c>
     </row>
     <row r="632">
@@ -44234,7 +44234,7 @@
         </is>
       </c>
       <c r="B633" s="2" t="n">
-        <v>37.00693511962891</v>
+        <v>37.00693130493164</v>
       </c>
     </row>
     <row r="634">
@@ -44254,7 +44254,7 @@
         </is>
       </c>
       <c r="B635" s="2" t="n">
-        <v>37.16604232788086</v>
+        <v>37.16603469848633</v>
       </c>
     </row>
     <row r="636">
@@ -44274,7 +44274,7 @@
         </is>
       </c>
       <c r="B637" s="2" t="n">
-        <v>37.02565002441406</v>
+        <v>37.0256462097168</v>
       </c>
     </row>
     <row r="638">
@@ -44294,7 +44294,7 @@
         </is>
       </c>
       <c r="B639" s="2" t="n">
-        <v>36.76358795166016</v>
+        <v>36.76358413696289</v>
       </c>
     </row>
     <row r="640">
@@ -44304,7 +44304,7 @@
         </is>
       </c>
       <c r="B640" s="2" t="n">
-        <v>36.53896713256836</v>
+        <v>36.53896331787109</v>
       </c>
     </row>
     <row r="641">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="B641" s="2" t="n">
-        <v>36.49217224121094</v>
+        <v>36.49216461181641</v>
       </c>
     </row>
     <row r="642">
@@ -44344,7 +44344,7 @@
         </is>
       </c>
       <c r="B644" s="2" t="n">
-        <v>36.72614669799805</v>
+        <v>36.72615051269531</v>
       </c>
     </row>
     <row r="645">
@@ -44354,7 +44354,7 @@
         </is>
       </c>
       <c r="B645" s="2" t="n">
-        <v>36.73550796508789</v>
+        <v>36.73550415039062</v>
       </c>
     </row>
     <row r="646">
@@ -44364,7 +44364,7 @@
         </is>
       </c>
       <c r="B646" s="2" t="n">
-        <v>37.10052490234375</v>
+        <v>37.10052108764648</v>
       </c>
     </row>
     <row r="647">
@@ -44444,7 +44444,7 @@
         </is>
       </c>
       <c r="B654" s="2" t="n">
-        <v>37.84983825683594</v>
+        <v>37.8498420715332</v>
       </c>
     </row>
     <row r="655">
@@ -44484,7 +44484,7 @@
         </is>
       </c>
       <c r="B658" s="2" t="n">
-        <v>37.89752197265625</v>
+        <v>37.89752578735352</v>
       </c>
     </row>
     <row r="659">
@@ -44494,7 +44494,7 @@
         </is>
       </c>
       <c r="B659" s="2" t="n">
-        <v>37.68772888183594</v>
+        <v>37.68772506713867</v>
       </c>
     </row>
     <row r="660">
@@ -44514,7 +44514,7 @@
         </is>
       </c>
       <c r="B661" s="2" t="n">
-        <v>37.61143112182617</v>
+        <v>37.61143493652344</v>
       </c>
     </row>
     <row r="662">
@@ -44524,7 +44524,7 @@
         </is>
       </c>
       <c r="B662" s="2" t="n">
-        <v>37.71633529663086</v>
+        <v>37.71633148193359</v>
       </c>
     </row>
     <row r="663">
@@ -44534,7 +44534,7 @@
         </is>
       </c>
       <c r="B663" s="2" t="n">
-        <v>37.18230438232422</v>
+        <v>37.18230056762695</v>
       </c>
     </row>
     <row r="664">
@@ -44544,7 +44544,7 @@
         </is>
       </c>
       <c r="B664" s="2" t="n">
-        <v>37.09646987915039</v>
+        <v>37.09647369384766</v>
       </c>
     </row>
     <row r="665">
@@ -44574,7 +44574,7 @@
         </is>
       </c>
       <c r="B667" s="2" t="n">
-        <v>36.47660827636719</v>
+        <v>36.47660446166992</v>
       </c>
     </row>
     <row r="668">
@@ -44594,7 +44594,7 @@
         </is>
       </c>
       <c r="B669" s="2" t="n">
-        <v>36.22866058349609</v>
+        <v>36.22866439819336</v>
       </c>
     </row>
     <row r="670">
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="B672" s="2" t="n">
-        <v>36.60057830810547</v>
+        <v>36.60058212280273</v>
       </c>
     </row>
     <row r="673">
@@ -44644,7 +44644,7 @@
         </is>
       </c>
       <c r="B674" s="2" t="n">
-        <v>37.05832290649414</v>
+        <v>37.05832672119141</v>
       </c>
     </row>
     <row r="675">
@@ -44654,7 +44654,7 @@
         </is>
       </c>
       <c r="B675" s="2" t="n">
-        <v>37.08693313598633</v>
+        <v>37.08692932128906</v>
       </c>
     </row>
     <row r="676">
@@ -44664,7 +44664,7 @@
         </is>
       </c>
       <c r="B676" s="2" t="n">
-        <v>37.10600280761719</v>
+        <v>37.10600662231445</v>
       </c>
     </row>
     <row r="677">
@@ -44674,7 +44674,7 @@
         </is>
       </c>
       <c r="B677" s="2" t="n">
-        <v>36.81038284301758</v>
+        <v>36.81037902832031</v>
       </c>
     </row>
     <row r="678">
@@ -44704,7 +44704,7 @@
         </is>
       </c>
       <c r="B680" s="2" t="n">
-        <v>36.85806655883789</v>
+        <v>36.85806274414062</v>
       </c>
     </row>
     <row r="681">
@@ -44714,7 +44714,7 @@
         </is>
       </c>
       <c r="B681" s="2" t="n">
-        <v>36.90574645996094</v>
+        <v>36.90573883056641</v>
       </c>
     </row>
     <row r="682">
@@ -44734,7 +44734,7 @@
         </is>
       </c>
       <c r="B683" s="2" t="n">
-        <v>37.79262924194336</v>
+        <v>37.79262542724609</v>
       </c>
     </row>
     <row r="684">
@@ -44774,7 +44774,7 @@
         </is>
       </c>
       <c r="B687" s="2" t="n">
-        <v>37.32534408569336</v>
+        <v>37.32534027099609</v>
       </c>
     </row>
     <row r="688">
@@ -44804,7 +44804,7 @@
         </is>
       </c>
       <c r="B690" s="2" t="n">
-        <v>38.22176361083984</v>
+        <v>38.22175979614258</v>
       </c>
     </row>
     <row r="691">
@@ -44814,7 +44814,7 @@
         </is>
       </c>
       <c r="B691" s="2" t="n">
-        <v>38.27897644042969</v>
+        <v>38.27898025512695</v>
       </c>
     </row>
     <row r="692">
@@ -44834,7 +44834,7 @@
         </is>
       </c>
       <c r="B693" s="2" t="n">
-        <v>38.73672103881836</v>
+        <v>38.73672485351562</v>
       </c>
     </row>
     <row r="694">
@@ -44854,7 +44854,7 @@
         </is>
       </c>
       <c r="B695" s="2" t="n">
-        <v>38.54599761962891</v>
+        <v>38.54599380493164</v>
       </c>
     </row>
     <row r="696">
@@ -44864,7 +44864,7 @@
         </is>
       </c>
       <c r="B696" s="2" t="n">
-        <v>38.62229156494141</v>
+        <v>38.62228775024414</v>
       </c>
     </row>
     <row r="697">
@@ -44874,7 +44874,7 @@
         </is>
       </c>
       <c r="B697" s="2" t="n">
-        <v>38.11686706542969</v>
+        <v>38.11685943603516</v>
       </c>
     </row>
     <row r="698">
@@ -44894,7 +44894,7 @@
         </is>
       </c>
       <c r="B699" s="2" t="n">
-        <v>38.60321426391602</v>
+        <v>38.60321807861328</v>
       </c>
     </row>
     <row r="700">
@@ -44904,7 +44904,7 @@
         </is>
       </c>
       <c r="B700" s="2" t="n">
-        <v>38.51738739013672</v>
+        <v>38.51738357543945</v>
       </c>
     </row>
     <row r="701">
@@ -44914,7 +44914,7 @@
         </is>
       </c>
       <c r="B701" s="2" t="n">
-        <v>38.17407608032227</v>
+        <v>38.17407989501953</v>
       </c>
     </row>
     <row r="702">
@@ -44944,7 +44944,7 @@
         </is>
       </c>
       <c r="B704" s="2" t="n">
-        <v>38.92744827270508</v>
+        <v>38.92745590209961</v>
       </c>
     </row>
     <row r="705">
@@ -44964,7 +44964,7 @@
         </is>
       </c>
       <c r="B706" s="2" t="n">
-        <v>39.44241333007812</v>
+        <v>39.44241714477539</v>
       </c>
     </row>
     <row r="707">
@@ -44974,7 +44974,7 @@
         </is>
       </c>
       <c r="B707" s="2" t="n">
-        <v>39.31844329833984</v>
+        <v>39.31844711303711</v>
       </c>
     </row>
     <row r="708">
@@ -45004,7 +45004,7 @@
         </is>
       </c>
       <c r="B710" s="2" t="n">
-        <v>38.94652557373047</v>
+        <v>38.9465217590332</v>
       </c>
     </row>
     <row r="711">
@@ -45024,7 +45024,7 @@
         </is>
       </c>
       <c r="B712" s="2" t="n">
-        <v>39.19447326660156</v>
+        <v>39.1944694519043</v>
       </c>
     </row>
     <row r="713">
@@ -45054,7 +45054,7 @@
         </is>
       </c>
       <c r="B715" s="2" t="n">
-        <v>38.99420928955078</v>
+        <v>38.99420547485352</v>
       </c>
     </row>
     <row r="716">
@@ -45084,7 +45084,7 @@
         </is>
       </c>
       <c r="B718" s="2" t="n">
-        <v>39.1754035949707</v>
+        <v>39.17539978027344</v>
       </c>
     </row>
     <row r="719">
@@ -45104,7 +45104,7 @@
         </is>
       </c>
       <c r="B720" s="2" t="n">
-        <v>39.36612319946289</v>
+        <v>39.36612701416016</v>
       </c>
     </row>
     <row r="721">
@@ -45144,7 +45144,7 @@
         </is>
       </c>
       <c r="B724" s="2" t="n">
-        <v>39.59500122070312</v>
+        <v>39.59499740600586</v>
       </c>
     </row>
     <row r="725">
@@ -45154,7 +45154,7 @@
         </is>
       </c>
       <c r="B725" s="2" t="n">
-        <v>39.86201095581055</v>
+        <v>39.86201477050781</v>
       </c>
     </row>
     <row r="726">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="B726" s="2" t="n">
-        <v>39.31844329833984</v>
+        <v>39.31844711303711</v>
       </c>
     </row>
     <row r="727">
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="B730" s="2" t="n">
-        <v>37.89752197265625</v>
+        <v>37.89752578735352</v>
       </c>
     </row>
     <row r="731">
@@ -45224,7 +45224,7 @@
         </is>
       </c>
       <c r="B732" s="2" t="n">
-        <v>38.0214958190918</v>
+        <v>38.02149963378906</v>
       </c>
     </row>
     <row r="733">
@@ -45244,7 +45244,7 @@
         </is>
       </c>
       <c r="B734" s="2" t="n">
-        <v>38.27897644042969</v>
+        <v>38.27898025512695</v>
       </c>
     </row>
     <row r="735">
@@ -45284,7 +45284,7 @@
         </is>
       </c>
       <c r="B738" s="2" t="n">
-        <v>39.26122283935547</v>
+        <v>39.26122665405273</v>
       </c>
     </row>
     <row r="739">
@@ -45304,7 +45304,7 @@
         </is>
       </c>
       <c r="B740" s="2" t="n">
-        <v>39.08957290649414</v>
+        <v>39.08956909179688</v>
       </c>
     </row>
     <row r="741">
@@ -45314,7 +45314,7 @@
         </is>
       </c>
       <c r="B741" s="2" t="n">
-        <v>39.12771606445312</v>
+        <v>39.12771224975586</v>
       </c>
     </row>
     <row r="742">
@@ -45324,7 +45324,7 @@
         </is>
       </c>
       <c r="B742" s="2" t="n">
-        <v>40.13856887817383</v>
+        <v>40.13857650756836</v>
       </c>
     </row>
     <row r="743">
@@ -45344,7 +45344,7 @@
         </is>
       </c>
       <c r="B744" s="2" t="n">
-        <v>40.53909683227539</v>
+        <v>40.53910064697266</v>
       </c>
     </row>
     <row r="745">
@@ -45354,7 +45354,7 @@
         </is>
       </c>
       <c r="B745" s="2" t="n">
-        <v>40.31022644042969</v>
+        <v>40.31022262573242</v>
       </c>
     </row>
     <row r="746">
@@ -45364,7 +45364,7 @@
         </is>
       </c>
       <c r="B746" s="2" t="n">
-        <v>40.31975936889648</v>
+        <v>40.31976318359375</v>
       </c>
     </row>
     <row r="747">
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="B747" s="2" t="n">
-        <v>40.4437370300293</v>
+        <v>40.44373321533203</v>
       </c>
     </row>
     <row r="748">
@@ -45394,7 +45394,7 @@
         </is>
       </c>
       <c r="B749" s="2" t="n">
-        <v>40.83473205566406</v>
+        <v>40.8347282409668</v>
       </c>
     </row>
     <row r="750">
@@ -45404,7 +45404,7 @@
         </is>
       </c>
       <c r="B750" s="2" t="n">
-        <v>41.05406188964844</v>
+        <v>41.0540657043457</v>
       </c>
     </row>
     <row r="751">
@@ -45414,7 +45414,7 @@
         </is>
       </c>
       <c r="B751" s="2" t="n">
-        <v>41.49272918701172</v>
+        <v>41.49273681640625</v>
       </c>
     </row>
     <row r="752">
@@ -45424,7 +45424,7 @@
         </is>
       </c>
       <c r="B752" s="2" t="n">
-        <v>41.57856369018555</v>
+        <v>41.57855987548828</v>
       </c>
     </row>
     <row r="753">
@@ -45434,7 +45434,7 @@
         </is>
       </c>
       <c r="B753" s="2" t="n">
-        <v>41.75975799560547</v>
+        <v>41.7597541809082</v>
       </c>
     </row>
     <row r="754">
@@ -45444,7 +45444,7 @@
         </is>
       </c>
       <c r="B754" s="2" t="n">
-        <v>41.60717391967773</v>
+        <v>41.60717010498047</v>
       </c>
     </row>
     <row r="755">
@@ -45464,7 +45464,7 @@
         </is>
       </c>
       <c r="B756" s="2" t="n">
-        <v>41.21617889404297</v>
+        <v>41.21618270874023</v>
       </c>
     </row>
     <row r="757">
@@ -45514,7 +45514,7 @@
         </is>
       </c>
       <c r="B761" s="2" t="n">
-        <v>40.24346923828125</v>
+        <v>40.24347305297852</v>
       </c>
     </row>
     <row r="762">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="B763" s="2" t="n">
-        <v>40.27207946777344</v>
+        <v>40.27207565307617</v>
       </c>
     </row>
     <row r="764">
@@ -45564,7 +45564,7 @@
         </is>
       </c>
       <c r="B766" s="2" t="n">
-        <v>40.54863739013672</v>
+        <v>40.54863357543945</v>
       </c>
     </row>
     <row r="767">
@@ -45594,7 +45594,7 @@
         </is>
       </c>
       <c r="B769" s="2" t="n">
-        <v>40.19486999511719</v>
+        <v>40.19486618041992</v>
       </c>
     </row>
     <row r="770">
@@ -45604,7 +45604,7 @@
         </is>
       </c>
       <c r="B770" s="2" t="n">
-        <v>40.5981559753418</v>
+        <v>40.59815979003906</v>
       </c>
     </row>
     <row r="771">
@@ -45614,7 +45614,7 @@
         </is>
       </c>
       <c r="B771" s="2" t="n">
-        <v>40.50213623046875</v>
+        <v>40.50214004516602</v>
       </c>
     </row>
     <row r="772">
@@ -45624,7 +45624,7 @@
         </is>
       </c>
       <c r="B772" s="2" t="n">
-        <v>40.55014801025391</v>
+        <v>40.55014419555664</v>
       </c>
     </row>
     <row r="773">
@@ -45714,7 +45714,7 @@
         </is>
       </c>
       <c r="B781" s="2" t="n">
-        <v>40.89582824707031</v>
+        <v>40.89583206176758</v>
       </c>
     </row>
     <row r="782">
@@ -45744,7 +45744,7 @@
         </is>
       </c>
       <c r="B784" s="2" t="n">
-        <v>41.72161865234375</v>
+        <v>41.72162246704102</v>
       </c>
     </row>
     <row r="785">
@@ -45754,7 +45754,7 @@
         </is>
       </c>
       <c r="B785" s="2" t="n">
-        <v>41.89446258544922</v>
+        <v>41.89445877075195</v>
       </c>
     </row>
     <row r="786">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="B787" s="2" t="n">
-        <v>42.07690048217773</v>
+        <v>42.076904296875</v>
       </c>
     </row>
     <row r="788">
@@ -45814,7 +45814,7 @@
         </is>
       </c>
       <c r="B791" s="2" t="n">
-        <v>42.28815078735352</v>
+        <v>42.28814697265625</v>
       </c>
     </row>
     <row r="792">
@@ -45834,7 +45834,7 @@
         </is>
       </c>
       <c r="B793" s="2" t="n">
-        <v>41.83684921264648</v>
+        <v>41.83684539794922</v>
       </c>
     </row>
     <row r="794">
@@ -45844,7 +45844,7 @@
         </is>
       </c>
       <c r="B794" s="2" t="n">
-        <v>41.44315719604492</v>
+        <v>41.44315338134766</v>
       </c>
     </row>
     <row r="795">
@@ -45864,7 +45864,7 @@
         </is>
       </c>
       <c r="B796" s="2" t="n">
-        <v>41.38554000854492</v>
+        <v>41.38553619384766</v>
       </c>
     </row>
     <row r="797">
@@ -45874,7 +45874,7 @@
         </is>
       </c>
       <c r="B797" s="2" t="n">
-        <v>41.02066040039062</v>
+        <v>41.02065658569336</v>
       </c>
     </row>
     <row r="798">
@@ -45884,7 +45884,7 @@
         </is>
       </c>
       <c r="B798" s="2" t="n">
-        <v>40.42531585693359</v>
+        <v>40.42531967163086</v>
       </c>
     </row>
     <row r="799">
@@ -45944,7 +45944,7 @@
         </is>
       </c>
       <c r="B804" s="2" t="n">
-        <v>40.52133941650391</v>
+        <v>40.52134323120117</v>
       </c>
     </row>
     <row r="805">
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="B811" s="2" t="n">
-        <v>40.52133941650391</v>
+        <v>40.52134323120117</v>
       </c>
     </row>
     <row r="812">
@@ -46034,7 +46034,7 @@
         </is>
       </c>
       <c r="B813" s="2" t="n">
-        <v>40.75179672241211</v>
+        <v>40.75179290771484</v>
       </c>
     </row>
     <row r="814">
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="B822" s="2" t="n">
-        <v>41.79843521118164</v>
+        <v>41.79843902587891</v>
       </c>
     </row>
     <row r="823">
@@ -46134,7 +46134,7 @@
         </is>
       </c>
       <c r="B823" s="2" t="n">
-        <v>41.5391731262207</v>
+        <v>41.53917694091797</v>
       </c>
     </row>
     <row r="824">
@@ -46154,7 +46154,7 @@
         </is>
       </c>
       <c r="B825" s="2" t="n">
-        <v>41.64479827880859</v>
+        <v>41.64480209350586</v>
       </c>
     </row>
     <row r="826">
@@ -46194,7 +46194,7 @@
         </is>
       </c>
       <c r="B829" s="2" t="n">
-        <v>40.11804962158203</v>
+        <v>40.11804580688477</v>
       </c>
     </row>
     <row r="830">
@@ -46204,7 +46204,7 @@
         </is>
       </c>
       <c r="B830" s="2" t="n">
-        <v>40.45412826538086</v>
+        <v>40.45413208007812</v>
       </c>
     </row>
     <row r="831">
@@ -46214,7 +46214,7 @@
         </is>
       </c>
       <c r="B831" s="2" t="n">
-        <v>40.30049514770508</v>
+        <v>40.30049133300781</v>
       </c>
     </row>
     <row r="832">
@@ -46224,7 +46224,7 @@
         </is>
       </c>
       <c r="B832" s="2" t="n">
-        <v>40.5981559753418</v>
+        <v>40.59815979003906</v>
       </c>
     </row>
     <row r="833">
@@ -46234,7 +46234,7 @@
         </is>
       </c>
       <c r="B833" s="2" t="n">
-        <v>40.93423843383789</v>
+        <v>40.93424224853516</v>
       </c>
     </row>
     <row r="834">
@@ -46284,7 +46284,7 @@
         </is>
       </c>
       <c r="B838" s="2" t="n">
-        <v>42.03849029541016</v>
+        <v>42.03849411010742</v>
       </c>
     </row>
     <row r="839">
@@ -46294,7 +46294,7 @@
         </is>
       </c>
       <c r="B839" s="2" t="n">
-        <v>41.95207214355469</v>
+        <v>41.95206832885742</v>
       </c>
     </row>
     <row r="840">
@@ -46304,7 +46304,7 @@
         </is>
       </c>
       <c r="B840" s="2" t="n">
-        <v>42.27854919433594</v>
+        <v>42.27854537963867</v>
       </c>
     </row>
     <row r="841">
@@ -46324,7 +46324,7 @@
         </is>
       </c>
       <c r="B842" s="2" t="n">
-        <v>43.25797271728516</v>
+        <v>43.25796890258789</v>
       </c>
     </row>
     <row r="843">
@@ -46334,7 +46334,7 @@
         </is>
       </c>
       <c r="B843" s="2" t="n">
-        <v>44.84233856201172</v>
+        <v>44.84233474731445</v>
       </c>
     </row>
     <row r="844">
@@ -46374,7 +46374,7 @@
         </is>
       </c>
       <c r="B847" s="2" t="n">
-        <v>45.22642517089844</v>
+        <v>45.2264289855957</v>
       </c>
     </row>
     <row r="848">
@@ -46434,7 +46434,7 @@
         </is>
       </c>
       <c r="B853" s="2" t="n">
-        <v>44.19898986816406</v>
+        <v>44.1989860534668</v>
       </c>
     </row>
     <row r="854">
@@ -46474,7 +46474,7 @@
         </is>
       </c>
       <c r="B857" s="2" t="n">
-        <v>43.72848510742188</v>
+        <v>43.72848129272461</v>
       </c>
     </row>
     <row r="858">
@@ -46484,7 +46484,7 @@
         </is>
       </c>
       <c r="B858" s="2" t="n">
-        <v>43.6612663269043</v>
+        <v>43.66127014160156</v>
       </c>
     </row>
     <row r="859">
@@ -46494,7 +46494,7 @@
         </is>
       </c>
       <c r="B859" s="2" t="n">
-        <v>44.09336471557617</v>
+        <v>44.09336090087891</v>
       </c>
     </row>
     <row r="860">
@@ -46524,7 +46524,7 @@
         </is>
       </c>
       <c r="B862" s="2" t="n">
-        <v>43.43080902099609</v>
+        <v>43.43081283569336</v>
       </c>
     </row>
     <row r="863">
@@ -46534,7 +46534,7 @@
         </is>
       </c>
       <c r="B863" s="2" t="n">
-        <v>43.36360168457031</v>
+        <v>43.36359786987305</v>
       </c>
     </row>
     <row r="864">
@@ -46554,7 +46554,7 @@
         </is>
       </c>
       <c r="B865" s="2" t="n">
-        <v>43.51723098754883</v>
+        <v>43.51723480224609</v>
       </c>
     </row>
     <row r="866">
@@ -46564,7 +46564,7 @@
         </is>
       </c>
       <c r="B866" s="2" t="n">
-        <v>43.3828010559082</v>
+        <v>43.38280487060547</v>
       </c>
     </row>
     <row r="867">
@@ -46594,7 +46594,7 @@
         </is>
       </c>
       <c r="B869" s="2" t="n">
-        <v>42.72025299072266</v>
+        <v>42.72024917602539</v>
       </c>
     </row>
     <row r="870">
@@ -46614,7 +46614,7 @@
         </is>
       </c>
       <c r="B871" s="2" t="n">
-        <v>43.54603958129883</v>
+        <v>43.54603576660156</v>
       </c>
     </row>
     <row r="872">
@@ -46634,7 +46634,7 @@
         </is>
       </c>
       <c r="B873" s="2" t="n">
-        <v>43.95893096923828</v>
+        <v>43.95893478393555</v>
       </c>
     </row>
     <row r="874">
@@ -46654,7 +46654,7 @@
         </is>
       </c>
       <c r="B875" s="2" t="n">
-        <v>42.54740905761719</v>
+        <v>42.54741287231445</v>
       </c>
     </row>
     <row r="876">
@@ -46784,7 +46784,7 @@
         </is>
       </c>
       <c r="B888" s="2" t="n">
-        <v>41.5391731262207</v>
+        <v>41.53917694091797</v>
       </c>
     </row>
     <row r="889">
@@ -46804,7 +46804,7 @@
         </is>
       </c>
       <c r="B890" s="2" t="n">
-        <v>41.78883361816406</v>
+        <v>41.78883743286133</v>
       </c>
     </row>
     <row r="891">
@@ -46814,7 +46814,7 @@
         </is>
       </c>
       <c r="B891" s="2" t="n">
-        <v>41.89446258544922</v>
+        <v>41.89445877075195</v>
       </c>
     </row>
     <row r="892">
@@ -46854,7 +46854,7 @@
         </is>
       </c>
       <c r="B895" s="2" t="n">
-        <v>42.27854919433594</v>
+        <v>42.27854537963867</v>
       </c>
     </row>
     <row r="896">
@@ -46884,7 +46884,7 @@
         </is>
       </c>
       <c r="B898" s="2" t="n">
-        <v>42.27854919433594</v>
+        <v>42.27854537963867</v>
       </c>
     </row>
     <row r="899">

--- a/demo_output/test/prompt_7/figure_00_Globale aktiemarkeder — indekseret kursudvikl.xlsx
+++ b/demo_output/test/prompt_7/figure_00_Globale aktiemarkeder — indekseret kursudvikl.xlsx
@@ -37924,7 +37924,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>47.67718887329102</v>
+        <v>47.67719650268555</v>
       </c>
     </row>
     <row r="3">
@@ -37954,7 +37954,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>48.51362991333008</v>
+        <v>48.51363372802734</v>
       </c>
     </row>
     <row r="6">
@@ -37974,7 +37974,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>49.83057403564453</v>
+        <v>49.8305778503418</v>
       </c>
     </row>
     <row r="8">
@@ -38004,7 +38004,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>49.82167434692383</v>
+        <v>49.82168197631836</v>
       </c>
     </row>
     <row r="11">
@@ -38014,7 +38014,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>49.5725212097168</v>
+        <v>49.57252883911133</v>
       </c>
     </row>
     <row r="12">
@@ -38044,7 +38044,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>49.58402633666992</v>
+        <v>49.58403015136719</v>
       </c>
     </row>
     <row r="15">
@@ -38054,7 +38054,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>49.41422653198242</v>
+        <v>49.41423034667969</v>
       </c>
     </row>
     <row r="16">
@@ -38074,7 +38074,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>49.20866775512695</v>
+        <v>49.20867156982422</v>
       </c>
     </row>
     <row r="18">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>48.53837585449219</v>
+        <v>48.53837203979492</v>
       </c>
     </row>
     <row r="19">
@@ -38094,7 +38094,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>48.80648803710938</v>
+        <v>48.80649185180664</v>
       </c>
     </row>
     <row r="20">
@@ -38104,7 +38104,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>48.46687316894531</v>
+        <v>48.46686935424805</v>
       </c>
     </row>
     <row r="21">
@@ -38114,7 +38114,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>48.67243194580078</v>
+        <v>48.67243576049805</v>
       </c>
     </row>
     <row r="22">
@@ -38134,7 +38134,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>48.74393463134766</v>
+        <v>48.74393081665039</v>
       </c>
     </row>
     <row r="24">
@@ -38144,7 +38144,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>49.19079208374023</v>
+        <v>49.19079971313477</v>
       </c>
     </row>
     <row r="25">
@@ -38154,7 +38154,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>49.60190963745117</v>
+        <v>49.60190200805664</v>
       </c>
     </row>
     <row r="26">
@@ -38174,7 +38174,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>49.61083984375</v>
+        <v>49.61084365844727</v>
       </c>
     </row>
     <row r="28">
@@ -38224,7 +38224,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>48.04681396484375</v>
+        <v>48.04681777954102</v>
       </c>
     </row>
     <row r="33">
@@ -38244,7 +38244,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>47.85913848876953</v>
+        <v>47.8591423034668</v>
       </c>
     </row>
     <row r="35">
@@ -38264,7 +38264,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>47.94850921630859</v>
+        <v>47.94851303100586</v>
       </c>
     </row>
     <row r="37">
@@ -38274,7 +38274,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>48.15406799316406</v>
+        <v>48.15407180786133</v>
       </c>
     </row>
     <row r="38">
@@ -38284,7 +38284,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>48.27024459838867</v>
+        <v>48.2702522277832</v>
       </c>
     </row>
     <row r="39">
@@ -38304,7 +38304,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>47.09053039550781</v>
+        <v>47.09053421020508</v>
       </c>
     </row>
     <row r="41">
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>47.54634094238281</v>
+        <v>47.54633712768555</v>
       </c>
     </row>
     <row r="43">
@@ -38334,7 +38334,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>47.63571166992188</v>
+        <v>47.63570404052734</v>
       </c>
     </row>
     <row r="44">
@@ -38344,7 +38344,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46.92966461181641</v>
+        <v>46.92966079711914</v>
       </c>
     </row>
     <row r="45">
@@ -38364,7 +38364,7 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45.10644912719727</v>
+        <v>45.1064567565918</v>
       </c>
     </row>
     <row r="47">
@@ -38384,7 +38384,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46.56322860717773</v>
+        <v>46.563232421875</v>
       </c>
     </row>
     <row r="49">
@@ -38404,7 +38404,7 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46.44704818725586</v>
+        <v>46.44705200195312</v>
       </c>
     </row>
     <row r="51">
@@ -38424,7 +38424,7 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46.88497161865234</v>
+        <v>46.88497543334961</v>
       </c>
     </row>
     <row r="53">
@@ -38434,7 +38434,7 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46.81346893310547</v>
+        <v>46.8134765625</v>
       </c>
     </row>
     <row r="54">
@@ -38444,7 +38444,7 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46.42023468017578</v>
+        <v>46.42023849487305</v>
       </c>
     </row>
     <row r="55">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46.57216262817383</v>
+        <v>46.57217407226562</v>
       </c>
     </row>
     <row r="56">
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46.75985336303711</v>
+        <v>46.75984954833984</v>
       </c>
     </row>
     <row r="58">
@@ -38484,7 +38484,7 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46.34873580932617</v>
+        <v>46.34873199462891</v>
       </c>
     </row>
     <row r="59">
@@ -38494,7 +38494,7 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46.23255157470703</v>
+        <v>46.2325553894043</v>
       </c>
     </row>
     <row r="60">
@@ -38504,7 +38504,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45.8125</v>
+        <v>45.81249237060547</v>
       </c>
     </row>
     <row r="61">
@@ -38514,7 +38514,7 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>44.9724006652832</v>
+        <v>44.97239685058594</v>
       </c>
     </row>
     <row r="62">
@@ -38544,7 +38544,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>44.23953628540039</v>
+        <v>44.23954391479492</v>
       </c>
     </row>
     <row r="65">
@@ -38554,7 +38554,7 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>44.90983581542969</v>
+        <v>44.90983200073242</v>
       </c>
     </row>
     <row r="66">
@@ -38564,7 +38564,7 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45.92868041992188</v>
+        <v>45.92868423461914</v>
       </c>
     </row>
     <row r="67">
@@ -38574,7 +38574,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45.9823112487793</v>
+        <v>45.98230743408203</v>
       </c>
     </row>
     <row r="68">
@@ -38594,7 +38594,7 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46.10743713378906</v>
+        <v>46.10742950439453</v>
       </c>
     </row>
     <row r="70">
@@ -38614,7 +38614,7 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46.84028244018555</v>
+        <v>46.84028625488281</v>
       </c>
     </row>
     <row r="72">
@@ -38624,7 +38624,7 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>47.4390869140625</v>
+        <v>47.43908309936523</v>
       </c>
     </row>
     <row r="73">
@@ -38664,7 +38664,7 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>47.05478286743164</v>
+        <v>47.05477905273438</v>
       </c>
     </row>
     <row r="77">
@@ -38724,7 +38724,7 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46.10743713378906</v>
+        <v>46.10742950439453</v>
       </c>
     </row>
     <row r="83">
@@ -38744,7 +38744,7 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>44.67747116088867</v>
+        <v>44.67746734619141</v>
       </c>
     </row>
     <row r="85">
@@ -38754,7 +38754,7 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45.00814056396484</v>
+        <v>45.00814437866211</v>
       </c>
     </row>
     <row r="86">
@@ -38764,7 +38764,7 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45.57119750976562</v>
+        <v>45.57119369506836</v>
       </c>
     </row>
     <row r="87">
@@ -38774,7 +38774,7 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45.92868041992188</v>
+        <v>45.92868423461914</v>
       </c>
     </row>
     <row r="88">
@@ -38784,7 +38784,7 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45.38350677490234</v>
+        <v>45.38351440429688</v>
       </c>
     </row>
     <row r="89">
@@ -38804,7 +38804,7 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45.08858108520508</v>
+        <v>45.08858489990234</v>
       </c>
     </row>
     <row r="91">
@@ -38814,7 +38814,7 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>44.66853332519531</v>
+        <v>44.66852569580078</v>
       </c>
     </row>
     <row r="92">
@@ -38844,7 +38844,7 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>44.31997680664062</v>
+        <v>44.31997299194336</v>
       </c>
     </row>
     <row r="95">
@@ -38854,7 +38854,7 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>44.63277816772461</v>
+        <v>44.63277435302734</v>
       </c>
     </row>
     <row r="96">
@@ -38864,7 +38864,7 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>44.38253784179688</v>
+        <v>44.38254165649414</v>
       </c>
     </row>
     <row r="97">
@@ -38874,7 +38874,7 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45.24945449829102</v>
+        <v>45.24945068359375</v>
       </c>
     </row>
     <row r="98">
@@ -38884,7 +38884,7 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45.41925811767578</v>
+        <v>45.41926193237305</v>
       </c>
     </row>
     <row r="99">
@@ -38894,7 +38894,7 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45.32989501953125</v>
+        <v>45.32988739013672</v>
       </c>
     </row>
     <row r="100">
@@ -38904,7 +38904,7 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45.09751892089844</v>
+        <v>45.09751510620117</v>
       </c>
     </row>
     <row r="101">
@@ -38914,7 +38914,7 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45.72312545776367</v>
+        <v>45.72312927246094</v>
       </c>
     </row>
     <row r="102">
@@ -38934,7 +38934,7 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46.42023468017578</v>
+        <v>46.42023849487305</v>
       </c>
     </row>
     <row r="104">
@@ -38954,7 +38954,7 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46.92072296142578</v>
+        <v>46.92071914672852</v>
       </c>
     </row>
     <row r="106">
@@ -38974,7 +38974,7 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46.60791397094727</v>
+        <v>46.6079216003418</v>
       </c>
     </row>
     <row r="108">
@@ -38994,7 +38994,7 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46.75091934204102</v>
+        <v>46.75091552734375</v>
       </c>
     </row>
     <row r="110">
@@ -39014,7 +39014,7 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46.13424682617188</v>
+        <v>46.13423919677734</v>
       </c>
     </row>
     <row r="112">
@@ -39024,7 +39024,7 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46.17892456054688</v>
+        <v>46.17893218994141</v>
       </c>
     </row>
     <row r="113">
@@ -39034,7 +39034,7 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45.50862884521484</v>
+        <v>45.50862503051758</v>
       </c>
     </row>
     <row r="114">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45.66949844360352</v>
+        <v>45.66950225830078</v>
       </c>
     </row>
     <row r="117">
@@ -39074,7 +39074,7 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45.56225204467773</v>
+        <v>45.56225967407227</v>
       </c>
     </row>
     <row r="118">
@@ -39084,7 +39084,7 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45.50862884521484</v>
+        <v>45.50862503051758</v>
       </c>
     </row>
     <row r="119">
@@ -39094,7 +39094,7 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45.92868041992188</v>
+        <v>45.92868423461914</v>
       </c>
     </row>
     <row r="120">
@@ -39114,7 +39114,7 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45.56225204467773</v>
+        <v>45.56225967407227</v>
       </c>
     </row>
     <row r="122">
@@ -39124,7 +39124,7 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46.34873580932617</v>
+        <v>46.34873199462891</v>
       </c>
     </row>
     <row r="123">
@@ -39134,7 +39134,7 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46.47385406494141</v>
+        <v>46.47386169433594</v>
       </c>
     </row>
     <row r="124">
@@ -39164,7 +39164,7 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46.14318084716797</v>
+        <v>46.1431770324707</v>
       </c>
     </row>
     <row r="127">
@@ -39174,7 +39174,7 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45.58013153076172</v>
+        <v>45.58012771606445</v>
       </c>
     </row>
     <row r="128">
@@ -39184,7 +39184,7 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45.50862884521484</v>
+        <v>45.50862503051758</v>
       </c>
     </row>
     <row r="129">
@@ -39194,7 +39194,7 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45.1422004699707</v>
+        <v>45.14219665527344</v>
       </c>
     </row>
     <row r="130">
@@ -39204,7 +39204,7 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45.09751892089844</v>
+        <v>45.09751510620117</v>
       </c>
     </row>
     <row r="131">
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>43.52455902099609</v>
+        <v>43.52455139160156</v>
       </c>
     </row>
     <row r="133">
@@ -39234,7 +39234,7 @@
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>43.69436645507812</v>
+        <v>43.69436264038086</v>
       </c>
     </row>
     <row r="134">
@@ -39244,7 +39244,7 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>43.64967727661133</v>
+        <v>43.64968109130859</v>
       </c>
     </row>
     <row r="135">
@@ -39254,7 +39254,7 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>43.810546875</v>
+        <v>43.81055068969727</v>
       </c>
     </row>
     <row r="136">
@@ -39264,7 +39264,7 @@
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>44.3467903137207</v>
+        <v>44.34678268432617</v>
       </c>
     </row>
     <row r="137">
@@ -39274,7 +39274,7 @@
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>43.72117233276367</v>
+        <v>43.72117614746094</v>
       </c>
     </row>
     <row r="138">
@@ -39284,7 +39284,7 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>44.060791015625</v>
+        <v>44.06079483032227</v>
       </c>
     </row>
     <row r="139">
@@ -39294,7 +39294,7 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>44.75790786743164</v>
+        <v>44.75790405273438</v>
       </c>
     </row>
     <row r="140">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>44.9366455078125</v>
+        <v>44.93664169311523</v>
       </c>
     </row>
     <row r="141">
@@ -39314,7 +39314,7 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>44.72215270996094</v>
+        <v>44.72214889526367</v>
       </c>
     </row>
     <row r="142">
@@ -39324,7 +39324,7 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>44.75790786743164</v>
+        <v>44.75790405273438</v>
       </c>
     </row>
     <row r="143">
@@ -39334,7 +39334,7 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>44.04809188842773</v>
+        <v>44.04808807373047</v>
       </c>
     </row>
     <row r="144">
@@ -39344,7 +39344,7 @@
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>43.9483757019043</v>
+        <v>43.94837188720703</v>
       </c>
     </row>
     <row r="145">
@@ -39354,7 +39354,7 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>43.82146453857422</v>
+        <v>43.82145690917969</v>
       </c>
     </row>
     <row r="146">
@@ -39384,7 +39384,7 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>43.00558471679688</v>
+        <v>43.00558090209961</v>
       </c>
     </row>
     <row r="149">
@@ -39414,7 +39414,7 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>44.16593933105469</v>
+        <v>44.16594696044922</v>
       </c>
     </row>
     <row r="152">
@@ -39454,7 +39454,7 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>44.52519226074219</v>
+        <v>44.52518844604492</v>
       </c>
     </row>
     <row r="156">
@@ -39464,7 +39464,7 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>44.3075065612793</v>
+        <v>44.30751037597656</v>
       </c>
     </row>
     <row r="157">
@@ -39474,7 +39474,7 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>44.62496566772461</v>
+        <v>44.62496948242188</v>
       </c>
     </row>
     <row r="158">
@@ -39484,7 +39484,7 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>44.47076797485352</v>
+        <v>44.47077178955078</v>
       </c>
     </row>
     <row r="159">
@@ -39534,7 +39534,7 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45.36871719360352</v>
+        <v>45.36871337890625</v>
       </c>
     </row>
     <row r="164">
@@ -39554,7 +39554,7 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>45.46849060058594</v>
+        <v>45.46848678588867</v>
       </c>
     </row>
     <row r="166">
@@ -39564,7 +39564,7 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45.45034790039062</v>
+        <v>45.45034408569336</v>
       </c>
     </row>
     <row r="167">
@@ -39584,7 +39584,7 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>44.83358001708984</v>
+        <v>44.83357620239258</v>
       </c>
     </row>
     <row r="169">
@@ -39594,7 +39594,7 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>45.09661102294922</v>
+        <v>45.09661865234375</v>
       </c>
     </row>
     <row r="170">
@@ -39614,7 +39614,7 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>43.81772994995117</v>
+        <v>43.81772613525391</v>
       </c>
     </row>
     <row r="172">
@@ -39624,7 +39624,7 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>43.73609161376953</v>
+        <v>43.73609924316406</v>
       </c>
     </row>
     <row r="173">
@@ -39634,7 +39634,7 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>43.18281173706055</v>
+        <v>43.18281555175781</v>
       </c>
     </row>
     <row r="174">
@@ -39644,7 +39644,7 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>42.68396377563477</v>
+        <v>42.6839599609375</v>
       </c>
     </row>
     <row r="175">
@@ -39654,7 +39654,7 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>42.892578125</v>
+        <v>42.89257049560547</v>
       </c>
     </row>
     <row r="176">
@@ -39664,7 +39664,7 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>44.29843521118164</v>
+        <v>44.29843902587891</v>
       </c>
     </row>
     <row r="177">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>44.57054901123047</v>
+        <v>44.57054138183594</v>
       </c>
     </row>
     <row r="178">
@@ -39684,7 +39684,7 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>44.49798583984375</v>
+        <v>44.49798965454102</v>
       </c>
     </row>
     <row r="179">
@@ -39694,7 +39694,7 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>44.02634429931641</v>
+        <v>44.02634048461914</v>
       </c>
     </row>
     <row r="180">
@@ -39714,7 +39714,7 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>44.04448318481445</v>
+        <v>44.04447937011719</v>
       </c>
     </row>
     <row r="182">
@@ -39724,7 +39724,7 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>44.47076797485352</v>
+        <v>44.47077178955078</v>
       </c>
     </row>
     <row r="183">
@@ -39754,7 +39754,7 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>44.18960189819336</v>
+        <v>44.18959808349609</v>
       </c>
     </row>
     <row r="186">
@@ -39764,7 +39764,7 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>43.88121795654297</v>
+        <v>43.88122177124023</v>
       </c>
     </row>
     <row r="187">
@@ -39774,7 +39774,7 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>44.83358001708984</v>
+        <v>44.83357620239258</v>
       </c>
     </row>
     <row r="188">
@@ -39784,7 +39784,7 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>45.16010284423828</v>
+        <v>45.16010665893555</v>
       </c>
     </row>
     <row r="189">
@@ -39804,7 +39804,7 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>44.18960189819336</v>
+        <v>44.18959808349609</v>
       </c>
     </row>
     <row r="191">
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>43.05583953857422</v>
+        <v>43.05583572387695</v>
       </c>
     </row>
     <row r="193">
@@ -39844,7 +39844,7 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>42.94699478149414</v>
+        <v>42.94699096679688</v>
       </c>
     </row>
     <row r="195">
@@ -39864,7 +39864,7 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>41.82229614257812</v>
+        <v>41.82230377197266</v>
       </c>
     </row>
     <row r="197">
@@ -39874,7 +39874,7 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>41.89485549926758</v>
+        <v>41.89485931396484</v>
       </c>
     </row>
     <row r="198">
@@ -39884,7 +39884,7 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>41.30530166625977</v>
+        <v>41.3053092956543</v>
       </c>
     </row>
     <row r="199">
@@ -39904,7 +39904,7 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>38.95613861083984</v>
+        <v>38.95615005493164</v>
       </c>
     </row>
     <row r="201">
@@ -39924,7 +39924,7 @@
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>40.18968200683594</v>
+        <v>40.18967819213867</v>
       </c>
     </row>
     <row r="203">
@@ -39934,7 +39934,7 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>39.43686294555664</v>
+        <v>39.43685913085938</v>
       </c>
     </row>
     <row r="204">
@@ -39944,7 +39944,7 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>38.61148071289062</v>
+        <v>38.61147689819336</v>
       </c>
     </row>
     <row r="205">
@@ -39964,7 +39964,7 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>37.7316780090332</v>
+        <v>37.73168182373047</v>
       </c>
     </row>
     <row r="207">
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>40.77017211914062</v>
+        <v>40.77016830444336</v>
       </c>
     </row>
     <row r="208">
@@ -39984,7 +39984,7 @@
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>40.56156158447266</v>
+        <v>40.56155776977539</v>
       </c>
     </row>
     <row r="209">
@@ -40024,7 +40024,7 @@
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>40.96970367431641</v>
+        <v>40.9697151184082</v>
       </c>
     </row>
     <row r="213">
@@ -40034,7 +40034,7 @@
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>41.18739700317383</v>
+        <v>41.18739318847656</v>
       </c>
     </row>
     <row r="214">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>40.86087417602539</v>
+        <v>40.86087036132812</v>
       </c>
     </row>
     <row r="215">
@@ -40054,7 +40054,7 @@
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>40.99691772460938</v>
+        <v>40.99691390991211</v>
       </c>
     </row>
     <row r="216">
@@ -40064,7 +40064,7 @@
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>41.6953239440918</v>
+        <v>41.69531631469727</v>
       </c>
     </row>
     <row r="217">
@@ -40074,7 +40074,7 @@
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>41.57740783691406</v>
+        <v>41.5774040222168</v>
       </c>
     </row>
     <row r="218">
@@ -40084,7 +40084,7 @@
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>40.95156478881836</v>
+        <v>40.95157241821289</v>
       </c>
     </row>
     <row r="219">
@@ -40094,7 +40094,7 @@
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>41.6318244934082</v>
+        <v>41.63183212280273</v>
       </c>
     </row>
     <row r="220">
@@ -40104,7 +40104,7 @@
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>42.36650466918945</v>
+        <v>42.36650085449219</v>
       </c>
     </row>
     <row r="221">
@@ -40114,7 +40114,7 @@
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>41.58648300170898</v>
+        <v>41.58647918701172</v>
       </c>
     </row>
     <row r="222">
@@ -40174,7 +40174,7 @@
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>40.64319229125977</v>
+        <v>40.6431884765625</v>
       </c>
     </row>
     <row r="228">
@@ -40194,7 +40194,7 @@
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>39.98107147216797</v>
+        <v>39.9810676574707</v>
       </c>
     </row>
     <row r="230">
@@ -40204,7 +40204,7 @@
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>39.78152084350586</v>
+        <v>39.78152465820312</v>
       </c>
     </row>
     <row r="231">
@@ -40214,7 +40214,7 @@
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>39.54570007324219</v>
+        <v>39.54569625854492</v>
       </c>
     </row>
     <row r="232">
@@ -40224,7 +40224,7 @@
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>38.78380584716797</v>
+        <v>38.78380966186523</v>
       </c>
     </row>
     <row r="233">
@@ -40244,7 +40244,7 @@
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>38.15796661376953</v>
+        <v>38.15797424316406</v>
       </c>
     </row>
     <row r="235">
@@ -40254,7 +40254,7 @@
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>37.32352447509766</v>
+        <v>37.32352828979492</v>
       </c>
     </row>
     <row r="236">
@@ -40264,7 +40264,7 @@
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>37.75888824462891</v>
+        <v>37.75888442993164</v>
       </c>
     </row>
     <row r="237">
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>38.30309677124023</v>
+        <v>38.30309295654297</v>
       </c>
     </row>
     <row r="238">
@@ -40294,7 +40294,7 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>38.38472366333008</v>
+        <v>38.38471984863281</v>
       </c>
     </row>
     <row r="240">
@@ -40304,7 +40304,7 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>38.6659049987793</v>
+        <v>38.66589736938477</v>
       </c>
     </row>
     <row r="241">
@@ -40324,7 +40324,7 @@
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>37.6409797668457</v>
+        <v>37.64097595214844</v>
       </c>
     </row>
     <row r="243">
@@ -40334,7 +40334,7 @@
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>37.12398147583008</v>
+        <v>37.12397766113281</v>
       </c>
     </row>
     <row r="244">
@@ -40344,7 +40344,7 @@
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>36.0537109375</v>
+        <v>36.05370712280273</v>
       </c>
     </row>
     <row r="245">
@@ -40354,7 +40354,7 @@
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>36.22603607177734</v>
+        <v>36.22603225708008</v>
       </c>
     </row>
     <row r="246">
@@ -40364,7 +40364,7 @@
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>35.97208023071289</v>
+        <v>35.97207641601562</v>
       </c>
     </row>
     <row r="247">
@@ -40374,7 +40374,7 @@
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>35.73625564575195</v>
+        <v>35.73625183105469</v>
       </c>
     </row>
     <row r="248">
@@ -40384,7 +40384,7 @@
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>36.72489547729492</v>
+        <v>36.72489929199219</v>
       </c>
     </row>
     <row r="249">
@@ -40394,7 +40394,7 @@
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>36.57977676391602</v>
+        <v>36.57978057861328</v>
       </c>
     </row>
     <row r="250">
@@ -40404,7 +40404,7 @@
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>37.47771453857422</v>
+        <v>37.47771835327148</v>
       </c>
     </row>
     <row r="251">
@@ -40414,7 +40414,7 @@
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>36.57977676391602</v>
+        <v>36.57978057861328</v>
       </c>
     </row>
     <row r="252">
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>37.1602668762207</v>
+        <v>37.16026306152344</v>
       </c>
     </row>
     <row r="253">
@@ -40444,7 +40444,7 @@
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>37.59562301635742</v>
+        <v>37.59563064575195</v>
       </c>
     </row>
     <row r="255">
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>36.94257354736328</v>
+        <v>36.94258117675781</v>
       </c>
     </row>
     <row r="256">
@@ -40464,7 +40464,7 @@
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>37.12398147583008</v>
+        <v>37.12397766113281</v>
       </c>
     </row>
     <row r="257">
@@ -40474,7 +40474,7 @@
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>37.70446395874023</v>
+        <v>37.70447158813477</v>
       </c>
     </row>
     <row r="258">
@@ -40494,7 +40494,7 @@
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>38.67497253417969</v>
+        <v>38.67496871948242</v>
       </c>
     </row>
     <row r="260">
@@ -40504,7 +40504,7 @@
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>38.40286636352539</v>
+        <v>38.40287017822266</v>
       </c>
     </row>
     <row r="261">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>38.43008041381836</v>
+        <v>38.43007278442383</v>
       </c>
     </row>
     <row r="263">
@@ -40534,7 +40534,7 @@
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>38.63869476318359</v>
+        <v>38.63868713378906</v>
       </c>
     </row>
     <row r="264">
@@ -40554,7 +40554,7 @@
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>38.96521759033203</v>
+        <v>38.96521377563477</v>
       </c>
     </row>
     <row r="266">
@@ -40564,7 +40564,7 @@
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>38.04317474365234</v>
+        <v>38.04317855834961</v>
       </c>
     </row>
     <row r="267">
@@ -40584,7 +40584,7 @@
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>36.30521011352539</v>
+        <v>36.30520629882812</v>
       </c>
     </row>
     <row r="269">
@@ -40624,7 +40624,7 @@
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>36.28691101074219</v>
+        <v>36.28691864013672</v>
       </c>
     </row>
     <row r="273">
@@ -40634,7 +40634,7 @@
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>36.87234115600586</v>
+        <v>36.87233734130859</v>
       </c>
     </row>
     <row r="274">
@@ -40644,7 +40644,7 @@
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>36.21373748779297</v>
+        <v>36.21374130249023</v>
       </c>
     </row>
     <row r="275">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>36.3234977722168</v>
+        <v>36.32350540161133</v>
       </c>
     </row>
     <row r="276">
@@ -40664,7 +40664,7 @@
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>37.1833381652832</v>
+        <v>37.18334197998047</v>
       </c>
     </row>
     <row r="277">
@@ -40684,7 +40684,7 @@
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>37.00039672851562</v>
+        <v>37.00040054321289</v>
       </c>
     </row>
     <row r="279">
@@ -40704,7 +40704,7 @@
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>36.68024826049805</v>
+        <v>36.68024444580078</v>
       </c>
     </row>
     <row r="281">
@@ -40724,7 +40724,7 @@
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>36.16800308227539</v>
+        <v>36.16800689697266</v>
       </c>
     </row>
     <row r="283">
@@ -40744,7 +40744,7 @@
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>36.67109298706055</v>
+        <v>36.67110061645508</v>
       </c>
     </row>
     <row r="285">
@@ -40754,7 +40754,7 @@
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>36.67109298706055</v>
+        <v>36.67110061645508</v>
       </c>
     </row>
     <row r="286">
@@ -40764,7 +40764,7 @@
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>35.69235229492188</v>
+        <v>35.69234848022461</v>
       </c>
     </row>
     <row r="287">
@@ -40774,7 +40774,7 @@
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>35.55513381958008</v>
+        <v>35.55513763427734</v>
       </c>
     </row>
     <row r="288">
@@ -40794,7 +40794,7 @@
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>35.15266418457031</v>
+        <v>35.15266036987305</v>
       </c>
     </row>
     <row r="290">
@@ -40814,7 +40814,7 @@
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>35.58258438110352</v>
+        <v>35.58258056640625</v>
       </c>
     </row>
     <row r="292">
@@ -40824,7 +40824,7 @@
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>36.16800308227539</v>
+        <v>36.16800689697266</v>
       </c>
     </row>
     <row r="293">
@@ -40834,7 +40834,7 @@
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>36.01250457763672</v>
+        <v>36.01249313354492</v>
       </c>
     </row>
     <row r="294">
@@ -40844,7 +40844,7 @@
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>36.42412185668945</v>
+        <v>36.42411804199219</v>
       </c>
     </row>
     <row r="295">
@@ -40854,7 +40854,7 @@
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>36.05823135375977</v>
+        <v>36.05823516845703</v>
       </c>
     </row>
     <row r="296">
@@ -40864,7 +40864,7 @@
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>36.1862907409668</v>
+        <v>36.18629837036133</v>
       </c>
     </row>
     <row r="297">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="B299" s="2" t="n">
-        <v>36.72597885131836</v>
+        <v>36.72598266601562</v>
       </c>
     </row>
     <row r="300">
@@ -40954,7 +40954,7 @@
         </is>
       </c>
       <c r="B305" s="2" t="n">
-        <v>36.64366149902344</v>
+        <v>36.64365768432617</v>
       </c>
     </row>
     <row r="306">
@@ -40984,7 +40984,7 @@
         </is>
       </c>
       <c r="B308" s="2" t="n">
-        <v>37.00954055786133</v>
+        <v>37.00953674316406</v>
       </c>
     </row>
     <row r="309">
@@ -41014,7 +41014,7 @@
         </is>
       </c>
       <c r="B311" s="2" t="n">
-        <v>37.37543106079102</v>
+        <v>37.37543487548828</v>
       </c>
     </row>
     <row r="312">
@@ -41034,7 +41034,7 @@
         </is>
       </c>
       <c r="B313" s="2" t="n">
-        <v>37.21078872680664</v>
+        <v>37.21078109741211</v>
       </c>
     </row>
     <row r="314">
@@ -41044,7 +41044,7 @@
         </is>
       </c>
       <c r="B314" s="2" t="n">
-        <v>37.00039672851562</v>
+        <v>37.00040054321289</v>
       </c>
     </row>
     <row r="315">
@@ -41074,7 +41074,7 @@
         </is>
       </c>
       <c r="B317" s="2" t="n">
-        <v>36.36923980712891</v>
+        <v>36.36924362182617</v>
       </c>
     </row>
     <row r="318">
@@ -41084,7 +41084,7 @@
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>36.3600959777832</v>
+        <v>36.36009216308594</v>
       </c>
     </row>
     <row r="319">
@@ -41114,7 +41114,7 @@
         </is>
       </c>
       <c r="B321" s="2" t="n">
-        <v>36.36923980712891</v>
+        <v>36.36924362182617</v>
       </c>
     </row>
     <row r="322">
@@ -41124,7 +41124,7 @@
         </is>
       </c>
       <c r="B322" s="2" t="n">
-        <v>35.93932342529297</v>
+        <v>35.9393196105957</v>
       </c>
     </row>
     <row r="323">
@@ -41144,7 +41144,7 @@
         </is>
       </c>
       <c r="B324" s="2" t="n">
-        <v>35.78382110595703</v>
+        <v>35.78381729125977</v>
       </c>
     </row>
     <row r="325">
@@ -41154,7 +41154,7 @@
         </is>
       </c>
       <c r="B325" s="2" t="n">
-        <v>35.45452117919922</v>
+        <v>35.45451736450195</v>
       </c>
     </row>
     <row r="326">
@@ -41184,7 +41184,7 @@
         </is>
       </c>
       <c r="B328" s="2" t="n">
-        <v>35.15266418457031</v>
+        <v>35.15266036987305</v>
       </c>
     </row>
     <row r="329">
@@ -41194,7 +41194,7 @@
         </is>
       </c>
       <c r="B329" s="2" t="n">
-        <v>35.67405319213867</v>
+        <v>35.67404937744141</v>
       </c>
     </row>
     <row r="330">
@@ -41204,7 +41204,7 @@
         </is>
       </c>
       <c r="B330" s="2" t="n">
-        <v>36.20459365844727</v>
+        <v>36.20459747314453</v>
       </c>
     </row>
     <row r="331">
@@ -41224,7 +41224,7 @@
         </is>
       </c>
       <c r="B332" s="2" t="n">
-        <v>35.26242446899414</v>
+        <v>35.26242065429688</v>
       </c>
     </row>
     <row r="333">
@@ -41234,7 +41234,7 @@
         </is>
       </c>
       <c r="B333" s="2" t="n">
-        <v>34.88739013671875</v>
+        <v>34.88739395141602</v>
       </c>
     </row>
     <row r="334">
@@ -41244,7 +41244,7 @@
         </is>
       </c>
       <c r="B334" s="2" t="n">
-        <v>34.56723785400391</v>
+        <v>34.56724548339844</v>
       </c>
     </row>
     <row r="335">
@@ -41294,7 +41294,7 @@
         </is>
       </c>
       <c r="B339" s="2" t="n">
-        <v>32.91160583496094</v>
+        <v>32.91160202026367</v>
       </c>
     </row>
     <row r="340">
@@ -41304,7 +41304,7 @@
         </is>
       </c>
       <c r="B340" s="2" t="n">
-        <v>32.50912475585938</v>
+        <v>32.50912094116211</v>
       </c>
     </row>
     <row r="341">
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="B342" s="2" t="n">
-        <v>32.756103515625</v>
+        <v>32.75609970092773</v>
       </c>
     </row>
     <row r="343">
@@ -41344,7 +41344,7 @@
         </is>
       </c>
       <c r="B344" s="2" t="n">
-        <v>31.90540885925293</v>
+        <v>31.9054126739502</v>
       </c>
     </row>
     <row r="345">
@@ -41364,7 +41364,7 @@
         </is>
       </c>
       <c r="B346" s="2" t="n">
-        <v>33.48788452148438</v>
+        <v>33.48787689208984</v>
       </c>
     </row>
     <row r="347">
@@ -41374,7 +41374,7 @@
         </is>
       </c>
       <c r="B347" s="2" t="n">
-        <v>33.50617218017578</v>
+        <v>33.50616455078125</v>
       </c>
     </row>
     <row r="348">
@@ -41384,7 +41384,7 @@
         </is>
       </c>
       <c r="B348" s="2" t="n">
-        <v>33.304931640625</v>
+        <v>33.30492782592773</v>
       </c>
     </row>
     <row r="349">
@@ -41404,7 +41404,7 @@
         </is>
       </c>
       <c r="B350" s="2" t="n">
-        <v>32.15238571166992</v>
+        <v>32.15238952636719</v>
       </c>
     </row>
     <row r="351">
@@ -41414,7 +41414,7 @@
         </is>
       </c>
       <c r="B351" s="2" t="n">
-        <v>31.6401424407959</v>
+        <v>31.64013862609863</v>
       </c>
     </row>
     <row r="352">
@@ -41424,7 +41424,7 @@
         </is>
       </c>
       <c r="B352" s="2" t="n">
-        <v>31.67672729492188</v>
+        <v>31.67673110961914</v>
       </c>
     </row>
     <row r="353">
@@ -41434,7 +41434,7 @@
         </is>
       </c>
       <c r="B353" s="2" t="n">
-        <v>31.76820182800293</v>
+        <v>31.7681999206543</v>
       </c>
     </row>
     <row r="354">
@@ -41444,7 +41444,7 @@
         </is>
       </c>
       <c r="B354" s="2" t="n">
-        <v>31.29254722595215</v>
+        <v>31.29254913330078</v>
       </c>
     </row>
     <row r="355">
@@ -41454,7 +41454,7 @@
         </is>
       </c>
       <c r="B355" s="2" t="n">
-        <v>32.15238571166992</v>
+        <v>32.15238952636719</v>
       </c>
     </row>
     <row r="356">
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="B357" s="2" t="n">
-        <v>31.57611465454102</v>
+        <v>31.57610893249512</v>
       </c>
     </row>
     <row r="358">
@@ -41484,7 +41484,7 @@
         </is>
       </c>
       <c r="B358" s="2" t="n">
-        <v>31.77734756469727</v>
+        <v>31.77735710144043</v>
       </c>
     </row>
     <row r="359">
@@ -41494,7 +41494,7 @@
         </is>
       </c>
       <c r="B359" s="2" t="n">
-        <v>32.26214981079102</v>
+        <v>32.26215362548828</v>
       </c>
     </row>
     <row r="360">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="B360" s="2" t="n">
-        <v>31.03642654418945</v>
+        <v>31.03642463684082</v>
       </c>
     </row>
     <row r="361">
@@ -41514,7 +41514,7 @@
         </is>
       </c>
       <c r="B361" s="2" t="n">
-        <v>31.29254722595215</v>
+        <v>31.29254913330078</v>
       </c>
     </row>
     <row r="362">
@@ -41524,7 +41524,7 @@
         </is>
       </c>
       <c r="B362" s="2" t="n">
-        <v>31.8047924041748</v>
+        <v>31.80478668212891</v>
       </c>
     </row>
     <row r="363">
@@ -41544,7 +41544,7 @@
         </is>
       </c>
       <c r="B364" s="2" t="n">
-        <v>31.3657283782959</v>
+        <v>31.36573028564453</v>
       </c>
     </row>
     <row r="365">
@@ -41554,7 +41554,7 @@
         </is>
       </c>
       <c r="B365" s="2" t="n">
-        <v>31.27425003051758</v>
+        <v>31.27425384521484</v>
       </c>
     </row>
     <row r="366">
@@ -41564,7 +41564,7 @@
         </is>
       </c>
       <c r="B366" s="2" t="n">
-        <v>31.85052680969238</v>
+        <v>31.85053253173828</v>
       </c>
     </row>
     <row r="367">
@@ -41574,7 +41574,7 @@
         </is>
       </c>
       <c r="B367" s="2" t="n">
-        <v>31.58525657653809</v>
+        <v>31.58525466918945</v>
       </c>
     </row>
     <row r="368">
@@ -41584,7 +41584,7 @@
         </is>
       </c>
       <c r="B368" s="2" t="n">
-        <v>31.76820182800293</v>
+        <v>31.7681999206543</v>
       </c>
     </row>
     <row r="369">
@@ -41594,7 +41594,7 @@
         </is>
       </c>
       <c r="B369" s="2" t="n">
-        <v>33.11284255981445</v>
+        <v>33.11283874511719</v>
       </c>
     </row>
     <row r="370">
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="B370" s="2" t="n">
-        <v>33.13113021850586</v>
+        <v>33.13113784790039</v>
       </c>
     </row>
     <row r="371">
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="B372" s="2" t="n">
-        <v>32.79268264770508</v>
+        <v>32.79268646240234</v>
       </c>
     </row>
     <row r="373">
@@ -41634,7 +41634,7 @@
         </is>
       </c>
       <c r="B373" s="2" t="n">
-        <v>33.9818229675293</v>
+        <v>33.98181915283203</v>
       </c>
     </row>
     <row r="374">
@@ -41644,7 +41644,7 @@
         </is>
       </c>
       <c r="B374" s="2" t="n">
-        <v>34.90568542480469</v>
+        <v>34.90568923950195</v>
       </c>
     </row>
     <row r="375">
@@ -41654,7 +41654,7 @@
         </is>
       </c>
       <c r="B375" s="2" t="n">
-        <v>34.69529724121094</v>
+        <v>34.6953010559082</v>
       </c>
     </row>
     <row r="376">
@@ -41694,7 +41694,7 @@
         </is>
       </c>
       <c r="B379" s="2" t="n">
-        <v>34.78677749633789</v>
+        <v>34.78676986694336</v>
       </c>
     </row>
     <row r="380">
@@ -41704,7 +41704,7 @@
         </is>
       </c>
       <c r="B380" s="2" t="n">
-        <v>34.34771347045898</v>
+        <v>34.34770965576172</v>
       </c>
     </row>
     <row r="381">
@@ -41714,7 +41714,7 @@
         </is>
       </c>
       <c r="B381" s="2" t="n">
-        <v>34.43003463745117</v>
+        <v>34.43003845214844</v>
       </c>
     </row>
     <row r="382">
@@ -41724,7 +41724,7 @@
         </is>
       </c>
       <c r="B382" s="2" t="n">
-        <v>34.71359634399414</v>
+        <v>34.71360015869141</v>
       </c>
     </row>
     <row r="383">
@@ -41734,7 +41734,7 @@
         </is>
       </c>
       <c r="B383" s="2" t="n">
-        <v>34.54895401000977</v>
+        <v>34.54894638061523</v>
       </c>
     </row>
     <row r="384">
@@ -41784,7 +41784,7 @@
         </is>
       </c>
       <c r="B388" s="2" t="n">
-        <v>36.16800308227539</v>
+        <v>36.16800689697266</v>
       </c>
     </row>
     <row r="389">
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="B389" s="2" t="n">
-        <v>35.75637817382812</v>
+        <v>35.75638198852539</v>
       </c>
     </row>
     <row r="390">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="B391" s="2" t="n">
-        <v>35.5002555847168</v>
+        <v>35.50025939941406</v>
       </c>
     </row>
     <row r="392">
@@ -41824,7 +41824,7 @@
         </is>
       </c>
       <c r="B392" s="2" t="n">
-        <v>35.93017196655273</v>
+        <v>35.93017578125</v>
       </c>
     </row>
     <row r="393">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="B393" s="2" t="n">
-        <v>35.69235229492188</v>
+        <v>35.69234848022461</v>
       </c>
     </row>
     <row r="394">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="B394" s="2" t="n">
-        <v>35.58258438110352</v>
+        <v>35.58258056640625</v>
       </c>
     </row>
     <row r="395">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="B395" s="2" t="n">
-        <v>35.8370361328125</v>
+        <v>35.83703231811523</v>
       </c>
     </row>
     <row r="396">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="B397" s="2" t="n">
-        <v>35.02909851074219</v>
+        <v>35.02910232543945</v>
       </c>
     </row>
     <row r="398">
@@ -41884,7 +41884,7 @@
         </is>
       </c>
       <c r="B398" s="2" t="n">
-        <v>35.13125610351562</v>
+        <v>35.13125228881836</v>
       </c>
     </row>
     <row r="399">
@@ -41934,7 +41934,7 @@
         </is>
       </c>
       <c r="B403" s="2" t="n">
-        <v>35.10339736938477</v>
+        <v>35.10338973999023</v>
       </c>
     </row>
     <row r="404">
@@ -41954,7 +41954,7 @@
         </is>
       </c>
       <c r="B405" s="2" t="n">
-        <v>35.10339736938477</v>
+        <v>35.10338973999023</v>
       </c>
     </row>
     <row r="406">
@@ -41964,7 +41964,7 @@
         </is>
       </c>
       <c r="B406" s="2" t="n">
-        <v>35.68844985961914</v>
+        <v>35.68844604492188</v>
       </c>
     </row>
     <row r="407">
@@ -41974,7 +41974,7 @@
         </is>
       </c>
       <c r="B407" s="2" t="n">
-        <v>35.19626235961914</v>
+        <v>35.19625854492188</v>
       </c>
     </row>
     <row r="408">
@@ -41984,7 +41984,7 @@
         </is>
       </c>
       <c r="B408" s="2" t="n">
-        <v>35.49343490600586</v>
+        <v>35.49343109130859</v>
       </c>
     </row>
     <row r="409">
@@ -41994,7 +41994,7 @@
         </is>
       </c>
       <c r="B409" s="2" t="n">
-        <v>36.56139755249023</v>
+        <v>36.56138610839844</v>
       </c>
     </row>
     <row r="410">
@@ -42004,7 +42004,7 @@
         </is>
       </c>
       <c r="B410" s="2" t="n">
-        <v>36.44994735717773</v>
+        <v>36.449951171875</v>
       </c>
     </row>
     <row r="411">
@@ -42014,7 +42014,7 @@
         </is>
       </c>
       <c r="B411" s="2" t="n">
-        <v>37.21145248413086</v>
+        <v>37.21144866943359</v>
       </c>
     </row>
     <row r="412">
@@ -42034,7 +42034,7 @@
         </is>
       </c>
       <c r="B413" s="2" t="n">
-        <v>37.75936508178711</v>
+        <v>37.75936126708984</v>
       </c>
     </row>
     <row r="414">
@@ -42094,7 +42094,7 @@
         </is>
       </c>
       <c r="B419" s="2" t="n">
-        <v>38.16797256469727</v>
+        <v>38.16797637939453</v>
       </c>
     </row>
     <row r="420">
@@ -42124,7 +42124,7 @@
         </is>
       </c>
       <c r="B422" s="2" t="n">
-        <v>39.05949401855469</v>
+        <v>39.05949020385742</v>
       </c>
     </row>
     <row r="423">
@@ -42134,7 +42134,7 @@
         </is>
       </c>
       <c r="B423" s="2" t="n">
-        <v>39.09663772583008</v>
+        <v>39.09663009643555</v>
       </c>
     </row>
     <row r="424">
@@ -42144,7 +42144,7 @@
         </is>
       </c>
       <c r="B424" s="2" t="n">
-        <v>39.46809768676758</v>
+        <v>39.46810150146484</v>
       </c>
     </row>
     <row r="425">
@@ -42154,7 +42154,7 @@
         </is>
       </c>
       <c r="B425" s="2" t="n">
-        <v>39.28236389160156</v>
+        <v>39.28237152099609</v>
       </c>
     </row>
     <row r="426">
@@ -42164,7 +42164,7 @@
         </is>
       </c>
       <c r="B426" s="2" t="n">
-        <v>38.49300384521484</v>
+        <v>38.49300765991211</v>
       </c>
     </row>
     <row r="427">
@@ -42174,7 +42174,7 @@
         </is>
       </c>
       <c r="B427" s="2" t="n">
-        <v>38.40942764282227</v>
+        <v>38.409423828125</v>
       </c>
     </row>
     <row r="428">
@@ -42194,7 +42194,7 @@
         </is>
       </c>
       <c r="B429" s="2" t="n">
-        <v>38.65087509155273</v>
+        <v>38.65087890625</v>
       </c>
     </row>
     <row r="430">
@@ -42214,7 +42214,7 @@
         </is>
       </c>
       <c r="B431" s="2" t="n">
-        <v>37.40647506713867</v>
+        <v>37.40647125244141</v>
       </c>
     </row>
     <row r="432">
@@ -42234,7 +42234,7 @@
         </is>
       </c>
       <c r="B433" s="2" t="n">
-        <v>37.50862884521484</v>
+        <v>37.50862121582031</v>
       </c>
     </row>
     <row r="434">
@@ -42244,7 +42244,7 @@
         </is>
       </c>
       <c r="B434" s="2" t="n">
-        <v>37.6850700378418</v>
+        <v>37.68507385253906</v>
       </c>
     </row>
     <row r="435">
@@ -42294,7 +42294,7 @@
         </is>
       </c>
       <c r="B439" s="2" t="n">
-        <v>37.25788497924805</v>
+        <v>37.25789260864258</v>
       </c>
     </row>
     <row r="440">
@@ -42304,7 +42304,7 @@
         </is>
       </c>
       <c r="B440" s="2" t="n">
-        <v>36.84927749633789</v>
+        <v>36.84927368164062</v>
       </c>
     </row>
     <row r="441">
@@ -42314,7 +42314,7 @@
         </is>
       </c>
       <c r="B441" s="2" t="n">
-        <v>36.38494491577148</v>
+        <v>36.38494873046875</v>
       </c>
     </row>
     <row r="442">
@@ -42334,7 +42334,7 @@
         </is>
       </c>
       <c r="B443" s="2" t="n">
-        <v>36.38494491577148</v>
+        <v>36.38494873046875</v>
       </c>
     </row>
     <row r="444">
@@ -42354,7 +42354,7 @@
         </is>
       </c>
       <c r="B445" s="2" t="n">
-        <v>35.75345993041992</v>
+        <v>35.75345230102539</v>
       </c>
     </row>
     <row r="446">
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="B447" s="2" t="n">
-        <v>36.26421737670898</v>
+        <v>36.26422119140625</v>
       </c>
     </row>
     <row r="448">
@@ -42394,7 +42394,7 @@
         </is>
       </c>
       <c r="B449" s="2" t="n">
-        <v>36.71926498413086</v>
+        <v>36.71926879882812</v>
       </c>
     </row>
     <row r="450">
@@ -42404,7 +42404,7 @@
         </is>
       </c>
       <c r="B450" s="2" t="n">
-        <v>36.58925628662109</v>
+        <v>36.58925247192383</v>
       </c>
     </row>
     <row r="451">
@@ -42414,7 +42414,7 @@
         </is>
       </c>
       <c r="B451" s="2" t="n">
-        <v>35.97633743286133</v>
+        <v>35.97633361816406</v>
       </c>
     </row>
     <row r="452">
@@ -42424,7 +42424,7 @@
         </is>
       </c>
       <c r="B452" s="2" t="n">
-        <v>36.12492370605469</v>
+        <v>36.12491989135742</v>
       </c>
     </row>
     <row r="453">
@@ -42434,7 +42434,7 @@
         </is>
       </c>
       <c r="B453" s="2" t="n">
-        <v>35.32627105712891</v>
+        <v>35.32627487182617</v>
       </c>
     </row>
     <row r="454">
@@ -42454,7 +42454,7 @@
         </is>
       </c>
       <c r="B455" s="2" t="n">
-        <v>35.19626235961914</v>
+        <v>35.19625854492188</v>
       </c>
     </row>
     <row r="456">
@@ -42464,7 +42464,7 @@
         </is>
       </c>
       <c r="B456" s="2" t="n">
-        <v>35.2148323059082</v>
+        <v>35.21482467651367</v>
       </c>
     </row>
     <row r="457">
@@ -42474,7 +42474,7 @@
         </is>
       </c>
       <c r="B457" s="2" t="n">
-        <v>34.61119842529297</v>
+        <v>34.61120223999023</v>
       </c>
     </row>
     <row r="458">
@@ -42494,7 +42494,7 @@
         </is>
       </c>
       <c r="B459" s="2" t="n">
-        <v>34.92694854736328</v>
+        <v>34.92694473266602</v>
       </c>
     </row>
     <row r="460">
@@ -42514,7 +42514,7 @@
         </is>
       </c>
       <c r="B461" s="2" t="n">
-        <v>35.37270736694336</v>
+        <v>35.37270355224609</v>
       </c>
     </row>
     <row r="462">
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="B462" s="2" t="n">
-        <v>35.51200866699219</v>
+        <v>35.51200103759766</v>
       </c>
     </row>
     <row r="463">
@@ -42534,7 +42534,7 @@
         </is>
       </c>
       <c r="B463" s="2" t="n">
-        <v>36.00419235229492</v>
+        <v>36.00419998168945</v>
       </c>
     </row>
     <row r="464">
@@ -42544,7 +42544,7 @@
         </is>
       </c>
       <c r="B464" s="2" t="n">
-        <v>35.91132354736328</v>
+        <v>35.91131973266602</v>
       </c>
     </row>
     <row r="465">
@@ -42574,7 +42574,7 @@
         </is>
       </c>
       <c r="B467" s="2" t="n">
-        <v>36.32922744750977</v>
+        <v>36.3292236328125</v>
       </c>
     </row>
     <row r="468">
@@ -42594,7 +42594,7 @@
         </is>
       </c>
       <c r="B469" s="2" t="n">
-        <v>36.64496612548828</v>
+        <v>36.64497375488281</v>
       </c>
     </row>
     <row r="470">
@@ -42604,7 +42604,7 @@
         </is>
       </c>
       <c r="B470" s="2" t="n">
-        <v>36.71926498413086</v>
+        <v>36.71926879882812</v>
       </c>
     </row>
     <row r="471">
@@ -42614,7 +42614,7 @@
         </is>
       </c>
       <c r="B471" s="2" t="n">
-        <v>36.71926498413086</v>
+        <v>36.71926879882812</v>
       </c>
     </row>
     <row r="472">
@@ -42634,7 +42634,7 @@
         </is>
       </c>
       <c r="B473" s="2" t="n">
-        <v>36.57996368408203</v>
+        <v>36.57995986938477</v>
       </c>
     </row>
     <row r="474">
@@ -42654,7 +42654,7 @@
         </is>
       </c>
       <c r="B475" s="2" t="n">
-        <v>36.83998489379883</v>
+        <v>36.83998870849609</v>
       </c>
     </row>
     <row r="476">
@@ -42664,7 +42664,7 @@
         </is>
       </c>
       <c r="B476" s="2" t="n">
-        <v>36.57996368408203</v>
+        <v>36.57995986938477</v>
       </c>
     </row>
     <row r="477">
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="B477" s="2" t="n">
-        <v>37.08144378662109</v>
+        <v>37.08143997192383</v>
       </c>
     </row>
     <row r="478">
@@ -42684,7 +42684,7 @@
         </is>
       </c>
       <c r="B478" s="2" t="n">
-        <v>36.88642501831055</v>
+        <v>36.88642120361328</v>
       </c>
     </row>
     <row r="479">
@@ -42714,7 +42714,7 @@
         </is>
       </c>
       <c r="B481" s="2" t="n">
-        <v>36.62639617919922</v>
+        <v>36.62639999389648</v>
       </c>
     </row>
     <row r="482">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="B482" s="2" t="n">
-        <v>36.5706787109375</v>
+        <v>36.57067489624023</v>
       </c>
     </row>
     <row r="483">
@@ -42764,7 +42764,7 @@
         </is>
       </c>
       <c r="B486" s="2" t="n">
-        <v>35.66987609863281</v>
+        <v>35.66987991333008</v>
       </c>
     </row>
     <row r="487">
@@ -42774,7 +42774,7 @@
         </is>
       </c>
       <c r="B487" s="2" t="n">
-        <v>36.15277862548828</v>
+        <v>36.15278244018555</v>
       </c>
     </row>
     <row r="488">
@@ -42784,7 +42784,7 @@
         </is>
       </c>
       <c r="B488" s="2" t="n">
-        <v>36.3385124206543</v>
+        <v>36.33852005004883</v>
       </c>
     </row>
     <row r="489">
@@ -42794,7 +42794,7 @@
         </is>
       </c>
       <c r="B489" s="2" t="n">
-        <v>36.2177848815918</v>
+        <v>36.21778106689453</v>
       </c>
     </row>
     <row r="490">
@@ -42814,7 +42814,7 @@
         </is>
       </c>
       <c r="B491" s="2" t="n">
-        <v>35.80917358398438</v>
+        <v>35.80917739868164</v>
       </c>
     </row>
     <row r="492">
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="B492" s="2" t="n">
-        <v>36.09705352783203</v>
+        <v>36.09706115722656</v>
       </c>
     </row>
     <row r="493">
@@ -42834,7 +42834,7 @@
         </is>
       </c>
       <c r="B493" s="2" t="n">
-        <v>36.57996368408203</v>
+        <v>36.57995986938477</v>
       </c>
     </row>
     <row r="494">
@@ -42844,7 +42844,7 @@
         </is>
       </c>
       <c r="B494" s="2" t="n">
-        <v>36.59854125976562</v>
+        <v>36.59853363037109</v>
       </c>
     </row>
     <row r="495">
@@ -42854,7 +42854,7 @@
         </is>
       </c>
       <c r="B495" s="2" t="n">
-        <v>36.37565994262695</v>
+        <v>36.37565612792969</v>
       </c>
     </row>
     <row r="496">
@@ -42884,7 +42884,7 @@
         </is>
       </c>
       <c r="B498" s="2" t="n">
-        <v>35.79988479614258</v>
+        <v>35.79988098144531</v>
       </c>
     </row>
     <row r="499">
@@ -42894,7 +42894,7 @@
         </is>
       </c>
       <c r="B499" s="2" t="n">
-        <v>36.4592399597168</v>
+        <v>36.45923614501953</v>
       </c>
     </row>
     <row r="500">
@@ -42914,7 +42914,7 @@
         </is>
       </c>
       <c r="B501" s="2" t="n">
-        <v>36.36637496948242</v>
+        <v>36.36637115478516</v>
       </c>
     </row>
     <row r="502">
@@ -42924,7 +42924,7 @@
         </is>
       </c>
       <c r="B502" s="2" t="n">
-        <v>36.17135620117188</v>
+        <v>36.17135238647461</v>
       </c>
     </row>
     <row r="503">
@@ -42944,7 +42944,7 @@
         </is>
       </c>
       <c r="B504" s="2" t="n">
-        <v>36.49638748168945</v>
+        <v>36.49638366699219</v>
       </c>
     </row>
     <row r="505">
@@ -42954,7 +42954,7 @@
         </is>
       </c>
       <c r="B505" s="2" t="n">
-        <v>35.92989730834961</v>
+        <v>35.92990112304688</v>
       </c>
     </row>
     <row r="506">
@@ -42984,7 +42984,7 @@
         </is>
       </c>
       <c r="B508" s="2" t="n">
-        <v>36.2177848815918</v>
+        <v>36.21778106689453</v>
       </c>
     </row>
     <row r="509">
@@ -42994,7 +42994,7 @@
         </is>
       </c>
       <c r="B509" s="2" t="n">
-        <v>35.79988479614258</v>
+        <v>35.79988098144531</v>
       </c>
     </row>
     <row r="510">
@@ -43014,7 +43014,7 @@
         </is>
       </c>
       <c r="B511" s="2" t="n">
-        <v>36.09705352783203</v>
+        <v>36.09706115722656</v>
       </c>
     </row>
     <row r="512">
@@ -43024,7 +43024,7 @@
         </is>
       </c>
       <c r="B512" s="2" t="n">
-        <v>36.71926498413086</v>
+        <v>36.71926879882812</v>
       </c>
     </row>
     <row r="513">
@@ -43034,7 +43034,7 @@
         </is>
       </c>
       <c r="B513" s="2" t="n">
-        <v>36.70997619628906</v>
+        <v>36.7099723815918</v>
       </c>
     </row>
     <row r="514">
@@ -43044,7 +43044,7 @@
         </is>
       </c>
       <c r="B514" s="2" t="n">
-        <v>37.03500747680664</v>
+        <v>37.03501129150391</v>
       </c>
     </row>
     <row r="515">
@@ -43054,7 +43054,7 @@
         </is>
       </c>
       <c r="B515" s="2" t="n">
-        <v>36.87590408325195</v>
+        <v>36.87590026855469</v>
       </c>
     </row>
     <row r="516">
@@ -43104,7 +43104,7 @@
         </is>
       </c>
       <c r="B520" s="2" t="n">
-        <v>38.03646087646484</v>
+        <v>38.03646469116211</v>
       </c>
     </row>
     <row r="521">
@@ -43124,7 +43124,7 @@
         </is>
       </c>
       <c r="B522" s="2" t="n">
-        <v>38.26108932495117</v>
+        <v>38.26108551025391</v>
       </c>
     </row>
     <row r="523">
@@ -43154,7 +43154,7 @@
         </is>
       </c>
       <c r="B525" s="2" t="n">
-        <v>37.2034797668457</v>
+        <v>37.20347595214844</v>
       </c>
     </row>
     <row r="526">
@@ -43204,7 +43204,7 @@
         </is>
       </c>
       <c r="B530" s="2" t="n">
-        <v>36.73550415039062</v>
+        <v>36.73550796508789</v>
       </c>
     </row>
     <row r="531">
@@ -43214,7 +43214,7 @@
         </is>
       </c>
       <c r="B531" s="2" t="n">
-        <v>37.0256462097168</v>
+        <v>37.02565383911133</v>
       </c>
     </row>
     <row r="532">
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="B533" s="2" t="n">
-        <v>37.21283340454102</v>
+        <v>37.21283721923828</v>
       </c>
     </row>
     <row r="534">
@@ -43244,7 +43244,7 @@
         </is>
       </c>
       <c r="B534" s="2" t="n">
-        <v>36.45473098754883</v>
+        <v>36.45472717285156</v>
       </c>
     </row>
     <row r="535">
@@ -43254,7 +43254,7 @@
         </is>
       </c>
       <c r="B535" s="2" t="n">
-        <v>36.86653518676758</v>
+        <v>36.86653900146484</v>
       </c>
     </row>
     <row r="536">
@@ -43264,7 +43264,7 @@
         </is>
       </c>
       <c r="B536" s="2" t="n">
-        <v>36.89461135864258</v>
+        <v>36.89461517333984</v>
       </c>
     </row>
     <row r="537">
@@ -43284,7 +43284,7 @@
         </is>
       </c>
       <c r="B538" s="2" t="n">
-        <v>38.10197830200195</v>
+        <v>38.10197067260742</v>
       </c>
     </row>
     <row r="539">
@@ -43294,7 +43294,7 @@
         </is>
       </c>
       <c r="B539" s="2" t="n">
-        <v>38.5980224609375</v>
+        <v>38.59801864624023</v>
       </c>
     </row>
     <row r="540">
@@ -43304,7 +43304,7 @@
         </is>
       </c>
       <c r="B540" s="2" t="n">
-        <v>38.38275909423828</v>
+        <v>38.38275527954102</v>
       </c>
     </row>
     <row r="541">
@@ -43324,7 +43324,7 @@
         </is>
       </c>
       <c r="B542" s="2" t="n">
-        <v>38.14876937866211</v>
+        <v>38.14877319335938</v>
       </c>
     </row>
     <row r="543">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="B543" s="2" t="n">
-        <v>38.07390213012695</v>
+        <v>38.07389831542969</v>
       </c>
     </row>
     <row r="544">
@@ -43364,7 +43364,7 @@
         </is>
       </c>
       <c r="B546" s="2" t="n">
-        <v>38.25172424316406</v>
+        <v>38.25172805786133</v>
       </c>
     </row>
     <row r="547">
@@ -43374,7 +43374,7 @@
         </is>
       </c>
       <c r="B547" s="2" t="n">
-        <v>38.56994247436523</v>
+        <v>38.5699462890625</v>
       </c>
     </row>
     <row r="548">
@@ -43384,7 +43384,7 @@
         </is>
       </c>
       <c r="B548" s="2" t="n">
-        <v>38.79456329345703</v>
+        <v>38.79457092285156</v>
       </c>
     </row>
     <row r="549">
@@ -43394,7 +43394,7 @@
         </is>
       </c>
       <c r="B549" s="2" t="n">
-        <v>38.31724166870117</v>
+        <v>38.31723785400391</v>
       </c>
     </row>
     <row r="550">
@@ -43444,7 +43444,7 @@
         </is>
       </c>
       <c r="B554" s="2" t="n">
-        <v>37.98966598510742</v>
+        <v>37.98965835571289</v>
       </c>
     </row>
     <row r="555">
@@ -43464,7 +43464,7 @@
         </is>
       </c>
       <c r="B556" s="2" t="n">
-        <v>37.88671493530273</v>
+        <v>37.8867073059082</v>
       </c>
     </row>
     <row r="557">
@@ -43484,7 +43484,7 @@
         </is>
       </c>
       <c r="B558" s="2" t="n">
-        <v>37.52169418334961</v>
+        <v>37.52169799804688</v>
       </c>
     </row>
     <row r="559">
@@ -43494,7 +43494,7 @@
         </is>
       </c>
       <c r="B559" s="2" t="n">
-        <v>37.57785034179688</v>
+        <v>37.57785415649414</v>
       </c>
     </row>
     <row r="560">
@@ -43504,7 +43504,7 @@
         </is>
       </c>
       <c r="B560" s="2" t="n">
-        <v>37.0256462097168</v>
+        <v>37.02565383911133</v>
       </c>
     </row>
     <row r="561">
@@ -43514,7 +43514,7 @@
         </is>
       </c>
       <c r="B561" s="2" t="n">
-        <v>36.84782409667969</v>
+        <v>36.84782028198242</v>
       </c>
     </row>
     <row r="562">
@@ -43524,7 +43524,7 @@
         </is>
       </c>
       <c r="B562" s="2" t="n">
-        <v>36.4266471862793</v>
+        <v>36.42665100097656</v>
       </c>
     </row>
     <row r="563">
@@ -43534,7 +43534,7 @@
         </is>
       </c>
       <c r="B563" s="2" t="n">
-        <v>36.09907150268555</v>
+        <v>36.09906768798828</v>
       </c>
     </row>
     <row r="564">
@@ -43554,7 +43554,7 @@
         </is>
       </c>
       <c r="B565" s="2" t="n">
-        <v>35.93996047973633</v>
+        <v>35.93996429443359</v>
       </c>
     </row>
     <row r="566">
@@ -43564,7 +43564,7 @@
         </is>
       </c>
       <c r="B566" s="2" t="n">
-        <v>36.02419662475586</v>
+        <v>36.02420043945312</v>
       </c>
     </row>
     <row r="567">
@@ -43584,7 +43584,7 @@
         </is>
       </c>
       <c r="B568" s="2" t="n">
-        <v>36.52024459838867</v>
+        <v>36.52024841308594</v>
       </c>
     </row>
     <row r="569">
@@ -43594,7 +43594,7 @@
         </is>
       </c>
       <c r="B569" s="2" t="n">
-        <v>36.37984848022461</v>
+        <v>36.37985229492188</v>
       </c>
     </row>
     <row r="570">
@@ -43604,7 +43604,7 @@
         </is>
       </c>
       <c r="B570" s="2" t="n">
-        <v>36.41728973388672</v>
+        <v>36.41729354858398</v>
       </c>
     </row>
     <row r="571">
@@ -43614,7 +43614,7 @@
         </is>
       </c>
       <c r="B571" s="2" t="n">
-        <v>36.77294921875</v>
+        <v>36.77294540405273</v>
       </c>
     </row>
     <row r="572">
@@ -43654,7 +43654,7 @@
         </is>
       </c>
       <c r="B575" s="2" t="n">
-        <v>37.09117126464844</v>
+        <v>37.09116363525391</v>
       </c>
     </row>
     <row r="576">
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="B582" s="2" t="n">
-        <v>36.52024459838867</v>
+        <v>36.52024841308594</v>
       </c>
     </row>
     <row r="583">
@@ -43784,7 +43784,7 @@
         </is>
       </c>
       <c r="B588" s="2" t="n">
-        <v>35.58430862426758</v>
+        <v>35.58430480957031</v>
       </c>
     </row>
     <row r="589">
@@ -43794,7 +43794,7 @@
         </is>
       </c>
       <c r="B589" s="2" t="n">
-        <v>36.0054817199707</v>
+        <v>36.00547790527344</v>
       </c>
     </row>
     <row r="590">
@@ -43804,7 +43804,7 @@
         </is>
       </c>
       <c r="B590" s="2" t="n">
-        <v>35.84637069702148</v>
+        <v>35.84636688232422</v>
       </c>
     </row>
     <row r="591">
@@ -43814,7 +43814,7 @@
         </is>
       </c>
       <c r="B591" s="2" t="n">
-        <v>35.34096527099609</v>
+        <v>35.34096145629883</v>
       </c>
     </row>
     <row r="592">
@@ -43824,7 +43824,7 @@
         </is>
       </c>
       <c r="B592" s="2" t="n">
-        <v>35.39711761474609</v>
+        <v>35.39711380004883</v>
       </c>
     </row>
     <row r="593">
@@ -43844,7 +43844,7 @@
         </is>
       </c>
       <c r="B594" s="2" t="n">
-        <v>35.51879501342773</v>
+        <v>35.51879119873047</v>
       </c>
     </row>
     <row r="595">
@@ -43854,7 +43854,7 @@
         </is>
       </c>
       <c r="B595" s="2" t="n">
-        <v>35.34096527099609</v>
+        <v>35.34096145629883</v>
       </c>
     </row>
     <row r="596">
@@ -43864,7 +43864,7 @@
         </is>
       </c>
       <c r="B596" s="2" t="n">
-        <v>34.87299728393555</v>
+        <v>34.87298965454102</v>
       </c>
     </row>
     <row r="597">
@@ -43894,7 +43894,7 @@
         </is>
       </c>
       <c r="B599" s="2" t="n">
-        <v>35.4064826965332</v>
+        <v>35.40647888183594</v>
       </c>
     </row>
     <row r="600">
@@ -43924,7 +43924,7 @@
         </is>
       </c>
       <c r="B602" s="2" t="n">
-        <v>35.96804428100586</v>
+        <v>35.96804046630859</v>
       </c>
     </row>
     <row r="603">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="B604" s="2" t="n">
-        <v>35.43455505371094</v>
+        <v>35.4345588684082</v>
       </c>
     </row>
     <row r="605">
@@ -43954,7 +43954,7 @@
         </is>
       </c>
       <c r="B605" s="2" t="n">
-        <v>35.69661712646484</v>
+        <v>35.69662094116211</v>
       </c>
     </row>
     <row r="606">
@@ -43994,7 +43994,7 @@
         </is>
       </c>
       <c r="B609" s="2" t="n">
-        <v>34.43310928344727</v>
+        <v>34.43310546875</v>
       </c>
     </row>
     <row r="610">
@@ -44004,7 +44004,7 @@
         </is>
       </c>
       <c r="B610" s="2" t="n">
-        <v>34.40502548217773</v>
+        <v>34.405029296875</v>
       </c>
     </row>
     <row r="611">
@@ -44014,7 +44014,7 @@
         </is>
       </c>
       <c r="B611" s="2" t="n">
-        <v>34.84491348266602</v>
+        <v>34.84491729736328</v>
       </c>
     </row>
     <row r="612">
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="B619" s="2" t="n">
-        <v>35.99612045288086</v>
+        <v>35.99611663818359</v>
       </c>
     </row>
     <row r="620">
@@ -44144,7 +44144,7 @@
         </is>
       </c>
       <c r="B624" s="2" t="n">
-        <v>35.89316177368164</v>
+        <v>35.89316558837891</v>
       </c>
     </row>
     <row r="625">
@@ -44164,7 +44164,7 @@
         </is>
       </c>
       <c r="B626" s="2" t="n">
-        <v>36.83845901489258</v>
+        <v>36.83846282958984</v>
       </c>
     </row>
     <row r="627">
@@ -44194,7 +44194,7 @@
         </is>
       </c>
       <c r="B629" s="2" t="n">
-        <v>36.83845901489258</v>
+        <v>36.83846282958984</v>
       </c>
     </row>
     <row r="630">
@@ -44214,7 +44214,7 @@
         </is>
       </c>
       <c r="B631" s="2" t="n">
-        <v>37.06307983398438</v>
+        <v>37.06308746337891</v>
       </c>
     </row>
     <row r="632">
@@ -44224,7 +44224,7 @@
         </is>
       </c>
       <c r="B632" s="2" t="n">
-        <v>36.98821640014648</v>
+        <v>36.98821258544922</v>
       </c>
     </row>
     <row r="633">
@@ -44244,7 +44244,7 @@
         </is>
       </c>
       <c r="B634" s="2" t="n">
-        <v>36.85718154907227</v>
+        <v>36.857177734375</v>
       </c>
     </row>
     <row r="635">
@@ -44254,7 +44254,7 @@
         </is>
       </c>
       <c r="B635" s="2" t="n">
-        <v>37.16603469848633</v>
+        <v>37.16603851318359</v>
       </c>
     </row>
     <row r="636">
@@ -44264,7 +44264,7 @@
         </is>
       </c>
       <c r="B636" s="2" t="n">
-        <v>36.95077514648438</v>
+        <v>36.95077896118164</v>
       </c>
     </row>
     <row r="637">
@@ -44274,7 +44274,7 @@
         </is>
       </c>
       <c r="B637" s="2" t="n">
-        <v>37.0256462097168</v>
+        <v>37.02565383911133</v>
       </c>
     </row>
     <row r="638">
@@ -44334,7 +44334,7 @@
         </is>
       </c>
       <c r="B643" s="2" t="n">
-        <v>36.51088333129883</v>
+        <v>36.51088714599609</v>
       </c>
     </row>
     <row r="644">
@@ -44354,7 +44354,7 @@
         </is>
       </c>
       <c r="B645" s="2" t="n">
-        <v>36.73550415039062</v>
+        <v>36.73550796508789</v>
       </c>
     </row>
     <row r="646">
@@ -44374,7 +44374,7 @@
         </is>
       </c>
       <c r="B647" s="2" t="n">
-        <v>37.64336776733398</v>
+        <v>37.64337158203125</v>
       </c>
     </row>
     <row r="648">
@@ -44394,7 +44394,7 @@
         </is>
       </c>
       <c r="B649" s="2" t="n">
-        <v>37.4000244140625</v>
+        <v>37.40002059936523</v>
       </c>
     </row>
     <row r="650">
@@ -44434,7 +44434,7 @@
         </is>
       </c>
       <c r="B653" s="2" t="n">
-        <v>37.55421829223633</v>
+        <v>37.55421447753906</v>
       </c>
     </row>
     <row r="654">
@@ -44454,7 +44454,7 @@
         </is>
       </c>
       <c r="B655" s="2" t="n">
-        <v>38.06917953491211</v>
+        <v>38.06917572021484</v>
       </c>
     </row>
     <row r="656">
@@ -44464,7 +44464,7 @@
         </is>
       </c>
       <c r="B656" s="2" t="n">
-        <v>38.36480712890625</v>
+        <v>38.36481094360352</v>
       </c>
     </row>
     <row r="657">
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="B657" s="2" t="n">
-        <v>38.34573745727539</v>
+        <v>38.34573364257812</v>
       </c>
     </row>
     <row r="658">
@@ -44524,7 +44524,7 @@
         </is>
       </c>
       <c r="B662" s="2" t="n">
-        <v>37.71633148193359</v>
+        <v>37.71633911132812</v>
       </c>
     </row>
     <row r="663">
@@ -44634,7 +44634,7 @@
         </is>
       </c>
       <c r="B673" s="2" t="n">
-        <v>37.01064300537109</v>
+        <v>37.01064682006836</v>
       </c>
     </row>
     <row r="674">
@@ -44654,7 +44654,7 @@
         </is>
       </c>
       <c r="B675" s="2" t="n">
-        <v>37.08692932128906</v>
+        <v>37.08693313598633</v>
       </c>
     </row>
     <row r="676">
@@ -44674,7 +44674,7 @@
         </is>
       </c>
       <c r="B677" s="2" t="n">
-        <v>36.81037902832031</v>
+        <v>36.81037521362305</v>
       </c>
     </row>
     <row r="678">
@@ -44694,7 +44694,7 @@
         </is>
       </c>
       <c r="B679" s="2" t="n">
-        <v>36.96295928955078</v>
+        <v>36.96296310424805</v>
       </c>
     </row>
     <row r="680">
@@ -44704,7 +44704,7 @@
         </is>
       </c>
       <c r="B680" s="2" t="n">
-        <v>36.85806274414062</v>
+        <v>36.85805892944336</v>
       </c>
     </row>
     <row r="681">
@@ -44714,7 +44714,7 @@
         </is>
       </c>
       <c r="B681" s="2" t="n">
-        <v>36.90573883056641</v>
+        <v>36.90574264526367</v>
       </c>
     </row>
     <row r="682">
@@ -44824,7 +44824,7 @@
         </is>
       </c>
       <c r="B692" s="2" t="n">
-        <v>38.34573745727539</v>
+        <v>38.34573364257812</v>
       </c>
     </row>
     <row r="693">
@@ -44854,7 +44854,7 @@
         </is>
       </c>
       <c r="B695" s="2" t="n">
-        <v>38.54599380493164</v>
+        <v>38.54599761962891</v>
       </c>
     </row>
     <row r="696">
@@ -44894,7 +44894,7 @@
         </is>
       </c>
       <c r="B699" s="2" t="n">
-        <v>38.60321807861328</v>
+        <v>38.60321426391602</v>
       </c>
     </row>
     <row r="700">
@@ -44904,7 +44904,7 @@
         </is>
       </c>
       <c r="B700" s="2" t="n">
-        <v>38.51738357543945</v>
+        <v>38.51738739013672</v>
       </c>
     </row>
     <row r="701">
@@ -44914,7 +44914,7 @@
         </is>
       </c>
       <c r="B701" s="2" t="n">
-        <v>38.17407989501953</v>
+        <v>38.17407608032227</v>
       </c>
     </row>
     <row r="702">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="B702" s="2" t="n">
-        <v>38.72718811035156</v>
+        <v>38.7271842956543</v>
       </c>
     </row>
     <row r="703">
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="B703" s="2" t="n">
-        <v>38.96559906005859</v>
+        <v>38.96560287475586</v>
       </c>
     </row>
     <row r="704">
@@ -44944,7 +44944,7 @@
         </is>
       </c>
       <c r="B704" s="2" t="n">
-        <v>38.92745590209961</v>
+        <v>38.92745208740234</v>
       </c>
     </row>
     <row r="705">
@@ -44964,7 +44964,7 @@
         </is>
       </c>
       <c r="B706" s="2" t="n">
-        <v>39.44241714477539</v>
+        <v>39.44241333007812</v>
       </c>
     </row>
     <row r="707">
@@ -44974,7 +44974,7 @@
         </is>
       </c>
       <c r="B707" s="2" t="n">
-        <v>39.31844711303711</v>
+        <v>39.31844329833984</v>
       </c>
     </row>
     <row r="708">
@@ -44984,7 +44984,7 @@
         </is>
       </c>
       <c r="B708" s="2" t="n">
-        <v>39.11817932128906</v>
+        <v>39.11818313598633</v>
       </c>
     </row>
     <row r="709">
@@ -44994,7 +44994,7 @@
         </is>
       </c>
       <c r="B709" s="2" t="n">
-        <v>38.87976837158203</v>
+        <v>38.8797721862793</v>
       </c>
     </row>
     <row r="710">
@@ -45004,7 +45004,7 @@
         </is>
       </c>
       <c r="B710" s="2" t="n">
-        <v>38.9465217590332</v>
+        <v>38.94652557373047</v>
       </c>
     </row>
     <row r="711">
@@ -45034,7 +45034,7 @@
         </is>
       </c>
       <c r="B713" s="2" t="n">
-        <v>39.24215698242188</v>
+        <v>39.24215316772461</v>
       </c>
     </row>
     <row r="714">
@@ -45044,7 +45044,7 @@
         </is>
       </c>
       <c r="B714" s="2" t="n">
-        <v>38.96559906005859</v>
+        <v>38.96560287475586</v>
       </c>
     </row>
     <row r="715">
@@ -45064,7 +45064,7 @@
         </is>
       </c>
       <c r="B716" s="2" t="n">
-        <v>38.96559906005859</v>
+        <v>38.96560287475586</v>
       </c>
     </row>
     <row r="717">
@@ -45094,7 +45094,7 @@
         </is>
       </c>
       <c r="B719" s="2" t="n">
-        <v>39.24215698242188</v>
+        <v>39.24215316772461</v>
       </c>
     </row>
     <row r="720">
@@ -45144,7 +45144,7 @@
         </is>
       </c>
       <c r="B724" s="2" t="n">
-        <v>39.59499740600586</v>
+        <v>39.59500122070312</v>
       </c>
     </row>
     <row r="725">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="B726" s="2" t="n">
-        <v>39.31844711303711</v>
+        <v>39.31844329833984</v>
       </c>
     </row>
     <row r="727">
@@ -45184,7 +45184,7 @@
         </is>
       </c>
       <c r="B728" s="2" t="n">
-        <v>38.65089416503906</v>
+        <v>38.65089797973633</v>
       </c>
     </row>
     <row r="729">
@@ -45264,7 +45264,7 @@
         </is>
       </c>
       <c r="B736" s="2" t="n">
-        <v>38.72718811035156</v>
+        <v>38.7271842956543</v>
       </c>
     </row>
     <row r="737">
@@ -45274,7 +45274,7 @@
         </is>
       </c>
       <c r="B737" s="2" t="n">
-        <v>38.81301879882812</v>
+        <v>38.81301498413086</v>
       </c>
     </row>
     <row r="738">
@@ -45284,7 +45284,7 @@
         </is>
       </c>
       <c r="B738" s="2" t="n">
-        <v>39.26122665405273</v>
+        <v>39.26122283935547</v>
       </c>
     </row>
     <row r="739">
@@ -45304,7 +45304,7 @@
         </is>
       </c>
       <c r="B740" s="2" t="n">
-        <v>39.08956909179688</v>
+        <v>39.08957290649414</v>
       </c>
     </row>
     <row r="741">
@@ -45324,7 +45324,7 @@
         </is>
       </c>
       <c r="B742" s="2" t="n">
-        <v>40.13857650756836</v>
+        <v>40.13856887817383</v>
       </c>
     </row>
     <row r="743">
@@ -45344,7 +45344,7 @@
         </is>
       </c>
       <c r="B744" s="2" t="n">
-        <v>40.53910064697266</v>
+        <v>40.53909683227539</v>
       </c>
     </row>
     <row r="745">
@@ -45354,7 +45354,7 @@
         </is>
       </c>
       <c r="B745" s="2" t="n">
-        <v>40.31022262573242</v>
+        <v>40.31022644042969</v>
       </c>
     </row>
     <row r="746">
@@ -45384,7 +45384,7 @@
         </is>
       </c>
       <c r="B748" s="2" t="n">
-        <v>40.52956390380859</v>
+        <v>40.52956008911133</v>
       </c>
     </row>
     <row r="749">
@@ -45404,7 +45404,7 @@
         </is>
       </c>
       <c r="B750" s="2" t="n">
-        <v>41.0540657043457</v>
+        <v>41.05406188964844</v>
       </c>
     </row>
     <row r="751">
@@ -45414,7 +45414,7 @@
         </is>
       </c>
       <c r="B751" s="2" t="n">
-        <v>41.49273681640625</v>
+        <v>41.49273300170898</v>
       </c>
     </row>
     <row r="752">
@@ -45444,7 +45444,7 @@
         </is>
       </c>
       <c r="B754" s="2" t="n">
-        <v>41.60717010498047</v>
+        <v>41.60717391967773</v>
       </c>
     </row>
     <row r="755">
@@ -45454,7 +45454,7 @@
         </is>
       </c>
       <c r="B755" s="2" t="n">
-        <v>41.34969329833984</v>
+        <v>41.34968948364258</v>
       </c>
     </row>
     <row r="756">
@@ -45484,7 +45484,7 @@
         </is>
       </c>
       <c r="B758" s="2" t="n">
-        <v>41.02545166015625</v>
+        <v>41.02545547485352</v>
       </c>
     </row>
     <row r="759">
@@ -45504,7 +45504,7 @@
         </is>
       </c>
       <c r="B760" s="2" t="n">
-        <v>40.35791015625</v>
+        <v>40.35790634155273</v>
       </c>
     </row>
     <row r="761">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="B763" s="2" t="n">
-        <v>40.27207565307617</v>
+        <v>40.27207946777344</v>
       </c>
     </row>
     <row r="764">
@@ -45584,7 +45584,7 @@
         </is>
       </c>
       <c r="B768" s="2" t="n">
-        <v>40.32929611206055</v>
+        <v>40.32929992675781</v>
       </c>
     </row>
     <row r="769">
@@ -45624,7 +45624,7 @@
         </is>
       </c>
       <c r="B772" s="2" t="n">
-        <v>40.55014419555664</v>
+        <v>40.55014801025391</v>
       </c>
     </row>
     <row r="773">
@@ -45644,7 +45644,7 @@
         </is>
       </c>
       <c r="B774" s="2" t="n">
-        <v>41.18389511108398</v>
+        <v>41.18389892578125</v>
       </c>
     </row>
     <row r="775">
@@ -45704,7 +45704,7 @@
         </is>
       </c>
       <c r="B780" s="2" t="n">
-        <v>40.81901168823242</v>
+        <v>40.81900787353516</v>
       </c>
     </row>
     <row r="781">
@@ -45714,7 +45714,7 @@
         </is>
       </c>
       <c r="B781" s="2" t="n">
-        <v>40.89583206176758</v>
+        <v>40.89582824707031</v>
       </c>
     </row>
     <row r="782">
@@ -45744,7 +45744,7 @@
         </is>
       </c>
       <c r="B784" s="2" t="n">
-        <v>41.72162246704102</v>
+        <v>41.72161865234375</v>
       </c>
     </row>
     <row r="785">
@@ -45764,7 +45764,7 @@
         </is>
       </c>
       <c r="B786" s="2" t="n">
-        <v>41.90406036376953</v>
+        <v>41.9040641784668</v>
       </c>
     </row>
     <row r="787">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="B787" s="2" t="n">
-        <v>42.076904296875</v>
+        <v>42.07690048217773</v>
       </c>
     </row>
     <row r="788">
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="B792" s="2" t="n">
-        <v>42.52820587158203</v>
+        <v>42.5282096862793</v>
       </c>
     </row>
     <row r="793">
@@ -45854,7 +45854,7 @@
         </is>
       </c>
       <c r="B795" s="2" t="n">
-        <v>41.03986358642578</v>
+        <v>41.03985977172852</v>
       </c>
     </row>
     <row r="796">
@@ -45864,7 +45864,7 @@
         </is>
       </c>
       <c r="B796" s="2" t="n">
-        <v>41.38553619384766</v>
+        <v>41.38554382324219</v>
       </c>
     </row>
     <row r="797">
@@ -45884,7 +45884,7 @@
         </is>
       </c>
       <c r="B798" s="2" t="n">
-        <v>40.42531967163086</v>
+        <v>40.42531585693359</v>
       </c>
     </row>
     <row r="799">
@@ -45894,7 +45894,7 @@
         </is>
       </c>
       <c r="B799" s="2" t="n">
-        <v>40.26208114624023</v>
+        <v>40.2620849609375</v>
       </c>
     </row>
     <row r="800">
@@ -45964,7 +45964,7 @@
         </is>
       </c>
       <c r="B806" s="2" t="n">
-        <v>38.8121452331543</v>
+        <v>38.81214904785156</v>
       </c>
     </row>
     <row r="807">
@@ -46044,7 +46044,7 @@
         </is>
       </c>
       <c r="B814" s="2" t="n">
-        <v>41.20309829711914</v>
+        <v>41.20310211181641</v>
       </c>
     </row>
     <row r="815">
@@ -46054,7 +46054,7 @@
         </is>
       </c>
       <c r="B815" s="2" t="n">
-        <v>41.68321228027344</v>
+        <v>41.68320846557617</v>
       </c>
     </row>
     <row r="816">
@@ -46064,7 +46064,7 @@
         </is>
       </c>
       <c r="B816" s="2" t="n">
-        <v>42.08650588989258</v>
+        <v>42.08650207519531</v>
       </c>
     </row>
     <row r="817">
@@ -46074,7 +46074,7 @@
         </is>
       </c>
       <c r="B817" s="2" t="n">
-        <v>41.76003265380859</v>
+        <v>41.76002883911133</v>
       </c>
     </row>
     <row r="818">
@@ -46084,7 +46084,7 @@
         </is>
       </c>
       <c r="B818" s="2" t="n">
-        <v>41.92326354980469</v>
+        <v>41.92326736450195</v>
       </c>
     </row>
     <row r="819">
@@ -46094,7 +46094,7 @@
         </is>
       </c>
       <c r="B819" s="2" t="n">
-        <v>41.40474319458008</v>
+        <v>41.40474700927734</v>
       </c>
     </row>
     <row r="820">
@@ -46104,7 +46104,7 @@
         </is>
       </c>
       <c r="B820" s="2" t="n">
-        <v>42.09610748291016</v>
+        <v>42.09610366821289</v>
       </c>
     </row>
     <row r="821">
@@ -46134,7 +46134,7 @@
         </is>
       </c>
       <c r="B823" s="2" t="n">
-        <v>41.53917694091797</v>
+        <v>41.5391731262207</v>
       </c>
     </row>
     <row r="824">
@@ -46154,7 +46154,7 @@
         </is>
       </c>
       <c r="B825" s="2" t="n">
-        <v>41.64480209350586</v>
+        <v>41.64479827880859</v>
       </c>
     </row>
     <row r="826">
@@ -46164,7 +46164,7 @@
         </is>
       </c>
       <c r="B826" s="2" t="n">
-        <v>40.81901168823242</v>
+        <v>40.81900787353516</v>
       </c>
     </row>
     <row r="827">
@@ -46234,7 +46234,7 @@
         </is>
       </c>
       <c r="B833" s="2" t="n">
-        <v>40.93424224853516</v>
+        <v>40.93423843383789</v>
       </c>
     </row>
     <row r="834">
@@ -46244,7 +46244,7 @@
         </is>
       </c>
       <c r="B834" s="2" t="n">
-        <v>41.12628173828125</v>
+        <v>41.12628555297852</v>
       </c>
     </row>
     <row r="835">
@@ -46264,7 +46264,7 @@
         </is>
       </c>
       <c r="B836" s="2" t="n">
-        <v>41.30872344970703</v>
+        <v>41.3087272644043</v>
       </c>
     </row>
     <row r="837">
@@ -46284,7 +46284,7 @@
         </is>
       </c>
       <c r="B838" s="2" t="n">
-        <v>42.03849411010742</v>
+        <v>42.03849029541016</v>
       </c>
     </row>
     <row r="839">
@@ -46294,7 +46294,7 @@
         </is>
       </c>
       <c r="B839" s="2" t="n">
-        <v>41.95206832885742</v>
+        <v>41.95207214355469</v>
       </c>
     </row>
     <row r="840">
@@ -46314,7 +46314,7 @@
         </is>
       </c>
       <c r="B841" s="2" t="n">
-        <v>43.71887588500977</v>
+        <v>43.71887969970703</v>
       </c>
     </row>
     <row r="842">
@@ -46324,7 +46324,7 @@
         </is>
       </c>
       <c r="B842" s="2" t="n">
-        <v>43.25796890258789</v>
+        <v>43.25797271728516</v>
       </c>
     </row>
     <row r="843">
@@ -46334,7 +46334,7 @@
         </is>
       </c>
       <c r="B843" s="2" t="n">
-        <v>44.84233474731445</v>
+        <v>44.84233856201172</v>
       </c>
     </row>
     <row r="844">
@@ -46344,7 +46344,7 @@
         </is>
       </c>
       <c r="B844" s="2" t="n">
-        <v>44.75592041015625</v>
+        <v>44.75591659545898</v>
       </c>
     </row>
     <row r="845">
@@ -46394,7 +46394,7 @@
         </is>
       </c>
       <c r="B849" s="2" t="n">
-        <v>45.10159683227539</v>
+        <v>45.10160064697266</v>
       </c>
     </row>
     <row r="850">
@@ -46404,7 +46404,7 @@
         </is>
       </c>
       <c r="B850" s="2" t="n">
-        <v>45.4760856628418</v>
+        <v>45.47608184814453</v>
       </c>
     </row>
     <row r="851">
@@ -46434,7 +46434,7 @@
         </is>
       </c>
       <c r="B853" s="2" t="n">
-        <v>44.1989860534668</v>
+        <v>44.19898986816406</v>
       </c>
     </row>
     <row r="854">
@@ -46444,7 +46444,7 @@
         </is>
       </c>
       <c r="B854" s="2" t="n">
-        <v>44.51586151123047</v>
+        <v>44.51586532592773</v>
       </c>
     </row>
     <row r="855">
@@ -46474,7 +46474,7 @@
         </is>
       </c>
       <c r="B857" s="2" t="n">
-        <v>43.72848129272461</v>
+        <v>43.72848510742188</v>
       </c>
     </row>
     <row r="858">
@@ -46484,7 +46484,7 @@
         </is>
       </c>
       <c r="B858" s="2" t="n">
-        <v>43.66127014160156</v>
+        <v>43.6612663269043</v>
       </c>
     </row>
     <row r="859">
@@ -46494,7 +46494,7 @@
         </is>
       </c>
       <c r="B859" s="2" t="n">
-        <v>44.09336090087891</v>
+        <v>44.09336471557617</v>
       </c>
     </row>
     <row r="860">
@@ -46514,7 +46514,7 @@
         </is>
       </c>
       <c r="B861" s="2" t="n">
-        <v>43.69007110595703</v>
+        <v>43.6900749206543</v>
       </c>
     </row>
     <row r="862">
@@ -46554,7 +46554,7 @@
         </is>
       </c>
       <c r="B865" s="2" t="n">
-        <v>43.51723480224609</v>
+        <v>43.51723098754883</v>
       </c>
     </row>
     <row r="866">
@@ -46564,7 +46564,7 @@
         </is>
       </c>
       <c r="B866" s="2" t="n">
-        <v>43.38280487060547</v>
+        <v>43.3828010559082</v>
       </c>
     </row>
     <row r="867">
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="B867" s="2" t="n">
-        <v>42.96030807495117</v>
+        <v>42.96030426025391</v>
       </c>
     </row>
     <row r="868">
@@ -46584,7 +46584,7 @@
         </is>
       </c>
       <c r="B868" s="2" t="n">
-        <v>42.68183898925781</v>
+        <v>42.68184280395508</v>
       </c>
     </row>
     <row r="869">
@@ -46604,7 +46604,7 @@
         </is>
       </c>
       <c r="B870" s="2" t="n">
-        <v>42.96030807495117</v>
+        <v>42.96030426025391</v>
       </c>
     </row>
     <row r="871">
@@ -46624,7 +46624,7 @@
         </is>
       </c>
       <c r="B872" s="2" t="n">
-        <v>43.00831604003906</v>
+        <v>43.0083122253418</v>
       </c>
     </row>
     <row r="873">
@@ -46634,7 +46634,7 @@
         </is>
       </c>
       <c r="B873" s="2" t="n">
-        <v>43.95893478393555</v>
+        <v>43.95893096923828</v>
       </c>
     </row>
     <row r="874">
@@ -46704,7 +46704,7 @@
         </is>
       </c>
       <c r="B880" s="2" t="n">
-        <v>41.71201705932617</v>
+        <v>41.71201324462891</v>
       </c>
     </row>
     <row r="881">
@@ -46714,7 +46714,7 @@
         </is>
       </c>
       <c r="B881" s="2" t="n">
-        <v>41.68321228027344</v>
+        <v>41.68320846557617</v>
       </c>
     </row>
     <row r="882">
@@ -46754,7 +46754,7 @@
         </is>
       </c>
       <c r="B885" s="2" t="n">
-        <v>41.58718872070312</v>
+        <v>41.58718490600586</v>
       </c>
     </row>
     <row r="886">
@@ -46784,7 +46784,7 @@
         </is>
       </c>
       <c r="B888" s="2" t="n">
-        <v>41.53917694091797</v>
+        <v>41.5391731262207</v>
       </c>
     </row>
     <row r="889">
@@ -46804,7 +46804,7 @@
         </is>
       </c>
       <c r="B890" s="2" t="n">
-        <v>41.78883743286133</v>
+        <v>41.78883361816406</v>
       </c>
     </row>
     <row r="891">
@@ -46834,7 +46834,7 @@
         </is>
       </c>
       <c r="B893" s="2" t="n">
-        <v>42.10570526123047</v>
+        <v>42.10570907592773</v>
       </c>
     </row>
     <row r="894">
@@ -46864,7 +46864,7 @@
         </is>
       </c>
       <c r="B896" s="2" t="n">
-        <v>42.45138549804688</v>
+        <v>42.45138931274414</v>
       </c>
     </row>
     <row r="897">
@@ -46944,7 +46944,7 @@
         </is>
       </c>
       <c r="B904" s="2" t="n">
-        <v>41.50812911987305</v>
+        <v>41.50812530517578</v>
       </c>
     </row>
     <row r="905">
@@ -47014,7 +47014,7 @@
         </is>
       </c>
       <c r="B911" s="2" t="n">
-        <v>41.15661239624023</v>
+        <v>41.1566162109375</v>
       </c>
     </row>
     <row r="912">
@@ -47044,7 +47044,7 @@
         </is>
       </c>
       <c r="B914" s="2" t="n">
-        <v>40.81485748291016</v>
+        <v>40.81486129760742</v>
       </c>
     </row>
     <row r="915">
@@ -47064,7 +47064,7 @@
         </is>
       </c>
       <c r="B916" s="2" t="n">
-        <v>39.84819412231445</v>
+        <v>39.84819793701172</v>
       </c>
     </row>
     <row r="917">
@@ -47074,7 +47074,7 @@
         </is>
       </c>
       <c r="B917" s="2" t="n">
-        <v>40.29735565185547</v>
+        <v>40.2973518371582</v>
       </c>
     </row>
     <row r="918">
@@ -47124,7 +47124,7 @@
         </is>
       </c>
       <c r="B922" s="2" t="n">
-        <v>41.56671524047852</v>
+        <v>41.56671142578125</v>
       </c>
     </row>
     <row r="923">
@@ -47134,7 +47134,7 @@
         </is>
       </c>
       <c r="B923" s="2" t="n">
-        <v>41.66435623168945</v>
+        <v>41.66435241699219</v>
       </c>
     </row>
     <row r="924">
@@ -47164,7 +47164,7 @@
         </is>
       </c>
       <c r="B926" s="2" t="n">
-        <v>41.47883224487305</v>
+        <v>41.47883605957031</v>
       </c>
     </row>
     <row r="927">
@@ -47194,7 +47194,7 @@
         </is>
       </c>
       <c r="B929" s="2" t="n">
-        <v>41.71318054199219</v>
+        <v>41.71317672729492</v>
       </c>
     </row>
     <row r="930">
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="B933" s="2" t="n">
-        <v>42.22092819213867</v>
+        <v>42.22092437744141</v>
       </c>
     </row>
     <row r="934">
@@ -47254,7 +47254,7 @@
         </is>
       </c>
       <c r="B935" s="2" t="n">
-        <v>42.68960952758789</v>
+        <v>42.68961334228516</v>
       </c>
     </row>
     <row r="936">
@@ -47314,7 +47314,7 @@
         </is>
       </c>
       <c r="B941" s="2" t="n">
-        <v>43.56840133666992</v>
+        <v>43.56839752197266</v>
       </c>
     </row>
     <row r="942">
@@ -47324,7 +47324,7 @@
         </is>
       </c>
       <c r="B942" s="2" t="n">
-        <v>43.9687385559082</v>
+        <v>43.96873474121094</v>
       </c>
     </row>
     <row r="943">
@@ -47334,7 +47334,7 @@
         </is>
       </c>
       <c r="B943" s="2" t="n">
-        <v>43.84180068969727</v>
+        <v>43.84180450439453</v>
       </c>
     </row>
     <row r="944">
@@ -47344,7 +47344,7 @@
         </is>
       </c>
       <c r="B944" s="2" t="n">
-        <v>43.16806030273438</v>
+        <v>43.16806411743164</v>
       </c>
     </row>
     <row r="945">
@@ -47364,7 +47364,7 @@
         </is>
       </c>
       <c r="B946" s="2" t="n">
-        <v>43.62698745727539</v>
+        <v>43.62698364257812</v>
       </c>
     </row>
     <row r="947">
@@ -47394,7 +47394,7 @@
         </is>
       </c>
       <c r="B949" s="2" t="n">
-        <v>41.82058715820312</v>
+        <v>41.82059097290039</v>
       </c>
     </row>
     <row r="950">
@@ -47424,7 +47424,7 @@
         </is>
       </c>
       <c r="B952" s="2" t="n">
-        <v>43.15829849243164</v>
+        <v>43.15830230712891</v>
       </c>
     </row>
     <row r="953">
@@ -47444,7 +47444,7 @@
         </is>
       </c>
       <c r="B954" s="2" t="n">
-        <v>42.33809661865234</v>
+        <v>42.33809280395508</v>
       </c>
     </row>
     <row r="955">
@@ -47454,7 +47454,7 @@
         </is>
       </c>
       <c r="B955" s="2" t="n">
-        <v>42.68960952758789</v>
+        <v>42.68961334228516</v>
       </c>
     </row>
     <row r="956">
@@ -47514,7 +47514,7 @@
         </is>
       </c>
       <c r="B961" s="2" t="n">
-        <v>44.15426254272461</v>
+        <v>44.15425872802734</v>
       </c>
     </row>
     <row r="962">
@@ -47524,7 +47524,7 @@
         </is>
       </c>
       <c r="B962" s="2" t="n">
-        <v>43.74415588378906</v>
+        <v>43.74415969848633</v>
       </c>
     </row>
     <row r="963">
@@ -47544,7 +47544,7 @@
         </is>
       </c>
       <c r="B964" s="2" t="n">
-        <v>43.72462844848633</v>
+        <v>43.72462463378906</v>
       </c>
     </row>
     <row r="965">
@@ -47594,7 +47594,7 @@
         </is>
       </c>
       <c r="B969" s="2" t="n">
-        <v>42.67008590698242</v>
+        <v>42.67008209228516</v>
       </c>
     </row>
     <row r="970">
@@ -47604,7 +47604,7 @@
         </is>
       </c>
       <c r="B970" s="2" t="n">
-        <v>42.80678558349609</v>
+        <v>42.80678176879883</v>
       </c>
     </row>
     <row r="971">
@@ -47614,7 +47614,7 @@
         </is>
       </c>
       <c r="B971" s="2" t="n">
-        <v>42.86537170410156</v>
+        <v>42.8653678894043</v>
       </c>
     </row>
     <row r="972">
@@ -47664,7 +47664,7 @@
         </is>
       </c>
       <c r="B976" s="2" t="n">
-        <v>40.21923828125</v>
+        <v>40.21923446655273</v>
       </c>
     </row>
     <row r="977">
@@ -47724,7 +47724,7 @@
         </is>
       </c>
       <c r="B982" s="2" t="n">
-        <v>40.93203353881836</v>
+        <v>40.93202972412109</v>
       </c>
     </row>
     <row r="983">
@@ -47764,7 +47764,7 @@
         </is>
       </c>
       <c r="B986" s="2" t="n">
-        <v>42.50408554077148</v>
+        <v>42.50408935546875</v>
       </c>
     </row>
     <row r="987">
@@ -47784,7 +47784,7 @@
         </is>
       </c>
       <c r="B988" s="2" t="n">
-        <v>42.50408554077148</v>
+        <v>42.50408935546875</v>
       </c>
     </row>
     <row r="989">
@@ -47844,7 +47844,7 @@
         </is>
       </c>
       <c r="B994" s="2" t="n">
-        <v>44.09567642211914</v>
+        <v>44.09567260742188</v>
       </c>
     </row>
     <row r="995">
@@ -47854,7 +47854,7 @@
         </is>
       </c>
       <c r="B995" s="2" t="n">
-        <v>43.58792495727539</v>
+        <v>43.58792877197266</v>
       </c>
     </row>
     <row r="996">
@@ -47874,7 +47874,7 @@
         </is>
       </c>
       <c r="B997" s="2" t="n">
-        <v>43.8515625</v>
+        <v>43.85156631469727</v>
       </c>
     </row>
     <row r="998">
@@ -47914,7 +47914,7 @@
         </is>
       </c>
       <c r="B1001" s="2" t="n">
-        <v>45.19903945922852</v>
+        <v>45.19904327392578</v>
       </c>
     </row>
     <row r="1002">
@@ -47974,7 +47974,7 @@
         </is>
       </c>
       <c r="B1007" s="2" t="n">
-        <v>45.14045333862305</v>
+        <v>45.14045715332031</v>
       </c>
     </row>
     <row r="1008">
@@ -48004,7 +48004,7 @@
         </is>
       </c>
       <c r="B1010" s="2" t="n">
-        <v>44.99399566650391</v>
+        <v>44.99399185180664</v>
       </c>
     </row>
     <row r="1011">

--- a/demo_output/test/prompt_7/figure_00_Globale aktiemarkeder — indekseret kursudvikl.xlsx
+++ b/demo_output/test/prompt_7/figure_00_Globale aktiemarkeder — indekseret kursudvikl.xlsx
@@ -37924,7 +37924,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>47.67719650268555</v>
+        <v>47.67718124389648</v>
       </c>
     </row>
     <row r="3">
@@ -37934,7 +37934,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>48.14879989624023</v>
+        <v>48.14879608154297</v>
       </c>
     </row>
     <row r="4">
@@ -37944,7 +37944,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>48.50472640991211</v>
+        <v>48.50472259521484</v>
       </c>
     </row>
     <row r="5">
@@ -37954,7 +37954,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>48.51363372802734</v>
+        <v>48.51362609863281</v>
       </c>
     </row>
     <row r="6">
@@ -37964,7 +37964,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>48.82506942749023</v>
+        <v>48.8250732421875</v>
       </c>
     </row>
     <row r="7">
@@ -37994,7 +37994,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>49.37676620483398</v>
+        <v>49.37677001953125</v>
       </c>
     </row>
     <row r="10">
@@ -38004,7 +38004,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>49.82168197631836</v>
+        <v>49.82167434692383</v>
       </c>
     </row>
     <row r="11">
@@ -38014,7 +38014,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>49.57252883911133</v>
+        <v>49.5725212097168</v>
       </c>
     </row>
     <row r="12">
@@ -38024,7 +38024,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>49.332275390625</v>
+        <v>49.33227157592773</v>
       </c>
     </row>
     <row r="13">
@@ -38044,7 +38044,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>49.58403015136719</v>
+        <v>49.58403396606445</v>
       </c>
     </row>
     <row r="15">
@@ -38054,7 +38054,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>49.41423034667969</v>
+        <v>49.41422271728516</v>
       </c>
     </row>
     <row r="16">
@@ -38074,7 +38074,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>49.20867156982422</v>
+        <v>49.20866394042969</v>
       </c>
     </row>
     <row r="18">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>48.53837203979492</v>
+        <v>48.53837585449219</v>
       </c>
     </row>
     <row r="19">
@@ -38094,7 +38094,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>48.80649185180664</v>
+        <v>48.80649566650391</v>
       </c>
     </row>
     <row r="20">
@@ -38104,7 +38104,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>48.46686935424805</v>
+        <v>48.46687698364258</v>
       </c>
     </row>
     <row r="21">
@@ -38114,7 +38114,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>48.67243576049805</v>
+        <v>48.67242813110352</v>
       </c>
     </row>
     <row r="22">
@@ -38124,7 +38124,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>48.44899749755859</v>
+        <v>48.44899368286133</v>
       </c>
     </row>
     <row r="23">
@@ -38134,7 +38134,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>48.74393081665039</v>
+        <v>48.74392700195312</v>
       </c>
     </row>
     <row r="24">
@@ -38144,7 +38144,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>49.19079971313477</v>
+        <v>49.19079208374023</v>
       </c>
     </row>
     <row r="25">
@@ -38184,7 +38184,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>49.28910446166992</v>
+        <v>49.28910064697266</v>
       </c>
     </row>
     <row r="29">
@@ -38194,7 +38194,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>49.01205062866211</v>
+        <v>49.01204299926758</v>
       </c>
     </row>
     <row r="30">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>48.10044479370117</v>
+        <v>48.10044097900391</v>
       </c>
     </row>
     <row r="32">
@@ -38224,7 +38224,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>48.04681777954102</v>
+        <v>48.04682159423828</v>
       </c>
     </row>
     <row r="33">
@@ -38234,7 +38234,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>47.04584121704102</v>
+        <v>47.04584503173828</v>
       </c>
     </row>
     <row r="34">
@@ -38244,7 +38244,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>47.8591423034668</v>
+        <v>47.85913467407227</v>
       </c>
     </row>
     <row r="35">
@@ -38254,7 +38254,7 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>47.90382385253906</v>
+        <v>47.9038200378418</v>
       </c>
     </row>
     <row r="36">
@@ -38294,7 +38294,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>47.8948860168457</v>
+        <v>47.89488983154297</v>
       </c>
     </row>
     <row r="40">
@@ -38304,7 +38304,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>47.09053421020508</v>
+        <v>47.09053039550781</v>
       </c>
     </row>
     <row r="41">
@@ -38314,7 +38314,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>47.24246597290039</v>
+        <v>47.24246978759766</v>
       </c>
     </row>
     <row r="42">
@@ -38334,7 +38334,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>47.63570404052734</v>
+        <v>47.63570022583008</v>
       </c>
     </row>
     <row r="44">
@@ -38344,7 +38344,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46.92966079711914</v>
+        <v>46.92965698242188</v>
       </c>
     </row>
     <row r="45">
@@ -38364,7 +38364,7 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45.1064567565918</v>
+        <v>45.10645294189453</v>
       </c>
     </row>
     <row r="47">
@@ -38384,7 +38384,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46.563232421875</v>
+        <v>46.56322479248047</v>
       </c>
     </row>
     <row r="49">
@@ -38394,7 +38394,7 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46.11636352539062</v>
+        <v>46.11636734008789</v>
       </c>
     </row>
     <row r="50">
@@ -38404,7 +38404,7 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46.44705200195312</v>
+        <v>46.44704055786133</v>
       </c>
     </row>
     <row r="51">
@@ -38424,7 +38424,7 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46.88497543334961</v>
+        <v>46.88497161865234</v>
       </c>
     </row>
     <row r="53">
@@ -38444,7 +38444,7 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46.42023849487305</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="55">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46.57217407226562</v>
+        <v>46.57216644287109</v>
       </c>
     </row>
     <row r="56">
@@ -38484,7 +38484,7 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46.34873199462891</v>
+        <v>46.34873580932617</v>
       </c>
     </row>
     <row r="59">
@@ -38494,7 +38494,7 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46.2325553894043</v>
+        <v>46.23254776000977</v>
       </c>
     </row>
     <row r="60">
@@ -38504,7 +38504,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45.81249237060547</v>
+        <v>45.8125</v>
       </c>
     </row>
     <row r="61">
@@ -38514,7 +38514,7 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>44.97239685058594</v>
+        <v>44.97239303588867</v>
       </c>
     </row>
     <row r="62">
@@ -38524,7 +38524,7 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45.04389572143555</v>
+        <v>45.04388809204102</v>
       </c>
     </row>
     <row r="63">
@@ -38544,7 +38544,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>44.23954391479492</v>
+        <v>44.23953628540039</v>
       </c>
     </row>
     <row r="65">
@@ -38574,7 +38574,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45.98230743408203</v>
+        <v>45.98230361938477</v>
       </c>
     </row>
     <row r="68">
@@ -38594,7 +38594,7 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46.10742950439453</v>
+        <v>46.1074333190918</v>
       </c>
     </row>
     <row r="70">
@@ -38604,7 +38604,7 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46.20574188232422</v>
+        <v>46.20573806762695</v>
       </c>
     </row>
     <row r="71">
@@ -38614,7 +38614,7 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46.84028625488281</v>
+        <v>46.84029006958008</v>
       </c>
     </row>
     <row r="72">
@@ -38634,7 +38634,7 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>47.22458648681641</v>
+        <v>47.22459030151367</v>
       </c>
     </row>
     <row r="74">
@@ -38644,7 +38644,7 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>47.47483444213867</v>
+        <v>47.47483825683594</v>
       </c>
     </row>
     <row r="75">
@@ -38654,7 +38654,7 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>47.75188827514648</v>
+        <v>47.75189590454102</v>
       </c>
     </row>
     <row r="76">
@@ -38664,7 +38664,7 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>47.05477905273438</v>
+        <v>47.05478286743164</v>
       </c>
     </row>
     <row r="77">
@@ -38674,7 +38674,7 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46.96540832519531</v>
+        <v>46.96541213989258</v>
       </c>
     </row>
     <row r="78">
@@ -38684,7 +38684,7 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46.91178512573242</v>
+        <v>46.91179275512695</v>
       </c>
     </row>
     <row r="79">
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>47.03690719604492</v>
+        <v>47.03691101074219</v>
       </c>
     </row>
     <row r="80">
@@ -38724,7 +38724,7 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46.10742950439453</v>
+        <v>46.1074333190918</v>
       </c>
     </row>
     <row r="83">
@@ -38744,7 +38744,7 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>44.67746734619141</v>
+        <v>44.67747116088867</v>
       </c>
     </row>
     <row r="85">
@@ -38754,7 +38754,7 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45.00814437866211</v>
+        <v>45.00814819335938</v>
       </c>
     </row>
     <row r="86">
@@ -38794,7 +38794,7 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45.67844009399414</v>
+        <v>45.67844390869141</v>
       </c>
     </row>
     <row r="90">
@@ -38804,7 +38804,7 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45.08858489990234</v>
+        <v>45.08858108520508</v>
       </c>
     </row>
     <row r="91">
@@ -38824,7 +38824,7 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45.02602386474609</v>
+        <v>45.02601623535156</v>
       </c>
     </row>
     <row r="93">
@@ -38844,7 +38844,7 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>44.31997299194336</v>
+        <v>44.31996917724609</v>
       </c>
     </row>
     <row r="95">
@@ -38854,7 +38854,7 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>44.63277435302734</v>
+        <v>44.63278198242188</v>
       </c>
     </row>
     <row r="96">
@@ -38864,7 +38864,7 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>44.38254165649414</v>
+        <v>44.38253784179688</v>
       </c>
     </row>
     <row r="97">
@@ -38874,7 +38874,7 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45.24945068359375</v>
+        <v>45.24945449829102</v>
       </c>
     </row>
     <row r="98">
@@ -38914,7 +38914,7 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45.72312927246094</v>
+        <v>45.72312545776367</v>
       </c>
     </row>
     <row r="102">
@@ -38924,7 +38924,7 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45.86612319946289</v>
+        <v>45.86612701416016</v>
       </c>
     </row>
     <row r="103">
@@ -38934,7 +38934,7 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46.42023849487305</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="104">
@@ -38954,7 +38954,7 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46.92071914672852</v>
+        <v>46.92072677612305</v>
       </c>
     </row>
     <row r="106">
@@ -38964,7 +38964,7 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46.91178512573242</v>
+        <v>46.91179275512695</v>
       </c>
     </row>
     <row r="107">
@@ -38974,7 +38974,7 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46.6079216003418</v>
+        <v>46.60791778564453</v>
       </c>
     </row>
     <row r="108">
@@ -38994,7 +38994,7 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46.75091552734375</v>
+        <v>46.75091934204102</v>
       </c>
     </row>
     <row r="110">
@@ -39034,7 +39034,7 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45.50862503051758</v>
+        <v>45.50864028930664</v>
       </c>
     </row>
     <row r="114">
@@ -39044,7 +39044,7 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45.86612319946289</v>
+        <v>45.86612701416016</v>
       </c>
     </row>
     <row r="115">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45.66950225830078</v>
+        <v>45.66949844360352</v>
       </c>
     </row>
     <row r="117">
@@ -39074,7 +39074,7 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45.56225967407227</v>
+        <v>45.562255859375</v>
       </c>
     </row>
     <row r="118">
@@ -39084,7 +39084,7 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45.50862503051758</v>
+        <v>45.50864028930664</v>
       </c>
     </row>
     <row r="119">
@@ -39104,7 +39104,7 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45.74993515014648</v>
+        <v>45.74993896484375</v>
       </c>
     </row>
     <row r="121">
@@ -39114,7 +39114,7 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45.56225967407227</v>
+        <v>45.562255859375</v>
       </c>
     </row>
     <row r="122">
@@ -39124,7 +39124,7 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46.34873199462891</v>
+        <v>46.34873580932617</v>
       </c>
     </row>
     <row r="123">
@@ -39134,7 +39134,7 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46.47386169433594</v>
+        <v>46.47385787963867</v>
       </c>
     </row>
     <row r="124">
@@ -39164,7 +39164,7 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46.1431770324707</v>
+        <v>46.14318084716797</v>
       </c>
     </row>
     <row r="127">
@@ -39184,7 +39184,7 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45.50862503051758</v>
+        <v>45.50864028930664</v>
       </c>
     </row>
     <row r="129">
@@ -39194,7 +39194,7 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45.14219665527344</v>
+        <v>45.14220428466797</v>
       </c>
     </row>
     <row r="130">
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>43.52455139160156</v>
+        <v>43.52456283569336</v>
       </c>
     </row>
     <row r="133">
@@ -39244,7 +39244,7 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>43.64968109130859</v>
+        <v>43.64967727661133</v>
       </c>
     </row>
     <row r="135">
@@ -39254,7 +39254,7 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>43.81055068969727</v>
+        <v>43.81054306030273</v>
       </c>
     </row>
     <row r="136">
@@ -39274,7 +39274,7 @@
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>43.72117614746094</v>
+        <v>43.72117233276367</v>
       </c>
     </row>
     <row r="138">
@@ -39284,7 +39284,7 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>44.06079483032227</v>
+        <v>44.060791015625</v>
       </c>
     </row>
     <row r="139">
@@ -39294,7 +39294,7 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>44.75790405273438</v>
+        <v>44.75790023803711</v>
       </c>
     </row>
     <row r="140">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>44.93664169311523</v>
+        <v>44.93663787841797</v>
       </c>
     </row>
     <row r="141">
@@ -39324,7 +39324,7 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>44.75790405273438</v>
+        <v>44.75790023803711</v>
       </c>
     </row>
     <row r="143">
@@ -39334,7 +39334,7 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>44.04808807373047</v>
+        <v>44.04809951782227</v>
       </c>
     </row>
     <row r="144">
@@ -39344,7 +39344,7 @@
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>43.94837188720703</v>
+        <v>43.94836807250977</v>
       </c>
     </row>
     <row r="145">
@@ -39364,7 +39364,7 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>43.8758544921875</v>
+        <v>43.87585067749023</v>
       </c>
     </row>
     <row r="147">
@@ -39374,7 +39374,7 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>43.65828704833984</v>
+        <v>43.65828323364258</v>
       </c>
     </row>
     <row r="148">
@@ -39384,7 +39384,7 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>43.00558090209961</v>
+        <v>43.00558853149414</v>
       </c>
     </row>
     <row r="149">
@@ -39394,7 +39394,7 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>43.73081207275391</v>
+        <v>43.73080825805664</v>
       </c>
     </row>
     <row r="150">
@@ -39404,7 +39404,7 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>43.93931198120117</v>
+        <v>43.93930816650391</v>
       </c>
     </row>
     <row r="151">
@@ -39414,7 +39414,7 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>44.16594696044922</v>
+        <v>44.16594314575195</v>
       </c>
     </row>
     <row r="152">
@@ -39424,7 +39424,7 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>44.36537170410156</v>
+        <v>44.36537933349609</v>
       </c>
     </row>
     <row r="153">
@@ -39444,7 +39444,7 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>44.02090072631836</v>
+        <v>44.02089691162109</v>
       </c>
     </row>
     <row r="155">
@@ -39454,7 +39454,7 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>44.52518844604492</v>
+        <v>44.52519607543945</v>
       </c>
     </row>
     <row r="156">
@@ -39464,7 +39464,7 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>44.30751037597656</v>
+        <v>44.30751419067383</v>
       </c>
     </row>
     <row r="157">
@@ -39494,7 +39494,7 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>43.74516677856445</v>
+        <v>43.74516296386719</v>
       </c>
     </row>
     <row r="160">
@@ -39504,7 +39504,7 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>43.94470596313477</v>
+        <v>43.94470977783203</v>
       </c>
     </row>
     <row r="161">
@@ -39514,7 +39514,7 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>44.34379577636719</v>
+        <v>44.34378814697266</v>
       </c>
     </row>
     <row r="162">
@@ -39524,7 +39524,7 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>44.34379577636719</v>
+        <v>44.34378814697266</v>
       </c>
     </row>
     <row r="163">
@@ -39534,7 +39534,7 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45.36871337890625</v>
+        <v>45.36871719360352</v>
       </c>
     </row>
     <row r="164">
@@ -39554,7 +39554,7 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>45.46848678588867</v>
+        <v>45.46849060058594</v>
       </c>
     </row>
     <row r="166">
@@ -39564,7 +39564,7 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45.45034408569336</v>
+        <v>45.45034790039062</v>
       </c>
     </row>
     <row r="167">
@@ -39574,7 +39574,7 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>44.64310455322266</v>
+        <v>44.64310836791992</v>
       </c>
     </row>
     <row r="168">
@@ -39594,7 +39594,7 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>45.09661865234375</v>
+        <v>45.09661483764648</v>
       </c>
     </row>
     <row r="170">
@@ -39624,7 +39624,7 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>43.73609924316406</v>
+        <v>43.7360954284668</v>
       </c>
     </row>
     <row r="173">
@@ -39634,7 +39634,7 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>43.18281555175781</v>
+        <v>43.18281173706055</v>
       </c>
     </row>
     <row r="174">
@@ -39654,7 +39654,7 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>42.89257049560547</v>
+        <v>42.892578125</v>
       </c>
     </row>
     <row r="176">
@@ -39664,7 +39664,7 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>44.29843902587891</v>
+        <v>44.29844665527344</v>
       </c>
     </row>
     <row r="177">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>44.57054138183594</v>
+        <v>44.5705451965332</v>
       </c>
     </row>
     <row r="178">
@@ -39684,7 +39684,7 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>44.49798965454102</v>
+        <v>44.49798202514648</v>
       </c>
     </row>
     <row r="179">
@@ -39704,7 +39704,7 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>44.13517761230469</v>
+        <v>44.13518142700195</v>
       </c>
     </row>
     <row r="181">
@@ -39744,7 +39744,7 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>44.8698616027832</v>
+        <v>44.86985778808594</v>
       </c>
     </row>
     <row r="185">
@@ -39754,7 +39754,7 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>44.18959808349609</v>
+        <v>44.18960189819336</v>
       </c>
     </row>
     <row r="186">
@@ -39764,7 +39764,7 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>43.88122177124023</v>
+        <v>43.8812141418457</v>
       </c>
     </row>
     <row r="187">
@@ -39784,7 +39784,7 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>45.16010665893555</v>
+        <v>45.16010284423828</v>
       </c>
     </row>
     <row r="189">
@@ -39794,7 +39794,7 @@
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>44.634033203125</v>
+        <v>44.63403701782227</v>
       </c>
     </row>
     <row r="190">
@@ -39804,7 +39804,7 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>44.18959808349609</v>
+        <v>44.18960189819336</v>
       </c>
     </row>
     <row r="191">
@@ -39814,7 +39814,7 @@
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>43.56375885009766</v>
+        <v>43.56376647949219</v>
       </c>
     </row>
     <row r="192">
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>43.05583572387695</v>
+        <v>43.05583190917969</v>
       </c>
     </row>
     <row r="193">
@@ -39834,7 +39834,7 @@
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>42.16696929931641</v>
+        <v>42.16697311401367</v>
       </c>
     </row>
     <row r="194">
@@ -39844,7 +39844,7 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>42.94699096679688</v>
+        <v>42.94699478149414</v>
       </c>
     </row>
     <row r="195">
@@ -39854,7 +39854,7 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>42.3846435546875</v>
+        <v>42.38464736938477</v>
       </c>
     </row>
     <row r="196">
@@ -39864,7 +39864,7 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>41.82230377197266</v>
+        <v>41.82229995727539</v>
       </c>
     </row>
     <row r="197">
@@ -39874,7 +39874,7 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>41.89485931396484</v>
+        <v>41.89486312866211</v>
       </c>
     </row>
     <row r="198">
@@ -39884,7 +39884,7 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>41.3053092956543</v>
+        <v>41.30530166625977</v>
       </c>
     </row>
     <row r="199">
@@ -39894,7 +39894,7 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>40.47085189819336</v>
+        <v>40.47084808349609</v>
       </c>
     </row>
     <row r="200">
@@ -39904,7 +39904,7 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>38.95615005493164</v>
+        <v>38.95614242553711</v>
       </c>
     </row>
     <row r="201">
@@ -39914,7 +39914,7 @@
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>39.08312606811523</v>
+        <v>39.08312225341797</v>
       </c>
     </row>
     <row r="202">
@@ -39944,7 +39944,7 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>38.61147689819336</v>
+        <v>38.61147308349609</v>
       </c>
     </row>
     <row r="205">
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>40.77016830444336</v>
+        <v>40.77016448974609</v>
       </c>
     </row>
     <row r="208">
@@ -39984,7 +39984,7 @@
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>40.56155776977539</v>
+        <v>40.56155395507812</v>
       </c>
     </row>
     <row r="209">
@@ -40004,7 +40004,7 @@
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>40.50712966918945</v>
+        <v>40.50713348388672</v>
       </c>
     </row>
     <row r="211">
@@ -40014,7 +40014,7 @@
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>41.24181747436523</v>
+        <v>41.24181365966797</v>
       </c>
     </row>
     <row r="212">
@@ -40024,7 +40024,7 @@
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>40.9697151184082</v>
+        <v>40.96970367431641</v>
       </c>
     </row>
     <row r="213">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>40.86087036132812</v>
+        <v>40.86086654663086</v>
       </c>
     </row>
     <row r="215">
@@ -40054,7 +40054,7 @@
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>40.99691390991211</v>
+        <v>40.99692153930664</v>
       </c>
     </row>
     <row r="216">
@@ -40064,7 +40064,7 @@
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>41.69531631469727</v>
+        <v>41.69532775878906</v>
       </c>
     </row>
     <row r="217">
@@ -40104,7 +40104,7 @@
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>42.36650085449219</v>
+        <v>42.36650848388672</v>
       </c>
     </row>
     <row r="221">
@@ -40114,7 +40114,7 @@
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>41.58647918701172</v>
+        <v>41.58647537231445</v>
       </c>
     </row>
     <row r="222">
@@ -40134,7 +40134,7 @@
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>40.71574401855469</v>
+        <v>40.71574020385742</v>
       </c>
     </row>
     <row r="224">
@@ -40144,7 +40144,7 @@
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>40.75202941894531</v>
+        <v>40.75202560424805</v>
       </c>
     </row>
     <row r="225">
@@ -40154,7 +40154,7 @@
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>40.24409484863281</v>
+        <v>40.24409866333008</v>
       </c>
     </row>
     <row r="226">
@@ -40164,7 +40164,7 @@
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>40.11711883544922</v>
+        <v>40.11711502075195</v>
       </c>
     </row>
     <row r="227">
@@ -40174,7 +40174,7 @@
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>40.6431884765625</v>
+        <v>40.64318466186523</v>
       </c>
     </row>
     <row r="228">
@@ -40184,7 +40184,7 @@
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>40.11711883544922</v>
+        <v>40.11711502075195</v>
       </c>
     </row>
     <row r="229">
@@ -40194,7 +40194,7 @@
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>39.9810676574707</v>
+        <v>39.98106384277344</v>
       </c>
     </row>
     <row r="230">
@@ -40204,7 +40204,7 @@
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>39.78152465820312</v>
+        <v>39.78152847290039</v>
       </c>
     </row>
     <row r="231">
@@ -40214,7 +40214,7 @@
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>39.54569625854492</v>
+        <v>39.54570007324219</v>
       </c>
     </row>
     <row r="232">
@@ -40234,7 +40234,7 @@
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>38.43915176391602</v>
+        <v>38.43914794921875</v>
       </c>
     </row>
     <row r="234">
@@ -40254,7 +40254,7 @@
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>37.32352828979492</v>
+        <v>37.32352447509766</v>
       </c>
     </row>
     <row r="236">
@@ -40264,7 +40264,7 @@
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>37.75888442993164</v>
+        <v>37.75888824462891</v>
       </c>
     </row>
     <row r="237">
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>38.30309295654297</v>
+        <v>38.3031005859375</v>
       </c>
     </row>
     <row r="238">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>38.43915176391602</v>
+        <v>38.43914794921875</v>
       </c>
     </row>
     <row r="239">
@@ -40294,7 +40294,7 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>38.38471984863281</v>
+        <v>38.38472366333008</v>
       </c>
     </row>
     <row r="240">
@@ -40304,7 +40304,7 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>38.66589736938477</v>
+        <v>38.66590118408203</v>
       </c>
     </row>
     <row r="241">
@@ -40314,7 +40314,7 @@
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>39.08312606811523</v>
+        <v>39.08312225341797</v>
       </c>
     </row>
     <row r="242">
@@ -40334,7 +40334,7 @@
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>37.12397766113281</v>
+        <v>37.12398147583008</v>
       </c>
     </row>
     <row r="244">
@@ -40354,7 +40354,7 @@
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>36.22603225708008</v>
+        <v>36.22603607177734</v>
       </c>
     </row>
     <row r="246">
@@ -40364,7 +40364,7 @@
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>35.97207641601562</v>
+        <v>35.97207260131836</v>
       </c>
     </row>
     <row r="247">
@@ -40374,7 +40374,7 @@
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>35.73625183105469</v>
+        <v>35.73625564575195</v>
       </c>
     </row>
     <row r="248">
@@ -40384,7 +40384,7 @@
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>36.72489929199219</v>
+        <v>36.72489166259766</v>
       </c>
     </row>
     <row r="249">
@@ -40394,7 +40394,7 @@
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>36.57978057861328</v>
+        <v>36.57977676391602</v>
       </c>
     </row>
     <row r="250">
@@ -40414,7 +40414,7 @@
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>36.57978057861328</v>
+        <v>36.57977676391602</v>
       </c>
     </row>
     <row r="252">
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>37.16026306152344</v>
+        <v>37.16025924682617</v>
       </c>
     </row>
     <row r="253">
@@ -40464,7 +40464,7 @@
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>37.12397766113281</v>
+        <v>37.12398147583008</v>
       </c>
     </row>
     <row r="257">
@@ -40474,7 +40474,7 @@
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>37.70447158813477</v>
+        <v>37.7044677734375</v>
       </c>
     </row>
     <row r="258">
@@ -40484,7 +40484,7 @@
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>38.13983535766602</v>
+        <v>38.13983917236328</v>
       </c>
     </row>
     <row r="259">
@@ -40494,7 +40494,7 @@
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>38.67496871948242</v>
+        <v>38.67497253417969</v>
       </c>
     </row>
     <row r="260">
@@ -40504,7 +40504,7 @@
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>38.40287017822266</v>
+        <v>38.40287399291992</v>
       </c>
     </row>
     <row r="261">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>38.43007278442383</v>
+        <v>38.43008041381836</v>
       </c>
     </row>
     <row r="263">
@@ -40554,7 +40554,7 @@
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>38.96521377563477</v>
+        <v>38.9652214050293</v>
       </c>
     </row>
     <row r="266">
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>37.62240219116211</v>
+        <v>37.62240600585938</v>
       </c>
     </row>
     <row r="268">
@@ -40604,7 +40604,7 @@
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>37.29310989379883</v>
+        <v>37.29310607910156</v>
       </c>
     </row>
     <row r="271">
@@ -40624,7 +40624,7 @@
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>36.28691864013672</v>
+        <v>36.28691482543945</v>
       </c>
     </row>
     <row r="273">
@@ -40644,7 +40644,7 @@
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>36.21374130249023</v>
+        <v>36.2137336730957</v>
       </c>
     </row>
     <row r="275">
@@ -40674,7 +40674,7 @@
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>37.22907638549805</v>
+        <v>37.22908020019531</v>
       </c>
     </row>
     <row r="278">
@@ -40684,7 +40684,7 @@
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>37.00040054321289</v>
+        <v>37.00039672851562</v>
       </c>
     </row>
     <row r="279">
@@ -40694,7 +40694,7 @@
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>36.85404205322266</v>
+        <v>36.85403823852539</v>
       </c>
     </row>
     <row r="280">
@@ -40714,7 +40714,7 @@
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>36.45156097412109</v>
+        <v>36.45156478881836</v>
       </c>
     </row>
     <row r="282">
@@ -40724,7 +40724,7 @@
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>36.16800689697266</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="283">
@@ -40734,7 +40734,7 @@
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>35.94847106933594</v>
+        <v>35.94846343994141</v>
       </c>
     </row>
     <row r="284">
@@ -40744,7 +40744,7 @@
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>36.67110061645508</v>
+        <v>36.67110443115234</v>
       </c>
     </row>
     <row r="285">
@@ -40754,7 +40754,7 @@
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>36.67110061645508</v>
+        <v>36.67110443115234</v>
       </c>
     </row>
     <row r="286">
@@ -40764,7 +40764,7 @@
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>35.69234848022461</v>
+        <v>35.69235229492188</v>
       </c>
     </row>
     <row r="287">
@@ -40794,7 +40794,7 @@
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>35.15266036987305</v>
+        <v>35.15266799926758</v>
       </c>
     </row>
     <row r="290">
@@ -40814,7 +40814,7 @@
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>35.58258056640625</v>
+        <v>35.58258438110352</v>
       </c>
     </row>
     <row r="292">
@@ -40824,7 +40824,7 @@
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>36.16800689697266</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="293">
@@ -40844,7 +40844,7 @@
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>36.42411804199219</v>
+        <v>36.42412185668945</v>
       </c>
     </row>
     <row r="295">
@@ -40854,7 +40854,7 @@
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>36.05823516845703</v>
+        <v>36.05823135375977</v>
       </c>
     </row>
     <row r="296">
@@ -40864,7 +40864,7 @@
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>36.18629837036133</v>
+        <v>36.18629455566406</v>
       </c>
     </row>
     <row r="297">
@@ -40874,7 +40874,7 @@
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>35.90272903442383</v>
+        <v>35.90273284912109</v>
       </c>
     </row>
     <row r="298">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="B299" s="2" t="n">
-        <v>36.72598266601562</v>
+        <v>36.72597885131836</v>
       </c>
     </row>
     <row r="300">
@@ -40904,7 +40904,7 @@
         </is>
       </c>
       <c r="B300" s="2" t="n">
-        <v>36.55218124389648</v>
+        <v>36.55218505859375</v>
       </c>
     </row>
     <row r="301">
@@ -40914,7 +40914,7 @@
         </is>
       </c>
       <c r="B301" s="2" t="n">
-        <v>36.24118041992188</v>
+        <v>36.24117660522461</v>
       </c>
     </row>
     <row r="302">
@@ -40934,7 +40934,7 @@
         </is>
       </c>
       <c r="B303" s="2" t="n">
-        <v>36.35094451904297</v>
+        <v>36.35094833374023</v>
       </c>
     </row>
     <row r="304">
@@ -40964,7 +40964,7 @@
         </is>
       </c>
       <c r="B306" s="2" t="n">
-        <v>36.68939208984375</v>
+        <v>36.68939590454102</v>
       </c>
     </row>
     <row r="307">
@@ -40974,7 +40974,7 @@
         </is>
       </c>
       <c r="B307" s="2" t="n">
-        <v>36.55218124389648</v>
+        <v>36.55218505859375</v>
       </c>
     </row>
     <row r="308">
@@ -40984,7 +40984,7 @@
         </is>
       </c>
       <c r="B308" s="2" t="n">
-        <v>37.00953674316406</v>
+        <v>37.00954055786133</v>
       </c>
     </row>
     <row r="309">
@@ -40994,7 +40994,7 @@
         </is>
       </c>
       <c r="B309" s="2" t="n">
-        <v>37.15589904785156</v>
+        <v>37.15590286254883</v>
       </c>
     </row>
     <row r="310">
@@ -41014,7 +41014,7 @@
         </is>
       </c>
       <c r="B311" s="2" t="n">
-        <v>37.37543487548828</v>
+        <v>37.37543106079102</v>
       </c>
     </row>
     <row r="312">
@@ -41034,7 +41034,7 @@
         </is>
       </c>
       <c r="B313" s="2" t="n">
-        <v>37.21078109741211</v>
+        <v>37.21077728271484</v>
       </c>
     </row>
     <row r="314">
@@ -41044,7 +41044,7 @@
         </is>
       </c>
       <c r="B314" s="2" t="n">
-        <v>37.00040054321289</v>
+        <v>37.00039672851562</v>
       </c>
     </row>
     <row r="315">
@@ -41064,7 +41064,7 @@
         </is>
       </c>
       <c r="B316" s="2" t="n">
-        <v>36.17715454101562</v>
+        <v>36.17715072631836</v>
       </c>
     </row>
     <row r="317">
@@ -41074,7 +41074,7 @@
         </is>
       </c>
       <c r="B317" s="2" t="n">
-        <v>36.36924362182617</v>
+        <v>36.36923599243164</v>
       </c>
     </row>
     <row r="318">
@@ -41084,7 +41084,7 @@
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>36.36009216308594</v>
+        <v>36.3600959777832</v>
       </c>
     </row>
     <row r="319">
@@ -41094,7 +41094,7 @@
         </is>
       </c>
       <c r="B319" s="2" t="n">
-        <v>37.14675140380859</v>
+        <v>37.14674758911133</v>
       </c>
     </row>
     <row r="320">
@@ -41114,7 +41114,7 @@
         </is>
       </c>
       <c r="B321" s="2" t="n">
-        <v>36.36924362182617</v>
+        <v>36.36923599243164</v>
       </c>
     </row>
     <row r="322">
@@ -41144,7 +41144,7 @@
         </is>
       </c>
       <c r="B324" s="2" t="n">
-        <v>35.78381729125977</v>
+        <v>35.78382110595703</v>
       </c>
     </row>
     <row r="325">
@@ -41154,7 +41154,7 @@
         </is>
       </c>
       <c r="B325" s="2" t="n">
-        <v>35.45451736450195</v>
+        <v>35.45452117919922</v>
       </c>
     </row>
     <row r="326">
@@ -41164,7 +41164,7 @@
         </is>
       </c>
       <c r="B326" s="2" t="n">
-        <v>35.03374862670898</v>
+        <v>35.03374099731445</v>
       </c>
     </row>
     <row r="327">
@@ -41184,7 +41184,7 @@
         </is>
       </c>
       <c r="B328" s="2" t="n">
-        <v>35.15266036987305</v>
+        <v>35.15266799926758</v>
       </c>
     </row>
     <row r="329">
@@ -41204,7 +41204,7 @@
         </is>
       </c>
       <c r="B330" s="2" t="n">
-        <v>36.20459747314453</v>
+        <v>36.20458984375</v>
       </c>
     </row>
     <row r="331">
@@ -41224,7 +41224,7 @@
         </is>
       </c>
       <c r="B332" s="2" t="n">
-        <v>35.26242065429688</v>
+        <v>35.26243591308594</v>
       </c>
     </row>
     <row r="333">
@@ -41244,7 +41244,7 @@
         </is>
       </c>
       <c r="B334" s="2" t="n">
-        <v>34.56724548339844</v>
+        <v>34.56724166870117</v>
       </c>
     </row>
     <row r="335">
@@ -41254,7 +41254,7 @@
         </is>
       </c>
       <c r="B335" s="2" t="n">
-        <v>34.67700576782227</v>
+        <v>34.67700958251953</v>
       </c>
     </row>
     <row r="336">
@@ -41304,7 +41304,7 @@
         </is>
       </c>
       <c r="B340" s="2" t="n">
-        <v>32.50912094116211</v>
+        <v>32.50912475585938</v>
       </c>
     </row>
     <row r="341">
@@ -41314,7 +41314,7 @@
         </is>
       </c>
       <c r="B341" s="2" t="n">
-        <v>32.4725341796875</v>
+        <v>32.47253799438477</v>
       </c>
     </row>
     <row r="342">
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="B342" s="2" t="n">
-        <v>32.75609970092773</v>
+        <v>32.756103515625</v>
       </c>
     </row>
     <row r="343">
@@ -41354,7 +41354,7 @@
         </is>
       </c>
       <c r="B345" s="2" t="n">
-        <v>32.42679977416992</v>
+        <v>32.42679595947266</v>
       </c>
     </row>
     <row r="346">
@@ -41364,7 +41364,7 @@
         </is>
       </c>
       <c r="B346" s="2" t="n">
-        <v>33.48787689208984</v>
+        <v>33.48787307739258</v>
       </c>
     </row>
     <row r="347">
@@ -41384,7 +41384,7 @@
         </is>
       </c>
       <c r="B348" s="2" t="n">
-        <v>33.30492782592773</v>
+        <v>33.304931640625</v>
       </c>
     </row>
     <row r="349">
@@ -41404,7 +41404,7 @@
         </is>
       </c>
       <c r="B350" s="2" t="n">
-        <v>32.15238952636719</v>
+        <v>32.15238189697266</v>
       </c>
     </row>
     <row r="351">
@@ -41414,7 +41414,7 @@
         </is>
       </c>
       <c r="B351" s="2" t="n">
-        <v>31.64013862609863</v>
+        <v>31.6401424407959</v>
       </c>
     </row>
     <row r="352">
@@ -41424,7 +41424,7 @@
         </is>
       </c>
       <c r="B352" s="2" t="n">
-        <v>31.67673110961914</v>
+        <v>31.67673492431641</v>
       </c>
     </row>
     <row r="353">
@@ -41434,7 +41434,7 @@
         </is>
       </c>
       <c r="B353" s="2" t="n">
-        <v>31.7681999206543</v>
+        <v>31.76820182800293</v>
       </c>
     </row>
     <row r="354">
@@ -41444,7 +41444,7 @@
         </is>
       </c>
       <c r="B354" s="2" t="n">
-        <v>31.29254913330078</v>
+        <v>31.29254341125488</v>
       </c>
     </row>
     <row r="355">
@@ -41454,7 +41454,7 @@
         </is>
       </c>
       <c r="B355" s="2" t="n">
-        <v>32.15238952636719</v>
+        <v>32.15238189697266</v>
       </c>
     </row>
     <row r="356">
@@ -41464,7 +41464,7 @@
         </is>
       </c>
       <c r="B356" s="2" t="n">
-        <v>32.16152954101562</v>
+        <v>32.16153335571289</v>
       </c>
     </row>
     <row r="357">
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="B357" s="2" t="n">
-        <v>31.57610893249512</v>
+        <v>31.57611083984375</v>
       </c>
     </row>
     <row r="358">
@@ -41484,7 +41484,7 @@
         </is>
       </c>
       <c r="B358" s="2" t="n">
-        <v>31.77735710144043</v>
+        <v>31.77735328674316</v>
       </c>
     </row>
     <row r="359">
@@ -41514,7 +41514,7 @@
         </is>
       </c>
       <c r="B361" s="2" t="n">
-        <v>31.29254913330078</v>
+        <v>31.29254341125488</v>
       </c>
     </row>
     <row r="362">
@@ -41524,7 +41524,7 @@
         </is>
       </c>
       <c r="B362" s="2" t="n">
-        <v>31.80478668212891</v>
+        <v>31.80479049682617</v>
       </c>
     </row>
     <row r="363">
@@ -41534,7 +41534,7 @@
         </is>
       </c>
       <c r="B363" s="2" t="n">
-        <v>31.55781936645508</v>
+        <v>31.55781745910645</v>
       </c>
     </row>
     <row r="364">
@@ -41554,7 +41554,7 @@
         </is>
       </c>
       <c r="B365" s="2" t="n">
-        <v>31.27425384521484</v>
+        <v>31.27425575256348</v>
       </c>
     </row>
     <row r="366">
@@ -41564,7 +41564,7 @@
         </is>
       </c>
       <c r="B366" s="2" t="n">
-        <v>31.85053253173828</v>
+        <v>31.85052299499512</v>
       </c>
     </row>
     <row r="367">
@@ -41574,7 +41574,7 @@
         </is>
       </c>
       <c r="B367" s="2" t="n">
-        <v>31.58525466918945</v>
+        <v>31.58525276184082</v>
       </c>
     </row>
     <row r="368">
@@ -41584,7 +41584,7 @@
         </is>
       </c>
       <c r="B368" s="2" t="n">
-        <v>31.7681999206543</v>
+        <v>31.76820182800293</v>
       </c>
     </row>
     <row r="369">
@@ -41594,7 +41594,7 @@
         </is>
       </c>
       <c r="B369" s="2" t="n">
-        <v>33.11283874511719</v>
+        <v>33.11284255981445</v>
       </c>
     </row>
     <row r="370">
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="B370" s="2" t="n">
-        <v>33.13113784790039</v>
+        <v>33.13113403320312</v>
       </c>
     </row>
     <row r="371">
@@ -41614,7 +41614,7 @@
         </is>
       </c>
       <c r="B371" s="2" t="n">
-        <v>33.36896133422852</v>
+        <v>33.36896514892578</v>
       </c>
     </row>
     <row r="372">
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="B372" s="2" t="n">
-        <v>32.79268646240234</v>
+        <v>32.79268264770508</v>
       </c>
     </row>
     <row r="373">
@@ -41634,7 +41634,7 @@
         </is>
       </c>
       <c r="B373" s="2" t="n">
-        <v>33.98181915283203</v>
+        <v>33.9818229675293</v>
       </c>
     </row>
     <row r="374">
@@ -41644,7 +41644,7 @@
         </is>
       </c>
       <c r="B374" s="2" t="n">
-        <v>34.90568923950195</v>
+        <v>34.90568542480469</v>
       </c>
     </row>
     <row r="375">
@@ -41684,7 +41684,7 @@
         </is>
       </c>
       <c r="B378" s="2" t="n">
-        <v>34.98801422119141</v>
+        <v>34.98801803588867</v>
       </c>
     </row>
     <row r="379">
@@ -41694,7 +41694,7 @@
         </is>
       </c>
       <c r="B379" s="2" t="n">
-        <v>34.78676986694336</v>
+        <v>34.78677749633789</v>
       </c>
     </row>
     <row r="380">
@@ -41714,7 +41714,7 @@
         </is>
       </c>
       <c r="B381" s="2" t="n">
-        <v>34.43003845214844</v>
+        <v>34.43003463745117</v>
       </c>
     </row>
     <row r="382">
@@ -41734,7 +41734,7 @@
         </is>
       </c>
       <c r="B383" s="2" t="n">
-        <v>34.54894638061523</v>
+        <v>34.5489501953125</v>
       </c>
     </row>
     <row r="384">
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="B387" s="2" t="n">
-        <v>36.03079223632812</v>
+        <v>36.03079605102539</v>
       </c>
     </row>
     <row r="388">
@@ -41784,7 +41784,7 @@
         </is>
       </c>
       <c r="B388" s="2" t="n">
-        <v>36.16800689697266</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="389">
@@ -41804,7 +41804,7 @@
         </is>
       </c>
       <c r="B390" s="2" t="n">
-        <v>35.71064376831055</v>
+        <v>35.71064758300781</v>
       </c>
     </row>
     <row r="391">
@@ -41824,7 +41824,7 @@
         </is>
       </c>
       <c r="B392" s="2" t="n">
-        <v>35.93017578125</v>
+        <v>35.93017196655273</v>
       </c>
     </row>
     <row r="393">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="B393" s="2" t="n">
-        <v>35.69234848022461</v>
+        <v>35.69235229492188</v>
       </c>
     </row>
     <row r="394">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="B394" s="2" t="n">
-        <v>35.58258056640625</v>
+        <v>35.58258438110352</v>
       </c>
     </row>
     <row r="395">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="B395" s="2" t="n">
-        <v>35.83703231811523</v>
+        <v>35.8370361328125</v>
       </c>
     </row>
     <row r="396">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="B397" s="2" t="n">
-        <v>35.02910232543945</v>
+        <v>35.02909851074219</v>
       </c>
     </row>
     <row r="398">
@@ -41884,7 +41884,7 @@
         </is>
       </c>
       <c r="B398" s="2" t="n">
-        <v>35.13125228881836</v>
+        <v>35.13125610351562</v>
       </c>
     </row>
     <row r="399">
@@ -41894,7 +41894,7 @@
         </is>
       </c>
       <c r="B399" s="2" t="n">
-        <v>35.15911483764648</v>
+        <v>35.15911102294922</v>
       </c>
     </row>
     <row r="400">
@@ -41914,7 +41914,7 @@
         </is>
       </c>
       <c r="B401" s="2" t="n">
-        <v>35.46556854248047</v>
+        <v>35.46557235717773</v>
       </c>
     </row>
     <row r="402">
@@ -41944,7 +41944,7 @@
         </is>
       </c>
       <c r="B404" s="2" t="n">
-        <v>35.62344360351562</v>
+        <v>35.62344741821289</v>
       </c>
     </row>
     <row r="405">
@@ -41964,7 +41964,7 @@
         </is>
       </c>
       <c r="B406" s="2" t="n">
-        <v>35.68844604492188</v>
+        <v>35.68844985961914</v>
       </c>
     </row>
     <row r="407">
@@ -41984,7 +41984,7 @@
         </is>
       </c>
       <c r="B408" s="2" t="n">
-        <v>35.49343109130859</v>
+        <v>35.49343490600586</v>
       </c>
     </row>
     <row r="409">
@@ -41994,7 +41994,7 @@
         </is>
       </c>
       <c r="B409" s="2" t="n">
-        <v>36.56138610839844</v>
+        <v>36.5613899230957</v>
       </c>
     </row>
     <row r="410">
@@ -42014,7 +42014,7 @@
         </is>
       </c>
       <c r="B411" s="2" t="n">
-        <v>37.21144866943359</v>
+        <v>37.21145248413086</v>
       </c>
     </row>
     <row r="412">
@@ -42034,7 +42034,7 @@
         </is>
       </c>
       <c r="B413" s="2" t="n">
-        <v>37.75936126708984</v>
+        <v>37.75936889648438</v>
       </c>
     </row>
     <row r="414">
@@ -42044,7 +42044,7 @@
         </is>
       </c>
       <c r="B414" s="2" t="n">
-        <v>37.91724014282227</v>
+        <v>37.917236328125</v>
       </c>
     </row>
     <row r="415">
@@ -42064,7 +42064,7 @@
         </is>
       </c>
       <c r="B416" s="2" t="n">
-        <v>38.35370635986328</v>
+        <v>38.35370254516602</v>
       </c>
     </row>
     <row r="417">
@@ -42074,7 +42074,7 @@
         </is>
       </c>
       <c r="B417" s="2" t="n">
-        <v>38.14011383056641</v>
+        <v>38.14011001586914</v>
       </c>
     </row>
     <row r="418">
@@ -42084,7 +42084,7 @@
         </is>
       </c>
       <c r="B418" s="2" t="n">
-        <v>37.88009262084961</v>
+        <v>37.88008880615234</v>
       </c>
     </row>
     <row r="419">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="B421" s="2" t="n">
-        <v>39.0316276550293</v>
+        <v>39.03162384033203</v>
       </c>
     </row>
     <row r="422">
@@ -42124,7 +42124,7 @@
         </is>
       </c>
       <c r="B422" s="2" t="n">
-        <v>39.05949020385742</v>
+        <v>39.05948638916016</v>
       </c>
     </row>
     <row r="423">
@@ -42154,7 +42154,7 @@
         </is>
       </c>
       <c r="B425" s="2" t="n">
-        <v>39.28237152099609</v>
+        <v>39.28236770629883</v>
       </c>
     </row>
     <row r="426">
@@ -42164,7 +42164,7 @@
         </is>
       </c>
       <c r="B426" s="2" t="n">
-        <v>38.49300765991211</v>
+        <v>38.49301528930664</v>
       </c>
     </row>
     <row r="427">
@@ -42174,7 +42174,7 @@
         </is>
       </c>
       <c r="B427" s="2" t="n">
-        <v>38.409423828125</v>
+        <v>38.40942764282227</v>
       </c>
     </row>
     <row r="428">
@@ -42194,7 +42194,7 @@
         </is>
       </c>
       <c r="B429" s="2" t="n">
-        <v>38.65087890625</v>
+        <v>38.65087509155273</v>
       </c>
     </row>
     <row r="430">
@@ -42204,7 +42204,7 @@
         </is>
       </c>
       <c r="B430" s="2" t="n">
-        <v>37.96366882324219</v>
+        <v>37.96367263793945</v>
       </c>
     </row>
     <row r="431">
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="B432" s="2" t="n">
-        <v>37.5550537109375</v>
+        <v>37.55505752563477</v>
       </c>
     </row>
     <row r="433">
@@ -42234,7 +42234,7 @@
         </is>
       </c>
       <c r="B433" s="2" t="n">
-        <v>37.50862121582031</v>
+        <v>37.50862503051758</v>
       </c>
     </row>
     <row r="434">
@@ -42254,7 +42254,7 @@
         </is>
       </c>
       <c r="B435" s="2" t="n">
-        <v>37.32289123535156</v>
+        <v>37.32289505004883</v>
       </c>
     </row>
     <row r="436">
@@ -42264,7 +42264,7 @@
         </is>
       </c>
       <c r="B436" s="2" t="n">
-        <v>37.62935256958008</v>
+        <v>37.62934875488281</v>
       </c>
     </row>
     <row r="437">
@@ -42274,7 +42274,7 @@
         </is>
       </c>
       <c r="B437" s="2" t="n">
-        <v>37.56434631347656</v>
+        <v>37.5643424987793</v>
       </c>
     </row>
     <row r="438">
@@ -42284,7 +42284,7 @@
         </is>
       </c>
       <c r="B438" s="2" t="n">
-        <v>37.24860000610352</v>
+        <v>37.24860382080078</v>
       </c>
     </row>
     <row r="439">
@@ -42294,7 +42294,7 @@
         </is>
       </c>
       <c r="B439" s="2" t="n">
-        <v>37.25789260864258</v>
+        <v>37.25788497924805</v>
       </c>
     </row>
     <row r="440">
@@ -42304,7 +42304,7 @@
         </is>
       </c>
       <c r="B440" s="2" t="n">
-        <v>36.84927368164062</v>
+        <v>36.84927749633789</v>
       </c>
     </row>
     <row r="441">
@@ -42314,7 +42314,7 @@
         </is>
       </c>
       <c r="B441" s="2" t="n">
-        <v>36.38494873046875</v>
+        <v>36.38494491577148</v>
       </c>
     </row>
     <row r="442">
@@ -42334,7 +42334,7 @@
         </is>
       </c>
       <c r="B443" s="2" t="n">
-        <v>36.38494873046875</v>
+        <v>36.38494491577148</v>
       </c>
     </row>
     <row r="444">
@@ -42344,7 +42344,7 @@
         </is>
       </c>
       <c r="B444" s="2" t="n">
-        <v>35.56772232055664</v>
+        <v>35.56772613525391</v>
       </c>
     </row>
     <row r="445">
@@ -42354,7 +42354,7 @@
         </is>
       </c>
       <c r="B445" s="2" t="n">
-        <v>35.75345230102539</v>
+        <v>35.75345611572266</v>
       </c>
     </row>
     <row r="446">
@@ -42364,7 +42364,7 @@
         </is>
       </c>
       <c r="B446" s="2" t="n">
-        <v>35.50271606445312</v>
+        <v>35.50271224975586</v>
       </c>
     </row>
     <row r="447">
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="B447" s="2" t="n">
-        <v>36.26422119140625</v>
+        <v>36.26421737670898</v>
       </c>
     </row>
     <row r="448">
@@ -42384,7 +42384,7 @@
         </is>
       </c>
       <c r="B448" s="2" t="n">
-        <v>36.39422988891602</v>
+        <v>36.39423370361328</v>
       </c>
     </row>
     <row r="449">
@@ -42394,7 +42394,7 @@
         </is>
       </c>
       <c r="B449" s="2" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="450">
@@ -42424,7 +42424,7 @@
         </is>
       </c>
       <c r="B452" s="2" t="n">
-        <v>36.12491989135742</v>
+        <v>36.12492370605469</v>
       </c>
     </row>
     <row r="453">
@@ -42434,7 +42434,7 @@
         </is>
       </c>
       <c r="B453" s="2" t="n">
-        <v>35.32627487182617</v>
+        <v>35.32627105712891</v>
       </c>
     </row>
     <row r="454">
@@ -42444,7 +42444,7 @@
         </is>
       </c>
       <c r="B454" s="2" t="n">
-        <v>35.14054107666016</v>
+        <v>35.14053344726562</v>
       </c>
     </row>
     <row r="455">
@@ -42464,7 +42464,7 @@
         </is>
       </c>
       <c r="B456" s="2" t="n">
-        <v>35.21482467651367</v>
+        <v>35.21482849121094</v>
       </c>
     </row>
     <row r="457">
@@ -42474,7 +42474,7 @@
         </is>
       </c>
       <c r="B457" s="2" t="n">
-        <v>34.61120223999023</v>
+        <v>34.6112060546875</v>
       </c>
     </row>
     <row r="458">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="B458" s="2" t="n">
-        <v>35.14054107666016</v>
+        <v>35.14053344726562</v>
       </c>
     </row>
     <row r="459">
@@ -42494,7 +42494,7 @@
         </is>
       </c>
       <c r="B459" s="2" t="n">
-        <v>34.92694473266602</v>
+        <v>34.92694854736328</v>
       </c>
     </row>
     <row r="460">
@@ -42504,7 +42504,7 @@
         </is>
       </c>
       <c r="B460" s="2" t="n">
-        <v>35.05696105957031</v>
+        <v>35.05695724487305</v>
       </c>
     </row>
     <row r="461">
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="B462" s="2" t="n">
-        <v>35.51200103759766</v>
+        <v>35.51200485229492</v>
       </c>
     </row>
     <row r="463">
@@ -42534,7 +42534,7 @@
         </is>
       </c>
       <c r="B463" s="2" t="n">
-        <v>36.00419998168945</v>
+        <v>36.00419616699219</v>
       </c>
     </row>
     <row r="464">
@@ -42544,7 +42544,7 @@
         </is>
       </c>
       <c r="B464" s="2" t="n">
-        <v>35.91131973266602</v>
+        <v>35.91132354736328</v>
       </c>
     </row>
     <row r="465">
@@ -42564,7 +42564,7 @@
         </is>
       </c>
       <c r="B466" s="2" t="n">
-        <v>36.22707366943359</v>
+        <v>36.22706985473633</v>
       </c>
     </row>
     <row r="467">
@@ -42594,7 +42594,7 @@
         </is>
       </c>
       <c r="B469" s="2" t="n">
-        <v>36.64497375488281</v>
+        <v>36.64496994018555</v>
       </c>
     </row>
     <row r="470">
@@ -42604,7 +42604,7 @@
         </is>
       </c>
       <c r="B470" s="2" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="471">
@@ -42614,7 +42614,7 @@
         </is>
       </c>
       <c r="B471" s="2" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="472">
@@ -42634,7 +42634,7 @@
         </is>
       </c>
       <c r="B473" s="2" t="n">
-        <v>36.57995986938477</v>
+        <v>36.5799674987793</v>
       </c>
     </row>
     <row r="474">
@@ -42644,7 +42644,7 @@
         </is>
       </c>
       <c r="B474" s="2" t="n">
-        <v>36.61711120605469</v>
+        <v>36.61711502075195</v>
       </c>
     </row>
     <row r="475">
@@ -42664,7 +42664,7 @@
         </is>
       </c>
       <c r="B476" s="2" t="n">
-        <v>36.57995986938477</v>
+        <v>36.5799674987793</v>
       </c>
     </row>
     <row r="477">
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="B477" s="2" t="n">
-        <v>37.08143997192383</v>
+        <v>37.08144378662109</v>
       </c>
     </row>
     <row r="478">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="B482" s="2" t="n">
-        <v>36.57067489624023</v>
+        <v>36.5706787109375</v>
       </c>
     </row>
     <row r="483">
@@ -42734,7 +42734,7 @@
         </is>
       </c>
       <c r="B483" s="2" t="n">
-        <v>36.22707366943359</v>
+        <v>36.22706985473633</v>
       </c>
     </row>
     <row r="484">
@@ -42754,7 +42754,7 @@
         </is>
       </c>
       <c r="B485" s="2" t="n">
-        <v>35.46556854248047</v>
+        <v>35.46557235717773</v>
       </c>
     </row>
     <row r="486">
@@ -42764,7 +42764,7 @@
         </is>
       </c>
       <c r="B486" s="2" t="n">
-        <v>35.66987991333008</v>
+        <v>35.66987609863281</v>
       </c>
     </row>
     <row r="487">
@@ -42784,7 +42784,7 @@
         </is>
       </c>
       <c r="B488" s="2" t="n">
-        <v>36.33852005004883</v>
+        <v>36.3385124206543</v>
       </c>
     </row>
     <row r="489">
@@ -42794,7 +42794,7 @@
         </is>
       </c>
       <c r="B489" s="2" t="n">
-        <v>36.21778106689453</v>
+        <v>36.21778869628906</v>
       </c>
     </row>
     <row r="490">
@@ -42804,7 +42804,7 @@
         </is>
       </c>
       <c r="B490" s="2" t="n">
-        <v>35.86489105224609</v>
+        <v>35.86489486694336</v>
       </c>
     </row>
     <row r="491">
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="B492" s="2" t="n">
-        <v>36.09706115722656</v>
+        <v>36.0970573425293</v>
       </c>
     </row>
     <row r="493">
@@ -42834,7 +42834,7 @@
         </is>
       </c>
       <c r="B493" s="2" t="n">
-        <v>36.57995986938477</v>
+        <v>36.5799674987793</v>
       </c>
     </row>
     <row r="494">
@@ -42854,7 +42854,7 @@
         </is>
       </c>
       <c r="B495" s="2" t="n">
-        <v>36.37565612792969</v>
+        <v>36.37565994262695</v>
       </c>
     </row>
     <row r="496">
@@ -42864,7 +42864,7 @@
         </is>
       </c>
       <c r="B496" s="2" t="n">
-        <v>36.35708618164062</v>
+        <v>36.35708999633789</v>
       </c>
     </row>
     <row r="497">
@@ -42874,7 +42874,7 @@
         </is>
       </c>
       <c r="B497" s="2" t="n">
-        <v>36.22707366943359</v>
+        <v>36.22706985473633</v>
       </c>
     </row>
     <row r="498">
@@ -42884,7 +42884,7 @@
         </is>
       </c>
       <c r="B498" s="2" t="n">
-        <v>35.79988098144531</v>
+        <v>35.79988479614258</v>
       </c>
     </row>
     <row r="499">
@@ -42894,7 +42894,7 @@
         </is>
       </c>
       <c r="B499" s="2" t="n">
-        <v>36.45923614501953</v>
+        <v>36.45923233032227</v>
       </c>
     </row>
     <row r="500">
@@ -42914,7 +42914,7 @@
         </is>
       </c>
       <c r="B501" s="2" t="n">
-        <v>36.36637115478516</v>
+        <v>36.36637496948242</v>
       </c>
     </row>
     <row r="502">
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="B506" s="2" t="n">
-        <v>35.66059112548828</v>
+        <v>35.66059494018555</v>
       </c>
     </row>
     <row r="507">
@@ -42984,7 +42984,7 @@
         </is>
       </c>
       <c r="B508" s="2" t="n">
-        <v>36.21778106689453</v>
+        <v>36.21778869628906</v>
       </c>
     </row>
     <row r="509">
@@ -42994,7 +42994,7 @@
         </is>
       </c>
       <c r="B509" s="2" t="n">
-        <v>35.79988098144531</v>
+        <v>35.79988479614258</v>
       </c>
     </row>
     <row r="510">
@@ -43004,7 +43004,7 @@
         </is>
       </c>
       <c r="B510" s="2" t="n">
-        <v>35.46556854248047</v>
+        <v>35.46557235717773</v>
       </c>
     </row>
     <row r="511">
@@ -43014,7 +43014,7 @@
         </is>
       </c>
       <c r="B511" s="2" t="n">
-        <v>36.09706115722656</v>
+        <v>36.0970573425293</v>
       </c>
     </row>
     <row r="512">
@@ -43024,7 +43024,7 @@
         </is>
       </c>
       <c r="B512" s="2" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="513">
@@ -43034,7 +43034,7 @@
         </is>
       </c>
       <c r="B513" s="2" t="n">
-        <v>36.7099723815918</v>
+        <v>36.70998001098633</v>
       </c>
     </row>
     <row r="514">
@@ -43074,7 +43074,7 @@
         </is>
       </c>
       <c r="B517" s="2" t="n">
-        <v>37.30643081665039</v>
+        <v>37.30642700195312</v>
       </c>
     </row>
     <row r="518">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="B519" s="2" t="n">
-        <v>37.75568389892578</v>
+        <v>37.75568008422852</v>
       </c>
     </row>
     <row r="520">
@@ -43104,7 +43104,7 @@
         </is>
       </c>
       <c r="B520" s="2" t="n">
-        <v>38.03646469116211</v>
+        <v>38.03646087646484</v>
       </c>
     </row>
     <row r="521">
@@ -43114,7 +43114,7 @@
         </is>
       </c>
       <c r="B521" s="2" t="n">
-        <v>38.39211654663086</v>
+        <v>38.39212036132812</v>
       </c>
     </row>
     <row r="522">
@@ -43134,7 +43134,7 @@
         </is>
       </c>
       <c r="B523" s="2" t="n">
-        <v>37.51233673095703</v>
+        <v>37.51233291625977</v>
       </c>
     </row>
     <row r="524">
@@ -43154,7 +43154,7 @@
         </is>
       </c>
       <c r="B525" s="2" t="n">
-        <v>37.20347595214844</v>
+        <v>37.2034797668457</v>
       </c>
     </row>
     <row r="526">
@@ -43194,7 +43194,7 @@
         </is>
       </c>
       <c r="B529" s="2" t="n">
-        <v>36.93205642700195</v>
+        <v>36.93205261230469</v>
       </c>
     </row>
     <row r="530">
@@ -43204,7 +43204,7 @@
         </is>
       </c>
       <c r="B530" s="2" t="n">
-        <v>36.73550796508789</v>
+        <v>36.73551177978516</v>
       </c>
     </row>
     <row r="531">
@@ -43214,7 +43214,7 @@
         </is>
       </c>
       <c r="B531" s="2" t="n">
-        <v>37.02565383911133</v>
+        <v>37.02565002441406</v>
       </c>
     </row>
     <row r="532">
@@ -43224,7 +43224,7 @@
         </is>
       </c>
       <c r="B532" s="2" t="n">
-        <v>37.43746185302734</v>
+        <v>37.43745803833008</v>
       </c>
     </row>
     <row r="533">
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="B533" s="2" t="n">
-        <v>37.21283721923828</v>
+        <v>37.21283340454102</v>
       </c>
     </row>
     <row r="534">
@@ -43244,7 +43244,7 @@
         </is>
       </c>
       <c r="B534" s="2" t="n">
-        <v>36.45472717285156</v>
+        <v>36.45473098754883</v>
       </c>
     </row>
     <row r="535">
@@ -43284,7 +43284,7 @@
         </is>
       </c>
       <c r="B538" s="2" t="n">
-        <v>38.10197067260742</v>
+        <v>38.10197448730469</v>
       </c>
     </row>
     <row r="539">
@@ -43294,7 +43294,7 @@
         </is>
       </c>
       <c r="B539" s="2" t="n">
-        <v>38.59801864624023</v>
+        <v>38.5980224609375</v>
       </c>
     </row>
     <row r="540">
@@ -43314,7 +43314,7 @@
         </is>
       </c>
       <c r="B541" s="2" t="n">
-        <v>38.4295539855957</v>
+        <v>38.42955780029297</v>
       </c>
     </row>
     <row r="542">
@@ -43354,7 +43354,7 @@
         </is>
       </c>
       <c r="B545" s="2" t="n">
-        <v>37.73696136474609</v>
+        <v>37.73696517944336</v>
       </c>
     </row>
     <row r="546">
@@ -43374,7 +43374,7 @@
         </is>
       </c>
       <c r="B547" s="2" t="n">
-        <v>38.5699462890625</v>
+        <v>38.56994247436523</v>
       </c>
     </row>
     <row r="548">
@@ -43384,7 +43384,7 @@
         </is>
       </c>
       <c r="B548" s="2" t="n">
-        <v>38.79457092285156</v>
+        <v>38.79457473754883</v>
       </c>
     </row>
     <row r="549">
@@ -43394,7 +43394,7 @@
         </is>
       </c>
       <c r="B549" s="2" t="n">
-        <v>38.31723785400391</v>
+        <v>38.31724166870117</v>
       </c>
     </row>
     <row r="550">
@@ -43434,7 +43434,7 @@
         </is>
       </c>
       <c r="B553" s="2" t="n">
-        <v>37.83991622924805</v>
+        <v>37.83991241455078</v>
       </c>
     </row>
     <row r="554">
@@ -43444,7 +43444,7 @@
         </is>
       </c>
       <c r="B554" s="2" t="n">
-        <v>37.98965835571289</v>
+        <v>37.98966217041016</v>
       </c>
     </row>
     <row r="555">
@@ -43464,7 +43464,7 @@
         </is>
       </c>
       <c r="B556" s="2" t="n">
-        <v>37.8867073059082</v>
+        <v>37.88671112060547</v>
       </c>
     </row>
     <row r="557">
@@ -43504,7 +43504,7 @@
         </is>
       </c>
       <c r="B560" s="2" t="n">
-        <v>37.02565383911133</v>
+        <v>37.02565002441406</v>
       </c>
     </row>
     <row r="561">
@@ -43524,7 +43524,7 @@
         </is>
       </c>
       <c r="B562" s="2" t="n">
-        <v>36.42665100097656</v>
+        <v>36.4266471862793</v>
       </c>
     </row>
     <row r="563">
@@ -43534,7 +43534,7 @@
         </is>
       </c>
       <c r="B563" s="2" t="n">
-        <v>36.09906768798828</v>
+        <v>36.09907150268555</v>
       </c>
     </row>
     <row r="564">
@@ -43554,7 +43554,7 @@
         </is>
       </c>
       <c r="B565" s="2" t="n">
-        <v>35.93996429443359</v>
+        <v>35.93996810913086</v>
       </c>
     </row>
     <row r="566">
@@ -43564,7 +43564,7 @@
         </is>
       </c>
       <c r="B566" s="2" t="n">
-        <v>36.02420043945312</v>
+        <v>36.02419662475586</v>
       </c>
     </row>
     <row r="567">
@@ -43584,7 +43584,7 @@
         </is>
       </c>
       <c r="B568" s="2" t="n">
-        <v>36.52024841308594</v>
+        <v>36.52024459838867</v>
       </c>
     </row>
     <row r="569">
@@ -43604,7 +43604,7 @@
         </is>
       </c>
       <c r="B570" s="2" t="n">
-        <v>36.41729354858398</v>
+        <v>36.41728973388672</v>
       </c>
     </row>
     <row r="571">
@@ -43614,7 +43614,7 @@
         </is>
       </c>
       <c r="B571" s="2" t="n">
-        <v>36.77294540405273</v>
+        <v>36.77294921875</v>
       </c>
     </row>
     <row r="572">
@@ -43634,7 +43634,7 @@
         </is>
       </c>
       <c r="B573" s="2" t="n">
-        <v>37.11924743652344</v>
+        <v>37.11923980712891</v>
       </c>
     </row>
     <row r="574">
@@ -43654,7 +43654,7 @@
         </is>
       </c>
       <c r="B575" s="2" t="n">
-        <v>37.09116363525391</v>
+        <v>37.09116744995117</v>
       </c>
     </row>
     <row r="576">
@@ -43664,7 +43664,7 @@
         </is>
       </c>
       <c r="B576" s="2" t="n">
-        <v>36.79166793823242</v>
+        <v>36.79166412353516</v>
       </c>
     </row>
     <row r="577">
@@ -43674,7 +43674,7 @@
         </is>
       </c>
       <c r="B577" s="2" t="n">
-        <v>36.58575820922852</v>
+        <v>36.58576202392578</v>
       </c>
     </row>
     <row r="578">
@@ -43684,7 +43684,7 @@
         </is>
       </c>
       <c r="B578" s="2" t="n">
-        <v>36.15522766113281</v>
+        <v>36.15522384643555</v>
       </c>
     </row>
     <row r="579">
@@ -43694,7 +43694,7 @@
         </is>
       </c>
       <c r="B579" s="2" t="n">
-        <v>36.2301025390625</v>
+        <v>36.23009872436523</v>
       </c>
     </row>
     <row r="580">
@@ -43714,7 +43714,7 @@
         </is>
       </c>
       <c r="B581" s="2" t="n">
-        <v>36.56703948974609</v>
+        <v>36.56704330444336</v>
       </c>
     </row>
     <row r="582">
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="B582" s="2" t="n">
-        <v>36.52024841308594</v>
+        <v>36.52024459838867</v>
       </c>
     </row>
     <row r="583">
@@ -43744,7 +43744,7 @@
         </is>
       </c>
       <c r="B584" s="2" t="n">
-        <v>36.62319946289062</v>
+        <v>36.62319564819336</v>
       </c>
     </row>
     <row r="585">
@@ -43754,7 +43754,7 @@
         </is>
       </c>
       <c r="B585" s="2" t="n">
-        <v>36.57640075683594</v>
+        <v>36.57639694213867</v>
       </c>
     </row>
     <row r="586">
@@ -43774,7 +43774,7 @@
         </is>
       </c>
       <c r="B587" s="2" t="n">
-        <v>36.21138000488281</v>
+        <v>36.21138381958008</v>
       </c>
     </row>
     <row r="588">
@@ -43784,7 +43784,7 @@
         </is>
       </c>
       <c r="B588" s="2" t="n">
-        <v>35.58430480957031</v>
+        <v>35.58430862426758</v>
       </c>
     </row>
     <row r="589">
@@ -43804,7 +43804,7 @@
         </is>
       </c>
       <c r="B590" s="2" t="n">
-        <v>35.84636688232422</v>
+        <v>35.84637451171875</v>
       </c>
     </row>
     <row r="591">
@@ -43824,7 +43824,7 @@
         </is>
       </c>
       <c r="B592" s="2" t="n">
-        <v>35.39711380004883</v>
+        <v>35.39711761474609</v>
       </c>
     </row>
     <row r="593">
@@ -43844,7 +43844,7 @@
         </is>
       </c>
       <c r="B594" s="2" t="n">
-        <v>35.51879119873047</v>
+        <v>35.51879501342773</v>
       </c>
     </row>
     <row r="595">
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="B597" s="2" t="n">
-        <v>34.77004241943359</v>
+        <v>34.77004623413086</v>
       </c>
     </row>
     <row r="598">
@@ -43884,7 +43884,7 @@
         </is>
       </c>
       <c r="B598" s="2" t="n">
-        <v>34.90107727050781</v>
+        <v>34.90107345581055</v>
       </c>
     </row>
     <row r="599">
@@ -43904,7 +43904,7 @@
         </is>
       </c>
       <c r="B600" s="2" t="n">
-        <v>35.23801040649414</v>
+        <v>35.23801422119141</v>
       </c>
     </row>
     <row r="601">
@@ -43924,7 +43924,7 @@
         </is>
       </c>
       <c r="B602" s="2" t="n">
-        <v>35.96804046630859</v>
+        <v>35.96803665161133</v>
       </c>
     </row>
     <row r="603">
@@ -43934,7 +43934,7 @@
         </is>
       </c>
       <c r="B603" s="2" t="n">
-        <v>35.56558227539062</v>
+        <v>35.56559371948242</v>
       </c>
     </row>
     <row r="604">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="B604" s="2" t="n">
-        <v>35.4345588684082</v>
+        <v>35.43455505371094</v>
       </c>
     </row>
     <row r="605">
@@ -43964,7 +43964,7 @@
         </is>
       </c>
       <c r="B606" s="2" t="n">
-        <v>35.60302734375</v>
+        <v>35.60302352905273</v>
       </c>
     </row>
     <row r="607">
@@ -44004,7 +44004,7 @@
         </is>
       </c>
       <c r="B610" s="2" t="n">
-        <v>34.405029296875</v>
+        <v>34.40502548217773</v>
       </c>
     </row>
     <row r="611">
@@ -44074,7 +44074,7 @@
         </is>
       </c>
       <c r="B617" s="2" t="n">
-        <v>34.66708755493164</v>
+        <v>34.66709136962891</v>
       </c>
     </row>
     <row r="618">
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="B619" s="2" t="n">
-        <v>35.99611663818359</v>
+        <v>35.99612045288086</v>
       </c>
     </row>
     <row r="620">
@@ -44124,7 +44124,7 @@
         </is>
       </c>
       <c r="B622" s="2" t="n">
-        <v>35.97740173339844</v>
+        <v>35.97739791870117</v>
       </c>
     </row>
     <row r="623">
@@ -44154,7 +44154,7 @@
         </is>
       </c>
       <c r="B625" s="2" t="n">
-        <v>35.88380432128906</v>
+        <v>35.88380813598633</v>
       </c>
     </row>
     <row r="626">
@@ -44164,7 +44164,7 @@
         </is>
       </c>
       <c r="B626" s="2" t="n">
-        <v>36.83846282958984</v>
+        <v>36.83845901489258</v>
       </c>
     </row>
     <row r="627">
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="B627" s="2" t="n">
-        <v>37.14732360839844</v>
+        <v>37.14731979370117</v>
       </c>
     </row>
     <row r="628">
@@ -44184,7 +44184,7 @@
         </is>
       </c>
       <c r="B628" s="2" t="n">
-        <v>36.79166793823242</v>
+        <v>36.79166412353516</v>
       </c>
     </row>
     <row r="629">
@@ -44194,7 +44194,7 @@
         </is>
       </c>
       <c r="B629" s="2" t="n">
-        <v>36.83846282958984</v>
+        <v>36.83845901489258</v>
       </c>
     </row>
     <row r="630">
@@ -44204,7 +44204,7 @@
         </is>
       </c>
       <c r="B630" s="2" t="n">
-        <v>37.29706573486328</v>
+        <v>37.29706954956055</v>
       </c>
     </row>
     <row r="631">
@@ -44264,7 +44264,7 @@
         </is>
       </c>
       <c r="B636" s="2" t="n">
-        <v>36.95077896118164</v>
+        <v>36.95077514648438</v>
       </c>
     </row>
     <row r="637">
@@ -44274,7 +44274,7 @@
         </is>
       </c>
       <c r="B637" s="2" t="n">
-        <v>37.02565383911133</v>
+        <v>37.02565002441406</v>
       </c>
     </row>
     <row r="638">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="B641" s="2" t="n">
-        <v>36.49216461181641</v>
+        <v>36.49216842651367</v>
       </c>
     </row>
     <row r="642">
@@ -44334,7 +44334,7 @@
         </is>
       </c>
       <c r="B643" s="2" t="n">
-        <v>36.51088714599609</v>
+        <v>36.51087951660156</v>
       </c>
     </row>
     <row r="644">
@@ -44354,7 +44354,7 @@
         </is>
       </c>
       <c r="B645" s="2" t="n">
-        <v>36.73550796508789</v>
+        <v>36.73551177978516</v>
       </c>
     </row>
     <row r="646">
@@ -44364,7 +44364,7 @@
         </is>
       </c>
       <c r="B646" s="2" t="n">
-        <v>37.10052108764648</v>
+        <v>37.10052490234375</v>
       </c>
     </row>
     <row r="647">
@@ -44374,7 +44374,7 @@
         </is>
       </c>
       <c r="B647" s="2" t="n">
-        <v>37.64337158203125</v>
+        <v>37.64337539672852</v>
       </c>
     </row>
     <row r="648">
@@ -44384,7 +44384,7 @@
         </is>
       </c>
       <c r="B648" s="2" t="n">
-        <v>37.41874313354492</v>
+        <v>37.41873931884766</v>
       </c>
     </row>
     <row r="649">
@@ -44394,7 +44394,7 @@
         </is>
       </c>
       <c r="B649" s="2" t="n">
-        <v>37.40002059936523</v>
+        <v>37.40001678466797</v>
       </c>
     </row>
     <row r="650">
@@ -44414,7 +44414,7 @@
         </is>
       </c>
       <c r="B651" s="2" t="n">
-        <v>37.03925323486328</v>
+        <v>37.03925704956055</v>
       </c>
     </row>
     <row r="652">
@@ -44464,7 +44464,7 @@
         </is>
       </c>
       <c r="B656" s="2" t="n">
-        <v>38.36481094360352</v>
+        <v>38.36480712890625</v>
       </c>
     </row>
     <row r="657">
@@ -44524,7 +44524,7 @@
         </is>
       </c>
       <c r="B662" s="2" t="n">
-        <v>37.71633911132812</v>
+        <v>37.71633529663086</v>
       </c>
     </row>
     <row r="663">
@@ -44574,7 +44574,7 @@
         </is>
       </c>
       <c r="B667" s="2" t="n">
-        <v>36.47660446166992</v>
+        <v>36.47660827636719</v>
       </c>
     </row>
     <row r="668">
@@ -44594,7 +44594,7 @@
         </is>
       </c>
       <c r="B669" s="2" t="n">
-        <v>36.22866439819336</v>
+        <v>36.22866058349609</v>
       </c>
     </row>
     <row r="670">
@@ -44604,7 +44604,7 @@
         </is>
       </c>
       <c r="B670" s="2" t="n">
-        <v>36.61011505126953</v>
+        <v>36.61011123657227</v>
       </c>
     </row>
     <row r="671">
@@ -44634,7 +44634,7 @@
         </is>
       </c>
       <c r="B673" s="2" t="n">
-        <v>37.01064682006836</v>
+        <v>37.01064300537109</v>
       </c>
     </row>
     <row r="674">
@@ -44674,7 +44674,7 @@
         </is>
       </c>
       <c r="B677" s="2" t="n">
-        <v>36.81037521362305</v>
+        <v>36.81037902832031</v>
       </c>
     </row>
     <row r="678">
@@ -44684,7 +44684,7 @@
         </is>
       </c>
       <c r="B678" s="2" t="n">
-        <v>36.61011505126953</v>
+        <v>36.61011123657227</v>
       </c>
     </row>
     <row r="679">
@@ -44704,7 +44704,7 @@
         </is>
       </c>
       <c r="B680" s="2" t="n">
-        <v>36.85805892944336</v>
+        <v>36.85806274414062</v>
       </c>
     </row>
     <row r="681">
@@ -44734,7 +44734,7 @@
         </is>
       </c>
       <c r="B683" s="2" t="n">
-        <v>37.79262542724609</v>
+        <v>37.79262924194336</v>
       </c>
     </row>
     <row r="684">
@@ -44774,7 +44774,7 @@
         </is>
       </c>
       <c r="B687" s="2" t="n">
-        <v>37.32534027099609</v>
+        <v>37.32534408569336</v>
       </c>
     </row>
     <row r="688">
@@ -44874,7 +44874,7 @@
         </is>
       </c>
       <c r="B697" s="2" t="n">
-        <v>38.11685943603516</v>
+        <v>38.11686325073242</v>
       </c>
     </row>
     <row r="698">
@@ -44894,7 +44894,7 @@
         </is>
       </c>
       <c r="B699" s="2" t="n">
-        <v>38.60321426391602</v>
+        <v>38.60321807861328</v>
       </c>
     </row>
     <row r="700">
@@ -44914,7 +44914,7 @@
         </is>
       </c>
       <c r="B701" s="2" t="n">
-        <v>38.17407608032227</v>
+        <v>38.17407989501953</v>
       </c>
     </row>
     <row r="702">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="B702" s="2" t="n">
-        <v>38.7271842956543</v>
+        <v>38.72718811035156</v>
       </c>
     </row>
     <row r="703">
@@ -44944,7 +44944,7 @@
         </is>
       </c>
       <c r="B704" s="2" t="n">
-        <v>38.92745208740234</v>
+        <v>38.92745590209961</v>
       </c>
     </row>
     <row r="705">
@@ -44954,7 +44954,7 @@
         </is>
       </c>
       <c r="B705" s="2" t="n">
-        <v>39.01327896118164</v>
+        <v>39.01328277587891</v>
       </c>
     </row>
     <row r="706">
@@ -44964,7 +44964,7 @@
         </is>
       </c>
       <c r="B706" s="2" t="n">
-        <v>39.44241333007812</v>
+        <v>39.44241714477539</v>
       </c>
     </row>
     <row r="707">
@@ -45024,7 +45024,7 @@
         </is>
       </c>
       <c r="B712" s="2" t="n">
-        <v>39.1944694519043</v>
+        <v>39.19447326660156</v>
       </c>
     </row>
     <row r="713">
@@ -45104,7 +45104,7 @@
         </is>
       </c>
       <c r="B720" s="2" t="n">
-        <v>39.36612701416016</v>
+        <v>39.36612319946289</v>
       </c>
     </row>
     <row r="721">
@@ -45114,7 +45114,7 @@
         </is>
       </c>
       <c r="B721" s="2" t="n">
-        <v>39.39473342895508</v>
+        <v>39.39473724365234</v>
       </c>
     </row>
     <row r="722">
@@ -45134,7 +45134,7 @@
         </is>
       </c>
       <c r="B723" s="2" t="n">
-        <v>39.33751678466797</v>
+        <v>39.33752059936523</v>
       </c>
     </row>
     <row r="724">
@@ -45184,7 +45184,7 @@
         </is>
       </c>
       <c r="B728" s="2" t="n">
-        <v>38.65089797973633</v>
+        <v>38.65089416503906</v>
       </c>
     </row>
     <row r="729">
@@ -45264,7 +45264,7 @@
         </is>
       </c>
       <c r="B736" s="2" t="n">
-        <v>38.7271842956543</v>
+        <v>38.72718811035156</v>
       </c>
     </row>
     <row r="737">
@@ -45304,7 +45304,7 @@
         </is>
       </c>
       <c r="B740" s="2" t="n">
-        <v>39.08957290649414</v>
+        <v>39.08956909179688</v>
       </c>
     </row>
     <row r="741">
@@ -45324,7 +45324,7 @@
         </is>
       </c>
       <c r="B742" s="2" t="n">
-        <v>40.13856887817383</v>
+        <v>40.13857269287109</v>
       </c>
     </row>
     <row r="743">
@@ -45334,7 +45334,7 @@
         </is>
       </c>
       <c r="B743" s="2" t="n">
-        <v>40.50095748901367</v>
+        <v>40.50095367431641</v>
       </c>
     </row>
     <row r="744">
@@ -45384,7 +45384,7 @@
         </is>
       </c>
       <c r="B748" s="2" t="n">
-        <v>40.52956008911133</v>
+        <v>40.52956390380859</v>
       </c>
     </row>
     <row r="749">
@@ -45394,7 +45394,7 @@
         </is>
       </c>
       <c r="B749" s="2" t="n">
-        <v>40.8347282409668</v>
+        <v>40.83473205566406</v>
       </c>
     </row>
     <row r="750">
@@ -45414,7 +45414,7 @@
         </is>
       </c>
       <c r="B751" s="2" t="n">
-        <v>41.49273300170898</v>
+        <v>41.49274063110352</v>
       </c>
     </row>
     <row r="752">
@@ -45504,7 +45504,7 @@
         </is>
       </c>
       <c r="B760" s="2" t="n">
-        <v>40.35790634155273</v>
+        <v>40.35791015625</v>
       </c>
     </row>
     <row r="761">
@@ -45524,7 +45524,7 @@
         </is>
       </c>
       <c r="B762" s="2" t="n">
-        <v>39.85248184204102</v>
+        <v>39.85248565673828</v>
       </c>
     </row>
     <row r="763">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="B763" s="2" t="n">
-        <v>40.27207946777344</v>
+        <v>40.2720832824707</v>
       </c>
     </row>
     <row r="764">
@@ -45554,7 +45554,7 @@
         </is>
       </c>
       <c r="B765" s="2" t="n">
-        <v>40.34836959838867</v>
+        <v>40.34837341308594</v>
       </c>
     </row>
     <row r="766">
@@ -45614,7 +45614,7 @@
         </is>
       </c>
       <c r="B771" s="2" t="n">
-        <v>40.50214004516602</v>
+        <v>40.50213623046875</v>
       </c>
     </row>
     <row r="772">
@@ -45624,7 +45624,7 @@
         </is>
       </c>
       <c r="B772" s="2" t="n">
-        <v>40.55014801025391</v>
+        <v>40.55015182495117</v>
       </c>
     </row>
     <row r="773">
@@ -45644,7 +45644,7 @@
         </is>
       </c>
       <c r="B774" s="2" t="n">
-        <v>41.18389892578125</v>
+        <v>41.18389511108398</v>
       </c>
     </row>
     <row r="775">
@@ -45654,7 +45654,7 @@
         </is>
       </c>
       <c r="B775" s="2" t="n">
-        <v>41.11668014526367</v>
+        <v>41.11668395996094</v>
       </c>
     </row>
     <row r="776">
@@ -45664,7 +45664,7 @@
         </is>
       </c>
       <c r="B776" s="2" t="n">
-        <v>40.9726448059082</v>
+        <v>40.97264099121094</v>
       </c>
     </row>
     <row r="777">
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="B777" s="2" t="n">
-        <v>40.9726448059082</v>
+        <v>40.97264099121094</v>
       </c>
     </row>
     <row r="778">
@@ -45684,7 +45684,7 @@
         </is>
       </c>
       <c r="B778" s="2" t="n">
-        <v>40.87662506103516</v>
+        <v>40.87662124633789</v>
       </c>
     </row>
     <row r="779">
@@ -45694,7 +45694,7 @@
         </is>
       </c>
       <c r="B779" s="2" t="n">
-        <v>40.79020309448242</v>
+        <v>40.79020690917969</v>
       </c>
     </row>
     <row r="780">
@@ -45734,7 +45734,7 @@
         </is>
       </c>
       <c r="B783" s="2" t="n">
-        <v>41.11668014526367</v>
+        <v>41.11668395996094</v>
       </c>
     </row>
     <row r="784">
@@ -45754,7 +45754,7 @@
         </is>
       </c>
       <c r="B785" s="2" t="n">
-        <v>41.89445877075195</v>
+        <v>41.89446258544922</v>
       </c>
     </row>
     <row r="786">
@@ -45764,7 +45764,7 @@
         </is>
       </c>
       <c r="B786" s="2" t="n">
-        <v>41.9040641784668</v>
+        <v>41.90406036376953</v>
       </c>
     </row>
     <row r="787">
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="B792" s="2" t="n">
-        <v>42.5282096862793</v>
+        <v>42.52820587158203</v>
       </c>
     </row>
     <row r="793">
@@ -45834,7 +45834,7 @@
         </is>
       </c>
       <c r="B793" s="2" t="n">
-        <v>41.83684539794922</v>
+        <v>41.83684921264648</v>
       </c>
     </row>
     <row r="794">
@@ -45854,7 +45854,7 @@
         </is>
       </c>
       <c r="B795" s="2" t="n">
-        <v>41.03985977172852</v>
+        <v>41.03986358642578</v>
       </c>
     </row>
     <row r="796">
@@ -45864,7 +45864,7 @@
         </is>
       </c>
       <c r="B796" s="2" t="n">
-        <v>41.38554382324219</v>
+        <v>41.38554000854492</v>
       </c>
     </row>
     <row r="797">
@@ -45894,7 +45894,7 @@
         </is>
       </c>
       <c r="B799" s="2" t="n">
-        <v>40.2620849609375</v>
+        <v>40.26208114624023</v>
       </c>
     </row>
     <row r="800">
@@ -45924,7 +45924,7 @@
         </is>
       </c>
       <c r="B802" s="2" t="n">
-        <v>40.35810470581055</v>
+        <v>40.35810089111328</v>
       </c>
     </row>
     <row r="803">
@@ -45974,7 +45974,7 @@
         </is>
       </c>
       <c r="B807" s="2" t="n">
-        <v>39.03300094604492</v>
+        <v>39.03299713134766</v>
       </c>
     </row>
     <row r="808">
@@ -46004,7 +46004,7 @@
         </is>
       </c>
       <c r="B810" s="2" t="n">
-        <v>40.38691329956055</v>
+        <v>40.38690948486328</v>
       </c>
     </row>
     <row r="811">
@@ -46024,7 +46024,7 @@
         </is>
       </c>
       <c r="B812" s="2" t="n">
-        <v>40.9726448059082</v>
+        <v>40.97264099121094</v>
       </c>
     </row>
     <row r="813">
@@ -46034,7 +46034,7 @@
         </is>
       </c>
       <c r="B813" s="2" t="n">
-        <v>40.75179290771484</v>
+        <v>40.75179672241211</v>
       </c>
     </row>
     <row r="814">
@@ -46044,7 +46044,7 @@
         </is>
       </c>
       <c r="B814" s="2" t="n">
-        <v>41.20310211181641</v>
+        <v>41.20309829711914</v>
       </c>
     </row>
     <row r="815">
@@ -46054,7 +46054,7 @@
         </is>
       </c>
       <c r="B815" s="2" t="n">
-        <v>41.68320846557617</v>
+        <v>41.68321228027344</v>
       </c>
     </row>
     <row r="816">
@@ -46064,7 +46064,7 @@
         </is>
       </c>
       <c r="B816" s="2" t="n">
-        <v>42.08650207519531</v>
+        <v>42.08650588989258</v>
       </c>
     </row>
     <row r="817">
@@ -46074,7 +46074,7 @@
         </is>
       </c>
       <c r="B817" s="2" t="n">
-        <v>41.76002883911133</v>
+        <v>41.76003265380859</v>
       </c>
     </row>
     <row r="818">
@@ -46114,7 +46114,7 @@
         </is>
       </c>
       <c r="B821" s="2" t="n">
-        <v>41.74082565307617</v>
+        <v>41.74082946777344</v>
       </c>
     </row>
     <row r="822">
@@ -46204,7 +46204,7 @@
         </is>
       </c>
       <c r="B830" s="2" t="n">
-        <v>40.45413208007812</v>
+        <v>40.45412826538086</v>
       </c>
     </row>
     <row r="831">
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="B837" s="2" t="n">
-        <v>41.16468811035156</v>
+        <v>41.16469192504883</v>
       </c>
     </row>
     <row r="838">
@@ -46344,7 +46344,7 @@
         </is>
       </c>
       <c r="B844" s="2" t="n">
-        <v>44.75591659545898</v>
+        <v>44.75592041015625</v>
       </c>
     </row>
     <row r="845">
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="B848" s="2" t="n">
-        <v>44.68870544433594</v>
+        <v>44.68870162963867</v>
       </c>
     </row>
     <row r="849">
@@ -46404,7 +46404,7 @@
         </is>
       </c>
       <c r="B850" s="2" t="n">
-        <v>45.47608184814453</v>
+        <v>45.4760856628418</v>
       </c>
     </row>
     <row r="851">
@@ -46444,7 +46444,7 @@
         </is>
       </c>
       <c r="B854" s="2" t="n">
-        <v>44.51586532592773</v>
+        <v>44.51586151123047</v>
       </c>
     </row>
     <row r="855">
@@ -46454,7 +46454,7 @@
         </is>
       </c>
       <c r="B855" s="2" t="n">
-        <v>44.33341979980469</v>
+        <v>44.33342361450195</v>
       </c>
     </row>
     <row r="856">
@@ -46484,7 +46484,7 @@
         </is>
       </c>
       <c r="B858" s="2" t="n">
-        <v>43.6612663269043</v>
+        <v>43.66126251220703</v>
       </c>
     </row>
     <row r="859">
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="B867" s="2" t="n">
-        <v>42.96030426025391</v>
+        <v>42.96030807495117</v>
       </c>
     </row>
     <row r="868">
@@ -46604,7 +46604,7 @@
         </is>
       </c>
       <c r="B870" s="2" t="n">
-        <v>42.96030426025391</v>
+        <v>42.96030807495117</v>
       </c>
     </row>
     <row r="871">
@@ -46624,7 +46624,7 @@
         </is>
       </c>
       <c r="B872" s="2" t="n">
-        <v>43.0083122253418</v>
+        <v>43.00831604003906</v>
       </c>
     </row>
     <row r="873">
@@ -46634,7 +46634,7 @@
         </is>
       </c>
       <c r="B873" s="2" t="n">
-        <v>43.95893096923828</v>
+        <v>43.95893478393555</v>
       </c>
     </row>
     <row r="874">
@@ -46664,7 +46664,7 @@
         </is>
       </c>
       <c r="B876" s="2" t="n">
-        <v>41.74082565307617</v>
+        <v>41.74082946777344</v>
       </c>
     </row>
     <row r="877">
@@ -46714,7 +46714,7 @@
         </is>
       </c>
       <c r="B881" s="2" t="n">
-        <v>41.68320846557617</v>
+        <v>41.68321228027344</v>
       </c>
     </row>
     <row r="882">
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="B882" s="2" t="n">
-        <v>41.63520050048828</v>
+        <v>41.63519668579102</v>
       </c>
     </row>
     <row r="883">
@@ -46804,7 +46804,7 @@
         </is>
       </c>
       <c r="B890" s="2" t="n">
-        <v>41.78883361816406</v>
+        <v>41.78883743286133</v>
       </c>
     </row>
     <row r="891">
@@ -46814,7 +46814,7 @@
         </is>
       </c>
       <c r="B891" s="2" t="n">
-        <v>41.89445877075195</v>
+        <v>41.89446258544922</v>
       </c>
     </row>
     <row r="892">
@@ -46834,7 +46834,7 @@
         </is>
       </c>
       <c r="B893" s="2" t="n">
-        <v>42.10570907592773</v>
+        <v>42.10570526123047</v>
       </c>
     </row>
     <row r="894">
